--- a/research/traditional_assets/database/data/new_zealand/new_zealand_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_telecom_wireless.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nzse_vtl" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,118 +590,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0204</v>
+        <v>-0.0509</v>
       </c>
       <c r="G2">
-        <v>0.1743455497382199</v>
+        <v>0.2031055900621118</v>
       </c>
       <c r="H2">
-        <v>0.1743455497382199</v>
+        <v>0.2031055900621118</v>
       </c>
       <c r="I2">
-        <v>-0.04523560209424084</v>
+        <v>0.03503105590062111</v>
       </c>
       <c r="J2">
-        <v>-0.04523560209424084</v>
+        <v>0.03503105590062111</v>
       </c>
       <c r="K2">
-        <v>-11.9</v>
+        <v>-0.112</v>
       </c>
       <c r="L2">
-        <v>-0.6230366492146596</v>
+        <v>-0.006956521739130434</v>
       </c>
       <c r="M2">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.06924101198402131</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.04369747899159664</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.06924101198402131</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.04369747899159664</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>0.8070000000000001</v>
+        <v>0.308</v>
       </c>
       <c r="V2">
-        <v>0.10745672436751</v>
+        <v>0.04673748103186647</v>
       </c>
       <c r="W2">
-        <v>-0.4075342465753425</v>
+        <v>-0.008296296296296296</v>
       </c>
       <c r="X2">
-        <v>0.1634220026903123</v>
+        <v>0.1400136922257926</v>
       </c>
       <c r="Y2">
-        <v>-0.5709562492656548</v>
+        <v>-0.1483099885220889</v>
       </c>
       <c r="Z2">
-        <v>0.463907509958224</v>
+        <v>0.416095934665185</v>
       </c>
       <c r="AA2">
-        <v>-0.02098513552900029</v>
+        <v>0.01457627994727729</v>
       </c>
       <c r="AB2">
-        <v>0.06947285109532214</v>
+        <v>0.06152557689130193</v>
       </c>
       <c r="AC2">
-        <v>-0.09045798662432243</v>
+        <v>-0.04694929694402465</v>
       </c>
       <c r="AD2">
-        <v>26</v>
+        <v>22.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>26</v>
+        <v>22.5</v>
       </c>
       <c r="AG2">
-        <v>25.193</v>
+        <v>22.192</v>
       </c>
       <c r="AH2">
-        <v>0.7758877946881528</v>
+        <v>0.7734616706772086</v>
       </c>
       <c r="AI2">
-        <v>0.6582278481012658</v>
+        <v>0.6302521008403361</v>
       </c>
       <c r="AJ2">
-        <v>0.770357459560285</v>
+        <v>0.7710374539642832</v>
       </c>
       <c r="AK2">
-        <v>0.6510996821130438</v>
+        <v>0.6270343580470163</v>
       </c>
       <c r="AL2">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AM2">
-        <v>1.504</v>
+        <v>1.779</v>
       </c>
       <c r="AN2">
-        <v>7.807807807807808</v>
+        <v>6.880733944954128</v>
       </c>
       <c r="AO2">
-        <v>-0.5647058823529412</v>
+        <v>0.3081967213114754</v>
       </c>
       <c r="AP2">
-        <v>7.565465465465466</v>
+        <v>6.786544342507645</v>
       </c>
       <c r="AQ2">
-        <v>-0.5744680851063829</v>
+        <v>0.3170320404721753</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +718,8887 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0204</v>
+        <v>-0.0509</v>
       </c>
       <c r="G3">
-        <v>0.1743455497382199</v>
+        <v>0.2031055900621118</v>
       </c>
       <c r="H3">
-        <v>0.1743455497382199</v>
+        <v>0.2031055900621118</v>
       </c>
       <c r="I3">
-        <v>-0.04523560209424084</v>
+        <v>0.03503105590062111</v>
       </c>
       <c r="J3">
-        <v>-0.04523560209424084</v>
+        <v>0.03503105590062111</v>
       </c>
       <c r="K3">
-        <v>-11.9</v>
+        <v>-0.112</v>
       </c>
       <c r="L3">
-        <v>-0.6230366492146596</v>
+        <v>-0.006956521739130434</v>
       </c>
       <c r="M3">
+        <v>-0</v>
+      </c>
+      <c r="N3">
+        <v>-0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0.308</v>
+      </c>
+      <c r="V3">
+        <v>0.04673748103186647</v>
+      </c>
+      <c r="W3">
+        <v>-0.008296296296296296</v>
+      </c>
+      <c r="X3">
+        <v>0.1400136922257926</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1483099885220889</v>
+      </c>
+      <c r="Z3">
+        <v>0.416095934665185</v>
+      </c>
+      <c r="AA3">
+        <v>0.01457627994727729</v>
+      </c>
+      <c r="AB3">
+        <v>0.06152557689130193</v>
+      </c>
+      <c r="AC3">
+        <v>-0.04694929694402465</v>
+      </c>
+      <c r="AD3">
+        <v>22.5</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>22.5</v>
+      </c>
+      <c r="AG3">
+        <v>22.192</v>
+      </c>
+      <c r="AH3">
+        <v>0.7734616706772086</v>
+      </c>
+      <c r="AI3">
+        <v>0.6302521008403361</v>
+      </c>
+      <c r="AJ3">
+        <v>0.7710374539642832</v>
+      </c>
+      <c r="AK3">
+        <v>0.6270343580470163</v>
+      </c>
+      <c r="AL3">
+        <v>1.83</v>
+      </c>
+      <c r="AM3">
+        <v>1.779</v>
+      </c>
+      <c r="AN3">
+        <v>6.880733944954128</v>
+      </c>
+      <c r="AO3">
+        <v>0.3081967213114754</v>
+      </c>
+      <c r="AP3">
+        <v>6.786544342507645</v>
+      </c>
+      <c r="AQ3">
+        <v>0.3170320404721753</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Vital Limited (NZSE:VTL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NZSE:VTL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Telecom (Wireless)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1.66830601092896</v>
+      </c>
+      <c r="F2">
+        <v>4.54290677376211</v>
+      </c>
+      <c r="G2">
+        <v>6.88073394495413</v>
+      </c>
+      <c r="H2">
+        <v>8.362262996941899</v>
+      </c>
+      <c r="I2">
+        <v>0.7734616706772089</v>
+      </c>
+      <c r="J2">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K2">
+        <v>6.59</v>
+      </c>
+      <c r="L2">
+        <v>6.43571230288364</v>
+      </c>
+      <c r="M2">
+        <v>28.782</v>
+      </c>
+      <c r="N2">
+        <v>33.4723123028836</v>
+      </c>
+      <c r="O2">
+        <v>22.5</v>
+      </c>
+      <c r="P2">
+        <v>27.3446</v>
+      </c>
+      <c r="Q2">
+        <v>0.0615255768913019</v>
+      </c>
+      <c r="R2">
+        <v>0.0583411523460571</v>
+      </c>
+      <c r="S2">
+        <v>0.03853728</v>
+      </c>
+      <c r="T2">
+        <v>0.036648</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.140013692225793</v>
+      </c>
+      <c r="X2">
+        <v>0.398200539100953</v>
+      </c>
+      <c r="Y2">
+        <v>2.20029765708245</v>
+      </c>
+      <c r="Z2">
+        <v>7.8130551978468</v>
+      </c>
+      <c r="AA2">
+        <v>22.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.053524</v>
+      </c>
+      <c r="AC2">
+        <v>1.668306010928962</v>
+      </c>
+      <c r="AD2">
+        <v>22.5</v>
+      </c>
+      <c r="AE2">
+        <v>1.83</v>
+      </c>
+      <c r="AF2">
+        <v>0.217</v>
+      </c>
+      <c r="AG2">
+        <v>3.27</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>6.59</v>
+      </c>
+      <c r="AK2">
+        <v>0.046</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.28</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>1.88</v>
+      </c>
+      <c r="AR2">
+        <v>1.83</v>
+      </c>
+      <c r="AS2">
+        <v>22.5</v>
+      </c>
+      <c r="AT2">
+        <v>0.308</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.06806714487792773</v>
+      </c>
+      <c r="C2">
+        <v>22.65686787944739</v>
+      </c>
+      <c r="D2">
+        <v>22.34886787944739</v>
+      </c>
+      <c r="E2">
+        <v>-22.5</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.308</v>
+      </c>
+      <c r="H2">
+        <v>6.59</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>6.54</v>
+      </c>
+      <c r="K2">
+        <v>0.217</v>
+      </c>
+      <c r="L2">
+        <v>6.323</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>6.323</v>
+      </c>
+      <c r="O2">
+        <v>1.77044</v>
+      </c>
+      <c r="P2">
+        <v>4.55256</v>
+      </c>
+      <c r="Q2">
+        <v>4.769559999999999</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.06806714487792773</v>
+      </c>
+      <c r="T2">
+        <v>0.6362422799549508</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.28</v>
+      </c>
+      <c r="W2">
+        <v>0.032184</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.06791903687226954</v>
+      </c>
+      <c r="C3">
+        <v>22.47964080980092</v>
+      </c>
+      <c r="D3">
+        <v>22.46254080980092</v>
+      </c>
+      <c r="E3">
+        <v>-22.2091</v>
+      </c>
+      <c r="F3">
+        <v>0.2909</v>
+      </c>
+      <c r="G3">
+        <v>0.308</v>
+      </c>
+      <c r="H3">
+        <v>6.59</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>6.54</v>
+      </c>
+      <c r="K3">
+        <v>0.217</v>
+      </c>
+      <c r="L3">
+        <v>6.323</v>
+      </c>
+      <c r="M3">
+        <v>0.01300323</v>
+      </c>
+      <c r="N3">
+        <v>6.309996770000001</v>
+      </c>
+      <c r="O3">
+        <v>1.7667990956</v>
+      </c>
+      <c r="P3">
+        <v>4.5431976744</v>
+      </c>
+      <c r="Q3">
+        <v>4.7601976744</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.0682799968406763</v>
+      </c>
+      <c r="T3">
+        <v>0.6408694965364413</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.28</v>
+      </c>
+      <c r="W3">
+        <v>0.032184</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>486.2637975333821</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.06777092886661133</v>
+      </c>
+      <c r="C4">
+        <v>22.30357599981755</v>
+      </c>
+      <c r="D4">
+        <v>22.57737599981755</v>
+      </c>
+      <c r="E4">
+        <v>-21.9182</v>
+      </c>
+      <c r="F4">
+        <v>0.5818</v>
+      </c>
+      <c r="G4">
+        <v>0.308</v>
+      </c>
+      <c r="H4">
+        <v>6.59</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>6.54</v>
+      </c>
+      <c r="K4">
+        <v>0.217</v>
+      </c>
+      <c r="L4">
+        <v>6.323</v>
+      </c>
+      <c r="M4">
+        <v>0.02600646</v>
+      </c>
+      <c r="N4">
+        <v>6.296993540000001</v>
+      </c>
+      <c r="O4">
+        <v>1.7631581912</v>
+      </c>
+      <c r="P4">
+        <v>4.5338353488</v>
+      </c>
+      <c r="Q4">
+        <v>4.7508353488</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.06849719272103198</v>
+      </c>
+      <c r="T4">
+        <v>0.6455911461093908</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.28</v>
+      </c>
+      <c r="W4">
+        <v>0.032184</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>243.1318987666911</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.06762282086095314</v>
+      </c>
+      <c r="C5">
+        <v>22.12869136654587</v>
+      </c>
+      <c r="D5">
+        <v>22.69339136654587</v>
+      </c>
+      <c r="E5">
+        <v>-21.6273</v>
+      </c>
+      <c r="F5">
+        <v>0.8726999999999999</v>
+      </c>
+      <c r="G5">
+        <v>0.308</v>
+      </c>
+      <c r="H5">
+        <v>6.59</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>6.54</v>
+      </c>
+      <c r="K5">
+        <v>0.217</v>
+      </c>
+      <c r="L5">
+        <v>6.323</v>
+      </c>
+      <c r="M5">
+        <v>0.03900969</v>
+      </c>
+      <c r="N5">
+        <v>6.28399031</v>
+      </c>
+      <c r="O5">
+        <v>1.7595172868</v>
+      </c>
+      <c r="P5">
+        <v>4.5244730232</v>
+      </c>
+      <c r="Q5">
+        <v>4.741473023199999</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.06871886686696201</v>
+      </c>
+      <c r="T5">
+        <v>0.6504101492817826</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.28</v>
+      </c>
+      <c r="W5">
+        <v>0.032184</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>162.0879325111274</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.06747471285529495</v>
+      </c>
+      <c r="C6">
+        <v>21.9550051972085</v>
+      </c>
+      <c r="D6">
+        <v>22.8106051972085</v>
+      </c>
+      <c r="E6">
+        <v>-21.3364</v>
+      </c>
+      <c r="F6">
+        <v>1.1636</v>
+      </c>
+      <c r="G6">
+        <v>0.308</v>
+      </c>
+      <c r="H6">
+        <v>6.59</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>6.54</v>
+      </c>
+      <c r="K6">
+        <v>0.217</v>
+      </c>
+      <c r="L6">
+        <v>6.323</v>
+      </c>
+      <c r="M6">
+        <v>0.05201292</v>
+      </c>
+      <c r="N6">
+        <v>6.27098708</v>
+      </c>
+      <c r="O6">
+        <v>1.7558763824</v>
+      </c>
+      <c r="P6">
+        <v>4.5151106976</v>
+      </c>
+      <c r="Q6">
+        <v>4.7321106976</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.06894515922426557</v>
+      </c>
+      <c r="T6">
+        <v>0.6553295483535992</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.28</v>
+      </c>
+      <c r="W6">
+        <v>0.032184</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>121.5659493833455</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.06732660484963675</v>
+      </c>
+      <c r="C7">
+        <v>21.78253615881163</v>
+      </c>
+      <c r="D7">
+        <v>22.92903615881163</v>
+      </c>
+      <c r="E7">
+        <v>-21.0455</v>
+      </c>
+      <c r="F7">
+        <v>1.4545</v>
+      </c>
+      <c r="G7">
+        <v>0.308</v>
+      </c>
+      <c r="H7">
+        <v>6.59</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>6.54</v>
+      </c>
+      <c r="K7">
+        <v>0.217</v>
+      </c>
+      <c r="L7">
+        <v>6.323</v>
+      </c>
+      <c r="M7">
+        <v>0.06501615000000001</v>
+      </c>
+      <c r="N7">
+        <v>6.25798385</v>
+      </c>
+      <c r="O7">
+        <v>1.752235478</v>
+      </c>
+      <c r="P7">
+        <v>4.505748372</v>
+      </c>
+      <c r="Q7">
+        <v>4.722748372</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.06917621563119658</v>
+      </c>
+      <c r="T7">
+        <v>0.6603525137216646</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.28</v>
+      </c>
+      <c r="W7">
+        <v>0.032184</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>97.25275950667641</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.06717849684397854</v>
+      </c>
+      <c r="C8">
+        <v>21.61130330805555</v>
+      </c>
+      <c r="D8">
+        <v>23.04870330805555</v>
+      </c>
+      <c r="E8">
+        <v>-20.7546</v>
+      </c>
+      <c r="F8">
+        <v>1.7454</v>
+      </c>
+      <c r="G8">
+        <v>0.308</v>
+      </c>
+      <c r="H8">
+        <v>6.59</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>6.54</v>
+      </c>
+      <c r="K8">
+        <v>0.217</v>
+      </c>
+      <c r="L8">
+        <v>6.323</v>
+      </c>
+      <c r="M8">
+        <v>0.07801938</v>
+      </c>
+      <c r="N8">
+        <v>6.244980620000001</v>
+      </c>
+      <c r="O8">
+        <v>1.7485945736</v>
+      </c>
+      <c r="P8">
+        <v>4.496386046400001</v>
+      </c>
+      <c r="Q8">
+        <v>4.7133860464</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.06941218813189208</v>
+      </c>
+      <c r="T8">
+        <v>0.665482350693306</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.28</v>
+      </c>
+      <c r="W8">
+        <v>0.032184</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>81.04396625556369</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.06703038883832034</v>
+      </c>
+      <c r="C9">
+        <v>21.44132610155707</v>
+      </c>
+      <c r="D9">
+        <v>23.16962610155707</v>
+      </c>
+      <c r="E9">
+        <v>-20.4637</v>
+      </c>
+      <c r="F9">
+        <v>2.0363</v>
+      </c>
+      <c r="G9">
+        <v>0.308</v>
+      </c>
+      <c r="H9">
+        <v>6.59</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>6.54</v>
+      </c>
+      <c r="K9">
+        <v>0.217</v>
+      </c>
+      <c r="L9">
+        <v>6.323</v>
+      </c>
+      <c r="M9">
+        <v>0.09102261000000002</v>
+      </c>
+      <c r="N9">
+        <v>6.23197739</v>
+      </c>
+      <c r="O9">
+        <v>1.7449536692</v>
+      </c>
+      <c r="P9">
+        <v>4.4870237208</v>
+      </c>
+      <c r="Q9">
+        <v>4.7040237208</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.06965323531002188</v>
+      </c>
+      <c r="T9">
+        <v>0.6707225067396061</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.28</v>
+      </c>
+      <c r="W9">
+        <v>0.032184</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>69.46625679048314</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.06688228083266216</v>
+      </c>
+      <c r="C10">
+        <v>21.27262440639547</v>
+      </c>
+      <c r="D10">
+        <v>23.29182440639547</v>
+      </c>
+      <c r="E10">
+        <v>-20.1728</v>
+      </c>
+      <c r="F10">
+        <v>2.3272</v>
+      </c>
+      <c r="G10">
+        <v>0.308</v>
+      </c>
+      <c r="H10">
+        <v>6.59</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>6.54</v>
+      </c>
+      <c r="K10">
+        <v>0.217</v>
+      </c>
+      <c r="L10">
+        <v>6.323</v>
+      </c>
+      <c r="M10">
+        <v>0.10402584</v>
+      </c>
+      <c r="N10">
+        <v>6.21897416</v>
+      </c>
+      <c r="O10">
+        <v>1.7413127648</v>
+      </c>
+      <c r="P10">
+        <v>4.4776613952</v>
+      </c>
+      <c r="Q10">
+        <v>4.6946613952</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.06989952264419799</v>
+      </c>
+      <c r="T10">
+        <v>0.6760765792216955</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.28</v>
+      </c>
+      <c r="W10">
+        <v>0.032184</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>60.78297469167276</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.06673417282700397</v>
+      </c>
+      <c r="C11">
+        <v>21.10521851099401</v>
+      </c>
+      <c r="D11">
+        <v>23.41531851099402</v>
+      </c>
+      <c r="E11">
+        <v>-19.8819</v>
+      </c>
+      <c r="F11">
+        <v>2.6181</v>
+      </c>
+      <c r="G11">
+        <v>0.308</v>
+      </c>
+      <c r="H11">
+        <v>6.59</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>6.54</v>
+      </c>
+      <c r="K11">
+        <v>0.217</v>
+      </c>
+      <c r="L11">
+        <v>6.323</v>
+      </c>
+      <c r="M11">
+        <v>0.11702907</v>
+      </c>
+      <c r="N11">
+        <v>6.20597093</v>
+      </c>
+      <c r="O11">
+        <v>1.7376718604</v>
+      </c>
+      <c r="P11">
+        <v>4.4682990696</v>
+      </c>
+      <c r="Q11">
+        <v>4.6852990696</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.07015122288681755</v>
+      </c>
+      <c r="T11">
+        <v>0.6815483236264682</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.28</v>
+      </c>
+      <c r="W11">
+        <v>0.032184</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>54.02931083704245</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.06658606482134576</v>
+      </c>
+      <c r="C12">
+        <v>20.93912913634933</v>
+      </c>
+      <c r="D12">
+        <v>23.54012913634933</v>
+      </c>
+      <c r="E12">
+        <v>-19.591</v>
+      </c>
+      <c r="F12">
+        <v>2.909</v>
+      </c>
+      <c r="G12">
+        <v>0.308</v>
+      </c>
+      <c r="H12">
+        <v>6.59</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>6.54</v>
+      </c>
+      <c r="K12">
+        <v>0.217</v>
+      </c>
+      <c r="L12">
+        <v>6.323</v>
+      </c>
+      <c r="M12">
+        <v>0.1300323</v>
+      </c>
+      <c r="N12">
+        <v>6.192967700000001</v>
+      </c>
+      <c r="O12">
+        <v>1.734030956</v>
+      </c>
+      <c r="P12">
+        <v>4.458936744000001</v>
+      </c>
+      <c r="Q12">
+        <v>4.675936744</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.07040851646816196</v>
+      </c>
+      <c r="T12">
+        <v>0.6871416623513469</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.28</v>
+      </c>
+      <c r="W12">
+        <v>0.032184</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>48.62637975333821</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.06643795681568757</v>
+      </c>
+      <c r="C13">
+        <v>20.77437744762182</v>
+      </c>
+      <c r="D13">
+        <v>23.66627744762182</v>
+      </c>
+      <c r="E13">
+        <v>-19.3001</v>
+      </c>
+      <c r="F13">
+        <v>3.1999</v>
+      </c>
+      <c r="G13">
+        <v>0.308</v>
+      </c>
+      <c r="H13">
+        <v>6.59</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>6.54</v>
+      </c>
+      <c r="K13">
+        <v>0.217</v>
+      </c>
+      <c r="L13">
+        <v>6.323</v>
+      </c>
+      <c r="M13">
+        <v>0.14303553</v>
+      </c>
+      <c r="N13">
+        <v>6.179964470000001</v>
+      </c>
+      <c r="O13">
+        <v>1.7303900516</v>
+      </c>
+      <c r="P13">
+        <v>4.4495744184</v>
+      </c>
+      <c r="Q13">
+        <v>4.6665744184</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.07067159192773884</v>
+      </c>
+      <c r="T13">
+        <v>0.6928606940812789</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.28</v>
+      </c>
+      <c r="W13">
+        <v>0.032184</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>44.20579977576201</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.06628984881002936</v>
+      </c>
+      <c r="C14">
+        <v>20.61098506610105</v>
+      </c>
+      <c r="D14">
+        <v>23.79378506610105</v>
+      </c>
+      <c r="E14">
+        <v>-19.0092</v>
+      </c>
+      <c r="F14">
+        <v>3.4908</v>
+      </c>
+      <c r="G14">
+        <v>0.308</v>
+      </c>
+      <c r="H14">
+        <v>6.59</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>6.54</v>
+      </c>
+      <c r="K14">
+        <v>0.217</v>
+      </c>
+      <c r="L14">
+        <v>6.323</v>
+      </c>
+      <c r="M14">
+        <v>0.15603876</v>
+      </c>
+      <c r="N14">
+        <v>6.16696124</v>
+      </c>
+      <c r="O14">
+        <v>1.7267491472</v>
+      </c>
+      <c r="P14">
+        <v>4.4402120928</v>
+      </c>
+      <c r="Q14">
+        <v>4.657212092799999</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.07094064637503336</v>
+      </c>
+      <c r="T14">
+        <v>0.6987097038050731</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.28</v>
+      </c>
+      <c r="W14">
+        <v>0.032184</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>40.52198312778184</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.06614174080437116</v>
+      </c>
+      <c r="C15">
+        <v>20.44897408155967</v>
+      </c>
+      <c r="D15">
+        <v>23.92267408155967</v>
+      </c>
+      <c r="E15">
+        <v>-18.7183</v>
+      </c>
+      <c r="F15">
+        <v>3.7817</v>
+      </c>
+      <c r="G15">
+        <v>0.308</v>
+      </c>
+      <c r="H15">
+        <v>6.59</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>6.54</v>
+      </c>
+      <c r="K15">
+        <v>0.217</v>
+      </c>
+      <c r="L15">
+        <v>6.323</v>
+      </c>
+      <c r="M15">
+        <v>0.16904199</v>
+      </c>
+      <c r="N15">
+        <v>6.15395801</v>
+      </c>
+      <c r="O15">
+        <v>1.7231082428</v>
+      </c>
+      <c r="P15">
+        <v>4.4308497672</v>
+      </c>
+      <c r="Q15">
+        <v>4.647849767199999</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.07121588598203582</v>
+      </c>
+      <c r="T15">
+        <v>0.7046931735225178</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.28</v>
+      </c>
+      <c r="W15">
+        <v>0.032184</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>37.40490750256784</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.06599363279871297</v>
+      </c>
+      <c r="C16">
+        <v>20.28836706501123</v>
+      </c>
+      <c r="D16">
+        <v>24.05296706501123</v>
+      </c>
+      <c r="E16">
+        <v>-18.4274</v>
+      </c>
+      <c r="F16">
+        <v>4.0726</v>
+      </c>
+      <c r="G16">
+        <v>0.308</v>
+      </c>
+      <c r="H16">
+        <v>6.59</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>6.54</v>
+      </c>
+      <c r="K16">
+        <v>0.217</v>
+      </c>
+      <c r="L16">
+        <v>6.323</v>
+      </c>
+      <c r="M16">
+        <v>0.18204522</v>
+      </c>
+      <c r="N16">
+        <v>6.14095478</v>
+      </c>
+      <c r="O16">
+        <v>1.7194673384</v>
+      </c>
+      <c r="P16">
+        <v>4.4214874416</v>
+      </c>
+      <c r="Q16">
+        <v>4.6384874416</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.07149752651013136</v>
+      </c>
+      <c r="T16">
+        <v>0.7108157936985078</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.28</v>
+      </c>
+      <c r="W16">
+        <v>0.032184</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>34.73312839524157</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.06584552479305476</v>
+      </c>
+      <c r="C17">
+        <v>20.12918708188722</v>
+      </c>
+      <c r="D17">
+        <v>24.18468708188723</v>
+      </c>
+      <c r="E17">
+        <v>-18.1365</v>
+      </c>
+      <c r="F17">
+        <v>4.3635</v>
+      </c>
+      <c r="G17">
+        <v>0.308</v>
+      </c>
+      <c r="H17">
+        <v>6.59</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>6.54</v>
+      </c>
+      <c r="K17">
+        <v>0.217</v>
+      </c>
+      <c r="L17">
+        <v>6.323</v>
+      </c>
+      <c r="M17">
+        <v>0.19504845</v>
+      </c>
+      <c r="N17">
+        <v>6.127951550000001</v>
+      </c>
+      <c r="O17">
+        <v>1.715826434</v>
+      </c>
+      <c r="P17">
+        <v>4.412125116</v>
+      </c>
+      <c r="Q17">
+        <v>4.629125116</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.07178579387418207</v>
+      </c>
+      <c r="T17">
+        <v>0.7170824755256974</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.28</v>
+      </c>
+      <c r="W17">
+        <v>0.032184</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>32.41758650222548</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.06569741678739657</v>
+      </c>
+      <c r="C18">
+        <v>19.97145770564929</v>
+      </c>
+      <c r="D18">
+        <v>24.31785770564929</v>
+      </c>
+      <c r="E18">
+        <v>-17.8456</v>
+      </c>
+      <c r="F18">
+        <v>4.6544</v>
+      </c>
+      <c r="G18">
+        <v>0.308</v>
+      </c>
+      <c r="H18">
+        <v>6.59</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>6.54</v>
+      </c>
+      <c r="K18">
+        <v>0.217</v>
+      </c>
+      <c r="L18">
+        <v>6.323</v>
+      </c>
+      <c r="M18">
+        <v>0.20805168</v>
+      </c>
+      <c r="N18">
+        <v>6.114948320000001</v>
+      </c>
+      <c r="O18">
+        <v>1.7121855296</v>
+      </c>
+      <c r="P18">
+        <v>4.402762790400001</v>
+      </c>
+      <c r="Q18">
+        <v>4.6197627904</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.07208092474690068</v>
+      </c>
+      <c r="T18">
+        <v>0.7234983640630583</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.28</v>
+      </c>
+      <c r="W18">
+        <v>0.032184</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>30.39148734583638</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.06554930878173837</v>
+      </c>
+      <c r="C19">
+        <v>19.81520303185385</v>
+      </c>
+      <c r="D19">
+        <v>24.45250303185385</v>
+      </c>
+      <c r="E19">
+        <v>-17.5547</v>
+      </c>
+      <c r="F19">
+        <v>4.9453</v>
+      </c>
+      <c r="G19">
+        <v>0.308</v>
+      </c>
+      <c r="H19">
+        <v>6.59</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>6.54</v>
+      </c>
+      <c r="K19">
+        <v>0.217</v>
+      </c>
+      <c r="L19">
+        <v>6.323</v>
+      </c>
+      <c r="M19">
+        <v>0.22105491</v>
+      </c>
+      <c r="N19">
+        <v>6.10194509</v>
+      </c>
+      <c r="O19">
+        <v>1.7085446252</v>
+      </c>
+      <c r="P19">
+        <v>4.3934004648</v>
+      </c>
+      <c r="Q19">
+        <v>4.6104004648</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.07238316720691371</v>
+      </c>
+      <c r="T19">
+        <v>0.7300688523242109</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.28</v>
+      </c>
+      <c r="W19">
+        <v>0.032184</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>28.6037527960813</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.06540120077608019</v>
+      </c>
+      <c r="C20">
+        <v>19.66044769268641</v>
+      </c>
+      <c r="D20">
+        <v>24.58864769268641</v>
+      </c>
+      <c r="E20">
+        <v>-17.2638</v>
+      </c>
+      <c r="F20">
+        <v>5.2362</v>
+      </c>
+      <c r="G20">
+        <v>0.308</v>
+      </c>
+      <c r="H20">
+        <v>6.59</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>6.54</v>
+      </c>
+      <c r="K20">
+        <v>0.217</v>
+      </c>
+      <c r="L20">
+        <v>6.323</v>
+      </c>
+      <c r="M20">
+        <v>0.23405814</v>
+      </c>
+      <c r="N20">
+        <v>6.08894186</v>
+      </c>
+      <c r="O20">
+        <v>1.7049037208</v>
+      </c>
+      <c r="P20">
+        <v>4.3840381392</v>
+      </c>
+      <c r="Q20">
+        <v>4.6010381392</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.07269278143424412</v>
+      </c>
+      <c r="T20">
+        <v>0.7367995963966112</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.28</v>
+      </c>
+      <c r="W20">
+        <v>0.032184</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>27.01465541852123</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.06525309277042197</v>
+      </c>
+      <c r="C21">
+        <v>19.50721687198435</v>
+      </c>
+      <c r="D21">
+        <v>24.72631687198436</v>
+      </c>
+      <c r="E21">
+        <v>-16.9729</v>
+      </c>
+      <c r="F21">
+        <v>5.5271</v>
+      </c>
+      <c r="G21">
+        <v>0.308</v>
+      </c>
+      <c r="H21">
+        <v>6.59</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>6.54</v>
+      </c>
+      <c r="K21">
+        <v>0.217</v>
+      </c>
+      <c r="L21">
+        <v>6.323</v>
+      </c>
+      <c r="M21">
+        <v>0.24706137</v>
+      </c>
+      <c r="N21">
+        <v>6.07593863</v>
+      </c>
+      <c r="O21">
+        <v>1.7012628164</v>
+      </c>
+      <c r="P21">
+        <v>4.3746758136</v>
+      </c>
+      <c r="Q21">
+        <v>4.591675813599999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.07301004045731108</v>
+      </c>
+      <c r="T21">
+        <v>0.7436965316806757</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.28</v>
+      </c>
+      <c r="W21">
+        <v>0.032184</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>25.59283144912537</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.0651049847647638</v>
+      </c>
+      <c r="C22">
+        <v>19.35553632076682</v>
+      </c>
+      <c r="D22">
+        <v>24.86553632076683</v>
+      </c>
+      <c r="E22">
+        <v>-16.682</v>
+      </c>
+      <c r="F22">
+        <v>5.818000000000001</v>
+      </c>
+      <c r="G22">
+        <v>0.308</v>
+      </c>
+      <c r="H22">
+        <v>6.59</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>6.54</v>
+      </c>
+      <c r="K22">
+        <v>0.217</v>
+      </c>
+      <c r="L22">
+        <v>6.323</v>
+      </c>
+      <c r="M22">
+        <v>0.2600646</v>
+      </c>
+      <c r="N22">
+        <v>6.062935400000001</v>
+      </c>
+      <c r="O22">
+        <v>1.697621912</v>
+      </c>
+      <c r="P22">
+        <v>4.365313488</v>
+      </c>
+      <c r="Q22">
+        <v>4.582313488</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.07333523095595473</v>
+      </c>
+      <c r="T22">
+        <v>0.7507658903468418</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.28</v>
+      </c>
+      <c r="W22">
+        <v>0.032184</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>24.3131898766691</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.06495687675910558</v>
+      </c>
+      <c r="C23">
+        <v>19.20543237329282</v>
+      </c>
+      <c r="D23">
+        <v>25.00633237329281</v>
+      </c>
+      <c r="E23">
+        <v>-16.3911</v>
+      </c>
+      <c r="F23">
+        <v>6.108899999999999</v>
+      </c>
+      <c r="G23">
+        <v>0.308</v>
+      </c>
+      <c r="H23">
+        <v>6.59</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>6.54</v>
+      </c>
+      <c r="K23">
+        <v>0.217</v>
+      </c>
+      <c r="L23">
+        <v>6.323</v>
+      </c>
+      <c r="M23">
+        <v>0.27306783</v>
+      </c>
+      <c r="N23">
+        <v>6.04993217</v>
+      </c>
+      <c r="O23">
+        <v>1.6939810076</v>
+      </c>
+      <c r="P23">
+        <v>4.3559511624</v>
+      </c>
+      <c r="Q23">
+        <v>4.5729511624</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.07366865412545009</v>
+      </c>
+      <c r="T23">
+        <v>0.7580142201184805</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.28</v>
+      </c>
+      <c r="W23">
+        <v>0.032184</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>23.15541893016105</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.06480876875344739</v>
+      </c>
+      <c r="C24">
+        <v>19.05693196366725</v>
+      </c>
+      <c r="D24">
+        <v>25.14873196366725</v>
+      </c>
+      <c r="E24">
+        <v>-16.1002</v>
+      </c>
+      <c r="F24">
+        <v>6.3998</v>
+      </c>
+      <c r="G24">
+        <v>0.308</v>
+      </c>
+      <c r="H24">
+        <v>6.59</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>6.54</v>
+      </c>
+      <c r="K24">
+        <v>0.217</v>
+      </c>
+      <c r="L24">
+        <v>6.323</v>
+      </c>
+      <c r="M24">
+        <v>0.28607106</v>
+      </c>
+      <c r="N24">
+        <v>6.03692894</v>
+      </c>
+      <c r="O24">
+        <v>1.6903401032</v>
+      </c>
+      <c r="P24">
+        <v>4.3465888368</v>
+      </c>
+      <c r="Q24">
+        <v>4.563588836799999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.07401062660698382</v>
+      </c>
+      <c r="T24">
+        <v>0.7654484044996485</v>
+      </c>
+      <c r="U24">
+        <v>0.0447</v>
+      </c>
+      <c r="V24">
+        <v>0.28</v>
+      </c>
+      <c r="W24">
+        <v>0.032184</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>22.102899887881</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.0646606607477892</v>
+      </c>
+      <c r="C25">
+        <v>18.91006264301829</v>
+      </c>
+      <c r="D25">
+        <v>25.29276264301829</v>
+      </c>
+      <c r="E25">
+        <v>-15.8093</v>
+      </c>
+      <c r="F25">
+        <v>6.690700000000001</v>
+      </c>
+      <c r="G25">
+        <v>0.308</v>
+      </c>
+      <c r="H25">
+        <v>6.59</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>6.54</v>
+      </c>
+      <c r="K25">
+        <v>0.217</v>
+      </c>
+      <c r="L25">
+        <v>6.323</v>
+      </c>
+      <c r="M25">
+        <v>0.2990742900000001</v>
+      </c>
+      <c r="N25">
+        <v>6.02392571</v>
+      </c>
+      <c r="O25">
+        <v>1.6866991988</v>
+      </c>
+      <c r="P25">
+        <v>4.3372265112</v>
+      </c>
+      <c r="Q25">
+        <v>4.5542265112</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.07436148149063532</v>
+      </c>
+      <c r="T25">
+        <v>0.7730756845790284</v>
+      </c>
+      <c r="U25">
+        <v>0.0447</v>
+      </c>
+      <c r="V25">
+        <v>0.28</v>
+      </c>
+      <c r="W25">
+        <v>0.032184</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>21.14190424058183</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.064512552742131</v>
+      </c>
+      <c r="C26">
+        <v>18.76485259726798</v>
+      </c>
+      <c r="D26">
+        <v>25.43845259726798</v>
+      </c>
+      <c r="E26">
+        <v>-15.5184</v>
+      </c>
+      <c r="F26">
+        <v>6.981599999999999</v>
+      </c>
+      <c r="G26">
+        <v>0.308</v>
+      </c>
+      <c r="H26">
+        <v>6.59</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>6.54</v>
+      </c>
+      <c r="K26">
+        <v>0.217</v>
+      </c>
+      <c r="L26">
+        <v>6.323</v>
+      </c>
+      <c r="M26">
+        <v>0.31207752</v>
+      </c>
+      <c r="N26">
+        <v>6.010922480000001</v>
+      </c>
+      <c r="O26">
+        <v>1.6830582944</v>
+      </c>
+      <c r="P26">
+        <v>4.3278641856</v>
+      </c>
+      <c r="Q26">
+        <v>4.5448641856</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.07472156939754078</v>
+      </c>
+      <c r="T26">
+        <v>0.7809036825552343</v>
+      </c>
+      <c r="U26">
+        <v>0.0447</v>
+      </c>
+      <c r="V26">
+        <v>0.28</v>
+      </c>
+      <c r="W26">
+        <v>0.032184</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>20.26099156389092</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.06436444473647279</v>
+      </c>
+      <c r="C27">
+        <v>18.6213306655206</v>
+      </c>
+      <c r="D27">
+        <v>25.5858306655206</v>
+      </c>
+      <c r="E27">
+        <v>-15.2275</v>
+      </c>
+      <c r="F27">
+        <v>7.2725</v>
+      </c>
+      <c r="G27">
+        <v>0.308</v>
+      </c>
+      <c r="H27">
+        <v>6.59</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>6.54</v>
+      </c>
+      <c r="K27">
+        <v>0.217</v>
+      </c>
+      <c r="L27">
+        <v>6.323</v>
+      </c>
+      <c r="M27">
+        <v>0.32508075</v>
+      </c>
+      <c r="N27">
+        <v>5.997919250000001</v>
+      </c>
+      <c r="O27">
+        <v>1.67941739</v>
+      </c>
+      <c r="P27">
+        <v>4.31850186</v>
+      </c>
+      <c r="Q27">
+        <v>4.53550186</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.07509125964863039</v>
+      </c>
+      <c r="T27">
+        <v>0.7889404271441389</v>
+      </c>
+      <c r="U27">
+        <v>0.0447</v>
+      </c>
+      <c r="V27">
+        <v>0.28</v>
+      </c>
+      <c r="W27">
+        <v>0.032184</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>19.45055190133528</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.06421633673081459</v>
+      </c>
+      <c r="C28">
+        <v>18.47952635909411</v>
+      </c>
+      <c r="D28">
+        <v>25.73492635909411</v>
+      </c>
+      <c r="E28">
+        <v>-14.9366</v>
+      </c>
+      <c r="F28">
+        <v>7.563400000000001</v>
+      </c>
+      <c r="G28">
+        <v>0.308</v>
+      </c>
+      <c r="H28">
+        <v>6.59</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>6.54</v>
+      </c>
+      <c r="K28">
+        <v>0.217</v>
+      </c>
+      <c r="L28">
+        <v>6.323</v>
+      </c>
+      <c r="M28">
+        <v>0.3380839800000001</v>
+      </c>
+      <c r="N28">
+        <v>5.98491602</v>
+      </c>
+      <c r="O28">
+        <v>1.6757764856</v>
+      </c>
+      <c r="P28">
+        <v>4.3091395344</v>
+      </c>
+      <c r="Q28">
+        <v>4.526139534399999</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.07547094152812783</v>
+      </c>
+      <c r="T28">
+        <v>0.7971943810462573</v>
+      </c>
+      <c r="U28">
+        <v>0.0447</v>
+      </c>
+      <c r="V28">
+        <v>0.28</v>
+      </c>
+      <c r="W28">
+        <v>0.032184</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>18.70245375128392</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.0640682287251564</v>
+      </c>
+      <c r="C29">
+        <v>18.33946988122082</v>
+      </c>
+      <c r="D29">
+        <v>25.88576988122082</v>
+      </c>
+      <c r="E29">
+        <v>-14.6457</v>
+      </c>
+      <c r="F29">
+        <v>7.8543</v>
+      </c>
+      <c r="G29">
+        <v>0.308</v>
+      </c>
+      <c r="H29">
+        <v>6.59</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>6.54</v>
+      </c>
+      <c r="K29">
+        <v>0.217</v>
+      </c>
+      <c r="L29">
+        <v>6.323</v>
+      </c>
+      <c r="M29">
+        <v>0.35108721</v>
+      </c>
+      <c r="N29">
+        <v>5.97191279</v>
+      </c>
+      <c r="O29">
+        <v>1.6721355812</v>
+      </c>
+      <c r="P29">
+        <v>4.2997772088</v>
+      </c>
+      <c r="Q29">
+        <v>4.5167772088</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.07586102565089917</v>
+      </c>
+      <c r="T29">
+        <v>0.8056744706717212</v>
+      </c>
+      <c r="U29">
+        <v>0.0447</v>
+      </c>
+      <c r="V29">
+        <v>0.28</v>
+      </c>
+      <c r="W29">
+        <v>0.032184</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>18.00977027901415</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.06392012071949821</v>
+      </c>
+      <c r="C30">
+        <v>18.20119214744498</v>
+      </c>
+      <c r="D30">
+        <v>26.03839214744499</v>
+      </c>
+      <c r="E30">
+        <v>-14.3548</v>
+      </c>
+      <c r="F30">
+        <v>8.145200000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.308</v>
+      </c>
+      <c r="H30">
+        <v>6.59</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>6.54</v>
+      </c>
+      <c r="K30">
+        <v>0.217</v>
+      </c>
+      <c r="L30">
+        <v>6.323</v>
+      </c>
+      <c r="M30">
+        <v>0.3640904400000001</v>
+      </c>
+      <c r="N30">
+        <v>5.95890956</v>
+      </c>
+      <c r="O30">
+        <v>1.6684946768</v>
+      </c>
+      <c r="P30">
+        <v>4.2904148832</v>
+      </c>
+      <c r="Q30">
+        <v>4.5074148832</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.07626194544374751</v>
+      </c>
+      <c r="T30">
+        <v>0.814390118342337</v>
+      </c>
+      <c r="U30">
+        <v>0.0447</v>
+      </c>
+      <c r="V30">
+        <v>0.28</v>
+      </c>
+      <c r="W30">
+        <v>0.032184</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>17.36656419762079</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.06377201271384</v>
+      </c>
+      <c r="C31">
+        <v>18.06472480674629</v>
+      </c>
+      <c r="D31">
+        <v>26.19282480674629</v>
+      </c>
+      <c r="E31">
+        <v>-14.0639</v>
+      </c>
+      <c r="F31">
+        <v>8.4361</v>
+      </c>
+      <c r="G31">
+        <v>0.308</v>
+      </c>
+      <c r="H31">
+        <v>6.59</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>6.54</v>
+      </c>
+      <c r="K31">
+        <v>0.217</v>
+      </c>
+      <c r="L31">
+        <v>6.323</v>
+      </c>
+      <c r="M31">
+        <v>0.37709367</v>
+      </c>
+      <c r="N31">
+        <v>5.945906330000001</v>
+      </c>
+      <c r="O31">
+        <v>1.6648537724</v>
+      </c>
+      <c r="P31">
+        <v>4.281052557600001</v>
+      </c>
+      <c r="Q31">
+        <v>4.4980525576</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.07667415875188732</v>
+      </c>
+      <c r="T31">
+        <v>0.8233512772149419</v>
+      </c>
+      <c r="U31">
+        <v>0.0447</v>
+      </c>
+      <c r="V31">
+        <v>0.28</v>
+      </c>
+      <c r="W31">
+        <v>0.032184</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>16.76771715632352</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.0636239047081818</v>
+      </c>
+      <c r="C32">
+        <v>17.93010026341944</v>
+      </c>
+      <c r="D32">
+        <v>26.34910026341944</v>
+      </c>
+      <c r="E32">
+        <v>-13.773</v>
+      </c>
+      <c r="F32">
+        <v>8.727</v>
+      </c>
+      <c r="G32">
+        <v>0.308</v>
+      </c>
+      <c r="H32">
+        <v>6.59</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>6.54</v>
+      </c>
+      <c r="K32">
+        <v>0.217</v>
+      </c>
+      <c r="L32">
+        <v>6.323</v>
+      </c>
+      <c r="M32">
+        <v>0.3900969</v>
+      </c>
+      <c r="N32">
+        <v>5.932903100000001</v>
+      </c>
+      <c r="O32">
+        <v>1.661212868</v>
+      </c>
+      <c r="P32">
+        <v>4.271690232</v>
+      </c>
+      <c r="Q32">
+        <v>4.488690232</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.07709814958311687</v>
+      </c>
+      <c r="T32">
+        <v>0.8325684691981928</v>
+      </c>
+      <c r="U32">
+        <v>0.0447</v>
+      </c>
+      <c r="V32">
+        <v>0.28</v>
+      </c>
+      <c r="W32">
+        <v>0.032184</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>16.20879325111274</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.0634757967025236</v>
+      </c>
+      <c r="C33">
+        <v>17.79735169974182</v>
+      </c>
+      <c r="D33">
+        <v>26.50725169974182</v>
+      </c>
+      <c r="E33">
+        <v>-13.4821</v>
+      </c>
+      <c r="F33">
+        <v>9.017899999999999</v>
+      </c>
+      <c r="G33">
+        <v>0.308</v>
+      </c>
+      <c r="H33">
+        <v>6.59</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>6.54</v>
+      </c>
+      <c r="K33">
+        <v>0.217</v>
+      </c>
+      <c r="L33">
+        <v>6.323</v>
+      </c>
+      <c r="M33">
+        <v>0.40310013</v>
+      </c>
+      <c r="N33">
+        <v>5.91989987</v>
+      </c>
+      <c r="O33">
+        <v>1.6575719636</v>
+      </c>
+      <c r="P33">
+        <v>4.262327906399999</v>
+      </c>
+      <c r="Q33">
+        <v>4.479327906399999</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.0775344300036574</v>
+      </c>
+      <c r="T33">
+        <v>0.8420528261664653</v>
+      </c>
+      <c r="U33">
+        <v>0.0447</v>
+      </c>
+      <c r="V33">
+        <v>0.28</v>
+      </c>
+      <c r="W33">
+        <v>0.032184</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>15.68592895268974</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.06332768869686541</v>
+      </c>
+      <c r="C34">
+        <v>17.6665130994623</v>
+      </c>
+      <c r="D34">
+        <v>26.6673130994623</v>
+      </c>
+      <c r="E34">
+        <v>-13.1912</v>
+      </c>
+      <c r="F34">
+        <v>9.3088</v>
+      </c>
+      <c r="G34">
+        <v>0.308</v>
+      </c>
+      <c r="H34">
+        <v>6.59</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>6.54</v>
+      </c>
+      <c r="K34">
+        <v>0.217</v>
+      </c>
+      <c r="L34">
+        <v>6.323</v>
+      </c>
+      <c r="M34">
+        <v>0.41610336</v>
+      </c>
+      <c r="N34">
+        <v>5.90689664</v>
+      </c>
+      <c r="O34">
+        <v>1.6539310592</v>
+      </c>
+      <c r="P34">
+        <v>4.2529655808</v>
+      </c>
+      <c r="Q34">
+        <v>4.469965580799999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.07798354220127265</v>
+      </c>
+      <c r="T34">
+        <v>0.8518161348102753</v>
+      </c>
+      <c r="U34">
+        <v>0.0447</v>
+      </c>
+      <c r="V34">
+        <v>0.28</v>
+      </c>
+      <c r="W34">
+        <v>0.032184</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>15.19574367291819</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.0631795806912072</v>
+      </c>
+      <c r="C35">
+        <v>17.53761927214634</v>
+      </c>
+      <c r="D35">
+        <v>26.82931927214634</v>
+      </c>
+      <c r="E35">
+        <v>-12.9003</v>
+      </c>
+      <c r="F35">
+        <v>9.5997</v>
+      </c>
+      <c r="G35">
+        <v>0.308</v>
+      </c>
+      <c r="H35">
+        <v>6.59</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>6.54</v>
+      </c>
+      <c r="K35">
+        <v>0.217</v>
+      </c>
+      <c r="L35">
+        <v>6.323</v>
+      </c>
+      <c r="M35">
+        <v>0.4291065900000001</v>
+      </c>
+      <c r="N35">
+        <v>5.89389341</v>
+      </c>
+      <c r="O35">
+        <v>1.6502901548</v>
+      </c>
+      <c r="P35">
+        <v>4.2436032552</v>
+      </c>
+      <c r="Q35">
+        <v>4.4606032552</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.07844606073314508</v>
+      </c>
+      <c r="T35">
+        <v>0.8618708855031542</v>
+      </c>
+      <c r="U35">
+        <v>0.0447</v>
+      </c>
+      <c r="V35">
+        <v>0.28</v>
+      </c>
+      <c r="W35">
+        <v>0.032184</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>14.73526659192067</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.06303147268554901</v>
+      </c>
+      <c r="C36">
+        <v>17.41070587841374</v>
+      </c>
+      <c r="D36">
+        <v>26.99330587841375</v>
+      </c>
+      <c r="E36">
+        <v>-12.6094</v>
+      </c>
+      <c r="F36">
+        <v>9.890600000000001</v>
+      </c>
+      <c r="G36">
+        <v>0.308</v>
+      </c>
+      <c r="H36">
+        <v>6.59</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>6.54</v>
+      </c>
+      <c r="K36">
+        <v>0.217</v>
+      </c>
+      <c r="L36">
+        <v>6.323</v>
+      </c>
+      <c r="M36">
+        <v>0.4421098200000001</v>
+      </c>
+      <c r="N36">
+        <v>5.880890180000001</v>
+      </c>
+      <c r="O36">
+        <v>1.6466492504</v>
+      </c>
+      <c r="P36">
+        <v>4.2342409296</v>
+      </c>
+      <c r="Q36">
+        <v>4.4512409296</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.07892259497810457</v>
+      </c>
+      <c r="T36">
+        <v>0.8722303256109689</v>
+      </c>
+      <c r="U36">
+        <v>0.0447</v>
+      </c>
+      <c r="V36">
+        <v>0.28</v>
+      </c>
+      <c r="W36">
+        <v>0.032184</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>14.30187639804065</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.06288336467989082</v>
+      </c>
+      <c r="C37">
+        <v>17.28580945610783</v>
+      </c>
+      <c r="D37">
+        <v>27.15930945610784</v>
+      </c>
+      <c r="E37">
+        <v>-12.3185</v>
+      </c>
+      <c r="F37">
+        <v>10.1815</v>
+      </c>
+      <c r="G37">
+        <v>0.308</v>
+      </c>
+      <c r="H37">
+        <v>6.59</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>6.54</v>
+      </c>
+      <c r="K37">
+        <v>0.217</v>
+      </c>
+      <c r="L37">
+        <v>6.323</v>
+      </c>
+      <c r="M37">
+        <v>0.4551130500000001</v>
+      </c>
+      <c r="N37">
+        <v>5.86788695</v>
+      </c>
+      <c r="O37">
+        <v>1.643008346</v>
+      </c>
+      <c r="P37">
+        <v>4.224878604</v>
+      </c>
+      <c r="Q37">
+        <v>4.441878603999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.07941379181521666</v>
+      </c>
+      <c r="T37">
+        <v>0.882908517722101</v>
+      </c>
+      <c r="U37">
+        <v>0.0447</v>
+      </c>
+      <c r="V37">
+        <v>0.28</v>
+      </c>
+      <c r="W37">
+        <v>0.032184</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>13.89325135809663</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.06273525667423262</v>
+      </c>
+      <c r="C38">
+        <v>17.16296744743611</v>
+      </c>
+      <c r="D38">
+        <v>27.32736744743611</v>
+      </c>
+      <c r="E38">
+        <v>-12.0276</v>
+      </c>
+      <c r="F38">
+        <v>10.4724</v>
+      </c>
+      <c r="G38">
+        <v>0.308</v>
+      </c>
+      <c r="H38">
+        <v>6.59</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>6.54</v>
+      </c>
+      <c r="K38">
+        <v>0.217</v>
+      </c>
+      <c r="L38">
+        <v>6.323</v>
+      </c>
+      <c r="M38">
+        <v>0.4681162800000001</v>
+      </c>
+      <c r="N38">
+        <v>5.85488372</v>
+      </c>
+      <c r="O38">
+        <v>1.6393674416</v>
+      </c>
+      <c r="P38">
+        <v>4.2155162784</v>
+      </c>
+      <c r="Q38">
+        <v>4.4325162784</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.07992033855348847</v>
+      </c>
+      <c r="T38">
+        <v>0.8939204033367059</v>
+      </c>
+      <c r="U38">
+        <v>0.0447</v>
+      </c>
+      <c r="V38">
+        <v>0.28</v>
+      </c>
+      <c r="W38">
+        <v>0.032184</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>13.50732770926061</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.06258714866857443</v>
+      </c>
+      <c r="C39">
+        <v>17.04221822712478</v>
+      </c>
+      <c r="D39">
+        <v>27.49751822712478</v>
+      </c>
+      <c r="E39">
+        <v>-11.7367</v>
+      </c>
+      <c r="F39">
+        <v>10.7633</v>
+      </c>
+      <c r="G39">
+        <v>0.308</v>
+      </c>
+      <c r="H39">
+        <v>6.59</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>6.54</v>
+      </c>
+      <c r="K39">
+        <v>0.217</v>
+      </c>
+      <c r="L39">
+        <v>6.323</v>
+      </c>
+      <c r="M39">
+        <v>0.48111951</v>
+      </c>
+      <c r="N39">
+        <v>5.84188049</v>
+      </c>
+      <c r="O39">
+        <v>1.6357265372</v>
+      </c>
+      <c r="P39">
+        <v>4.2061539528</v>
+      </c>
+      <c r="Q39">
+        <v>4.4231539528</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.08044296614059432</v>
+      </c>
+      <c r="T39">
+        <v>0.9052818726216156</v>
+      </c>
+      <c r="U39">
+        <v>0.0447</v>
+      </c>
+      <c r="V39">
+        <v>0.28</v>
+      </c>
+      <c r="W39">
+        <v>0.032184</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>13.14226479819952</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.06274000066291623</v>
+      </c>
+      <c r="C40">
+        <v>16.57575221275216</v>
+      </c>
+      <c r="D40">
+        <v>27.32195221275217</v>
+      </c>
+      <c r="E40">
+        <v>-11.4458</v>
+      </c>
+      <c r="F40">
+        <v>11.0542</v>
+      </c>
+      <c r="G40">
+        <v>0.308</v>
+      </c>
+      <c r="H40">
+        <v>6.59</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>6.54</v>
+      </c>
+      <c r="K40">
+        <v>0.217</v>
+      </c>
+      <c r="L40">
+        <v>6.323</v>
+      </c>
+      <c r="M40">
+        <v>0.50628236</v>
+      </c>
+      <c r="N40">
+        <v>5.81671764</v>
+      </c>
+      <c r="O40">
+        <v>1.6286809392</v>
+      </c>
+      <c r="P40">
+        <v>4.1880367008</v>
+      </c>
+      <c r="Q40">
+        <v>4.405036700799999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.08098245268212295</v>
+      </c>
+      <c r="T40">
+        <v>0.9170098409157161</v>
+      </c>
+      <c r="U40">
+        <v>0.0458</v>
+      </c>
+      <c r="V40">
+        <v>0.28</v>
+      </c>
+      <c r="W40">
+        <v>0.032976</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>12.48907822899459</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.06259981265725803</v>
+      </c>
+      <c r="C41">
+        <v>16.44578667247053</v>
+      </c>
+      <c r="D41">
+        <v>27.48288667247053</v>
+      </c>
+      <c r="E41">
+        <v>-11.1549</v>
+      </c>
+      <c r="F41">
+        <v>11.3451</v>
+      </c>
+      <c r="G41">
+        <v>0.308</v>
+      </c>
+      <c r="H41">
+        <v>6.59</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>6.54</v>
+      </c>
+      <c r="K41">
+        <v>0.217</v>
+      </c>
+      <c r="L41">
+        <v>6.323</v>
+      </c>
+      <c r="M41">
+        <v>0.51960558</v>
+      </c>
+      <c r="N41">
+        <v>5.80339442</v>
+      </c>
+      <c r="O41">
+        <v>1.6249504376</v>
+      </c>
+      <c r="P41">
+        <v>4.1784439824</v>
+      </c>
+      <c r="Q41">
+        <v>4.3954439824</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.08153962730698038</v>
+      </c>
+      <c r="T41">
+        <v>0.9291223327604429</v>
+      </c>
+      <c r="U41">
+        <v>0.0458</v>
+      </c>
+      <c r="V41">
+        <v>0.28</v>
+      </c>
+      <c r="W41">
+        <v>0.032976</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>12.16884545389216</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.06245962465159982</v>
+      </c>
+      <c r="C42">
+        <v>16.31772826987871</v>
+      </c>
+      <c r="D42">
+        <v>27.64572826987871</v>
+      </c>
+      <c r="E42">
+        <v>-10.864</v>
+      </c>
+      <c r="F42">
+        <v>11.636</v>
+      </c>
+      <c r="G42">
+        <v>0.308</v>
+      </c>
+      <c r="H42">
+        <v>6.59</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>6.54</v>
+      </c>
+      <c r="K42">
+        <v>0.217</v>
+      </c>
+      <c r="L42">
+        <v>6.323</v>
+      </c>
+      <c r="M42">
+        <v>0.5329288000000001</v>
+      </c>
+      <c r="N42">
+        <v>5.7900712</v>
+      </c>
+      <c r="O42">
+        <v>1.621219936</v>
+      </c>
+      <c r="P42">
+        <v>4.168851264</v>
+      </c>
+      <c r="Q42">
+        <v>4.385851263999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.08211537441933305</v>
+      </c>
+      <c r="T42">
+        <v>0.9416385743333271</v>
+      </c>
+      <c r="U42">
+        <v>0.0458</v>
+      </c>
+      <c r="V42">
+        <v>0.28</v>
+      </c>
+      <c r="W42">
+        <v>0.032976</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>11.86462431754486</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.06231943664594163</v>
+      </c>
+      <c r="C43">
+        <v>16.1916111075574</v>
+      </c>
+      <c r="D43">
+        <v>27.8105111075574</v>
+      </c>
+      <c r="E43">
+        <v>-10.5731</v>
+      </c>
+      <c r="F43">
+        <v>11.9269</v>
+      </c>
+      <c r="G43">
+        <v>0.308</v>
+      </c>
+      <c r="H43">
+        <v>6.59</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>6.54</v>
+      </c>
+      <c r="K43">
+        <v>0.217</v>
+      </c>
+      <c r="L43">
+        <v>6.323</v>
+      </c>
+      <c r="M43">
+        <v>0.5462520200000001</v>
+      </c>
+      <c r="N43">
+        <v>5.776747980000001</v>
+      </c>
+      <c r="O43">
+        <v>1.6174894344</v>
+      </c>
+      <c r="P43">
+        <v>4.1592585456</v>
+      </c>
+      <c r="Q43">
+        <v>4.3762585456</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.08271063838295192</v>
+      </c>
+      <c r="T43">
+        <v>0.9545790952815635</v>
+      </c>
+      <c r="U43">
+        <v>0.0458</v>
+      </c>
+      <c r="V43">
+        <v>0.28</v>
+      </c>
+      <c r="W43">
+        <v>0.032976</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>11.57524323662913</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.06217924864028344</v>
+      </c>
+      <c r="C44">
+        <v>16.06747010603889</v>
+      </c>
+      <c r="D44">
+        <v>27.97727010603889</v>
+      </c>
+      <c r="E44">
+        <v>-10.2822</v>
+      </c>
+      <c r="F44">
+        <v>12.2178</v>
+      </c>
+      <c r="G44">
+        <v>0.308</v>
+      </c>
+      <c r="H44">
+        <v>6.59</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>6.54</v>
+      </c>
+      <c r="K44">
+        <v>0.217</v>
+      </c>
+      <c r="L44">
+        <v>6.323</v>
+      </c>
+      <c r="M44">
+        <v>0.5595752399999999</v>
+      </c>
+      <c r="N44">
+        <v>5.76342476</v>
+      </c>
+      <c r="O44">
+        <v>1.6137589328</v>
+      </c>
+      <c r="P44">
+        <v>4.1496658272</v>
+      </c>
+      <c r="Q44">
+        <v>4.366665827199999</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.08332642869014385</v>
+      </c>
+      <c r="T44">
+        <v>0.9679658410900838</v>
+      </c>
+      <c r="U44">
+        <v>0.0458</v>
+      </c>
+      <c r="V44">
+        <v>0.28</v>
+      </c>
+      <c r="W44">
+        <v>0.032976</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>11.29964220718558</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.06203906063462524</v>
+      </c>
+      <c r="C45">
+        <v>15.9453410284781</v>
+      </c>
+      <c r="D45">
+        <v>28.14604102847809</v>
+      </c>
+      <c r="E45">
+        <v>-9.991300000000001</v>
+      </c>
+      <c r="F45">
+        <v>12.5087</v>
+      </c>
+      <c r="G45">
+        <v>0.308</v>
+      </c>
+      <c r="H45">
+        <v>6.59</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>6.54</v>
+      </c>
+      <c r="K45">
+        <v>0.217</v>
+      </c>
+      <c r="L45">
+        <v>6.323</v>
+      </c>
+      <c r="M45">
+        <v>0.57289846</v>
+      </c>
+      <c r="N45">
+        <v>5.75010154</v>
+      </c>
+      <c r="O45">
+        <v>1.6100284312</v>
+      </c>
+      <c r="P45">
+        <v>4.1400731088</v>
+      </c>
+      <c r="Q45">
+        <v>4.3570731088</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.08396382567478111</v>
+      </c>
+      <c r="T45">
+        <v>0.9818222972778503</v>
+      </c>
+      <c r="U45">
+        <v>0.0458</v>
+      </c>
+      <c r="V45">
+        <v>0.28</v>
+      </c>
+      <c r="W45">
+        <v>0.032976</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>11.03685983027429</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.06189887262896705</v>
+      </c>
+      <c r="C46">
+        <v>15.82526050622213</v>
+      </c>
+      <c r="D46">
+        <v>28.31686050622213</v>
+      </c>
+      <c r="E46">
+        <v>-9.7004</v>
+      </c>
+      <c r="F46">
+        <v>12.7996</v>
+      </c>
+      <c r="G46">
+        <v>0.308</v>
+      </c>
+      <c r="H46">
+        <v>6.59</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>6.54</v>
+      </c>
+      <c r="K46">
+        <v>0.217</v>
+      </c>
+      <c r="L46">
+        <v>6.323</v>
+      </c>
+      <c r="M46">
+        <v>0.58622168</v>
+      </c>
+      <c r="N46">
+        <v>5.736778320000001</v>
+      </c>
+      <c r="O46">
+        <v>1.6062979296</v>
+      </c>
+      <c r="P46">
+        <v>4.130480390400001</v>
+      </c>
+      <c r="Q46">
+        <v>4.3474803904</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.08462398683744114</v>
+      </c>
+      <c r="T46">
+        <v>0.9961736269008944</v>
+      </c>
+      <c r="U46">
+        <v>0.0458</v>
+      </c>
+      <c r="V46">
+        <v>0.28</v>
+      </c>
+      <c r="W46">
+        <v>0.032976</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>10.78602210685896</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.06175868462330884</v>
+      </c>
+      <c r="C47">
+        <v>15.70726606531668</v>
+      </c>
+      <c r="D47">
+        <v>28.48976606531668</v>
+      </c>
+      <c r="E47">
+        <v>-9.4095</v>
+      </c>
+      <c r="F47">
+        <v>13.0905</v>
+      </c>
+      <c r="G47">
+        <v>0.308</v>
+      </c>
+      <c r="H47">
+        <v>6.59</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>6.54</v>
+      </c>
+      <c r="K47">
+        <v>0.217</v>
+      </c>
+      <c r="L47">
+        <v>6.323</v>
+      </c>
+      <c r="M47">
+        <v>0.5995449</v>
+      </c>
+      <c r="N47">
+        <v>5.723455100000001</v>
+      </c>
+      <c r="O47">
+        <v>1.602567428</v>
+      </c>
+      <c r="P47">
+        <v>4.120887672</v>
+      </c>
+      <c r="Q47">
+        <v>4.337887672</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.08530815386056152</v>
+      </c>
+      <c r="T47">
+        <v>1.011046823055685</v>
+      </c>
+      <c r="U47">
+        <v>0.0458</v>
+      </c>
+      <c r="V47">
+        <v>0.28</v>
+      </c>
+      <c r="W47">
+        <v>0.032976</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>10.54633272670654</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.06161849661765064</v>
+      </c>
+      <c r="C48">
+        <v>15.5913961539894</v>
+      </c>
+      <c r="D48">
+        <v>28.6647961539894</v>
+      </c>
+      <c r="E48">
+        <v>-9.118599999999999</v>
+      </c>
+      <c r="F48">
+        <v>13.3814</v>
+      </c>
+      <c r="G48">
+        <v>0.308</v>
+      </c>
+      <c r="H48">
+        <v>6.59</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>6.54</v>
+      </c>
+      <c r="K48">
+        <v>0.217</v>
+      </c>
+      <c r="L48">
+        <v>6.323</v>
+      </c>
+      <c r="M48">
+        <v>0.61286812</v>
+      </c>
+      <c r="N48">
+        <v>5.71013188</v>
+      </c>
+      <c r="O48">
+        <v>1.5988369264</v>
+      </c>
+      <c r="P48">
+        <v>4.1112949536</v>
+      </c>
+      <c r="Q48">
+        <v>4.328294953599999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.08601766040305674</v>
+      </c>
+      <c r="T48">
+        <v>1.02647087832732</v>
+      </c>
+      <c r="U48">
+        <v>0.0458</v>
+      </c>
+      <c r="V48">
+        <v>0.28</v>
+      </c>
+      <c r="W48">
+        <v>0.032976</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>10.31706462395205</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.06147830861199245</v>
+      </c>
+      <c r="C49">
+        <v>15.47769017115264</v>
+      </c>
+      <c r="D49">
+        <v>28.84199017115264</v>
+      </c>
+      <c r="E49">
+        <v>-8.8277</v>
+      </c>
+      <c r="F49">
+        <v>13.6723</v>
+      </c>
+      <c r="G49">
+        <v>0.308</v>
+      </c>
+      <c r="H49">
+        <v>6.59</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>6.54</v>
+      </c>
+      <c r="K49">
+        <v>0.217</v>
+      </c>
+      <c r="L49">
+        <v>6.323</v>
+      </c>
+      <c r="M49">
+        <v>0.62619134</v>
+      </c>
+      <c r="N49">
+        <v>5.69680866</v>
+      </c>
+      <c r="O49">
+        <v>1.5951064248</v>
+      </c>
+      <c r="P49">
+        <v>4.1017022352</v>
+      </c>
+      <c r="Q49">
+        <v>4.3187022352</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.08675394077734423</v>
+      </c>
+      <c r="T49">
+        <v>1.042476973420527</v>
+      </c>
+      <c r="U49">
+        <v>0.0458</v>
+      </c>
+      <c r="V49">
+        <v>0.28</v>
+      </c>
+      <c r="W49">
+        <v>0.032976</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>10.09755261067648</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.06209844060633425</v>
+      </c>
+      <c r="C50">
+        <v>14.41910613650695</v>
+      </c>
+      <c r="D50">
+        <v>28.07430613650694</v>
+      </c>
+      <c r="E50">
+        <v>-8.536800000000001</v>
+      </c>
+      <c r="F50">
+        <v>13.9632</v>
+      </c>
+      <c r="G50">
+        <v>0.308</v>
+      </c>
+      <c r="H50">
+        <v>6.59</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>6.54</v>
+      </c>
+      <c r="K50">
+        <v>0.217</v>
+      </c>
+      <c r="L50">
+        <v>6.323</v>
+      </c>
+      <c r="M50">
+        <v>0.6702336</v>
+      </c>
+      <c r="N50">
+        <v>5.652766400000001</v>
+      </c>
+      <c r="O50">
+        <v>1.582774592</v>
+      </c>
+      <c r="P50">
+        <v>4.069991808</v>
+      </c>
+      <c r="Q50">
+        <v>4.286991808</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.08751853962756587</v>
+      </c>
+      <c r="T50">
+        <v>1.05909868755578</v>
+      </c>
+      <c r="U50">
+        <v>0.048</v>
+      </c>
+      <c r="V50">
+        <v>0.28</v>
+      </c>
+      <c r="W50">
+        <v>0.03456</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>9.434024196936711</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.06197409260067605</v>
+      </c>
+      <c r="C51">
+        <v>14.27884780513524</v>
+      </c>
+      <c r="D51">
+        <v>28.22494780513524</v>
+      </c>
+      <c r="E51">
+        <v>-8.245900000000001</v>
+      </c>
+      <c r="F51">
+        <v>14.2541</v>
+      </c>
+      <c r="G51">
+        <v>0.308</v>
+      </c>
+      <c r="H51">
+        <v>6.59</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>6.54</v>
+      </c>
+      <c r="K51">
+        <v>0.217</v>
+      </c>
+      <c r="L51">
+        <v>6.323</v>
+      </c>
+      <c r="M51">
+        <v>0.6841967999999999</v>
+      </c>
+      <c r="N51">
+        <v>5.638803200000001</v>
+      </c>
+      <c r="O51">
+        <v>1.578864896</v>
+      </c>
+      <c r="P51">
+        <v>4.059938304</v>
+      </c>
+      <c r="Q51">
+        <v>4.276938304</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.08831312274642363</v>
+      </c>
+      <c r="T51">
+        <v>1.076372233617905</v>
+      </c>
+      <c r="U51">
+        <v>0.048</v>
+      </c>
+      <c r="V51">
+        <v>0.28</v>
+      </c>
+      <c r="W51">
+        <v>0.03456</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>9.241493090876778</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.06184974459501785</v>
+      </c>
+      <c r="C52">
+        <v>14.14021482722337</v>
+      </c>
+      <c r="D52">
+        <v>28.37721482722337</v>
+      </c>
+      <c r="E52">
+        <v>-7.955</v>
+      </c>
+      <c r="F52">
+        <v>14.545</v>
+      </c>
+      <c r="G52">
+        <v>0.308</v>
+      </c>
+      <c r="H52">
+        <v>6.59</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>6.54</v>
+      </c>
+      <c r="K52">
+        <v>0.217</v>
+      </c>
+      <c r="L52">
+        <v>6.323</v>
+      </c>
+      <c r="M52">
+        <v>0.69816</v>
+      </c>
+      <c r="N52">
+        <v>5.624840000000001</v>
+      </c>
+      <c r="O52">
+        <v>1.5749552</v>
+      </c>
+      <c r="P52">
+        <v>4.0498848</v>
+      </c>
+      <c r="Q52">
+        <v>4.2668848</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.0891394891900357</v>
+      </c>
+      <c r="T52">
+        <v>1.094336721522515</v>
+      </c>
+      <c r="U52">
+        <v>0.048</v>
+      </c>
+      <c r="V52">
+        <v>0.28</v>
+      </c>
+      <c r="W52">
+        <v>0.03456</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>9.056663229059243</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.06172539658935966</v>
+      </c>
+      <c r="C53">
+        <v>14.00323365066204</v>
+      </c>
+      <c r="D53">
+        <v>28.53113365066205</v>
+      </c>
+      <c r="E53">
+        <v>-7.664099999999999</v>
+      </c>
+      <c r="F53">
+        <v>14.8359</v>
+      </c>
+      <c r="G53">
+        <v>0.308</v>
+      </c>
+      <c r="H53">
+        <v>6.59</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>6.54</v>
+      </c>
+      <c r="K53">
+        <v>0.217</v>
+      </c>
+      <c r="L53">
+        <v>6.323</v>
+      </c>
+      <c r="M53">
+        <v>0.7121232000000001</v>
+      </c>
+      <c r="N53">
+        <v>5.610876800000001</v>
+      </c>
+      <c r="O53">
+        <v>1.571045504</v>
+      </c>
+      <c r="P53">
+        <v>4.039831296</v>
+      </c>
+      <c r="Q53">
+        <v>4.256831296</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.08999958487624421</v>
+      </c>
+      <c r="T53">
+        <v>1.113034453831396</v>
+      </c>
+      <c r="U53">
+        <v>0.048</v>
+      </c>
+      <c r="V53">
+        <v>0.28</v>
+      </c>
+      <c r="W53">
+        <v>0.03456</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>8.879081597116905</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
         <v>0.52</v>
       </c>
-      <c r="N3">
-        <v>0.06924101198402131</v>
-      </c>
-      <c r="O3">
-        <v>-0.04369747899159664</v>
-      </c>
-      <c r="P3">
-        <v>0.52</v>
-      </c>
-      <c r="Q3">
-        <v>0.06924101198402131</v>
-      </c>
-      <c r="R3">
-        <v>-0.04369747899159664</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="V3">
-        <v>0.10745672436751</v>
-      </c>
-      <c r="W3">
-        <v>-0.4075342465753425</v>
-      </c>
-      <c r="X3">
-        <v>0.1634220026903123</v>
-      </c>
-      <c r="Y3">
-        <v>-0.5709562492656548</v>
-      </c>
-      <c r="Z3">
-        <v>0.463907509958224</v>
-      </c>
-      <c r="AA3">
-        <v>-0.02098513552900029</v>
-      </c>
-      <c r="AB3">
-        <v>0.06947285109532214</v>
-      </c>
-      <c r="AC3">
-        <v>-0.09045798662432243</v>
-      </c>
-      <c r="AD3">
-        <v>26</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>26</v>
-      </c>
-      <c r="AG3">
-        <v>25.193</v>
-      </c>
-      <c r="AH3">
-        <v>0.7758877946881528</v>
-      </c>
-      <c r="AI3">
-        <v>0.6582278481012658</v>
-      </c>
-      <c r="AJ3">
-        <v>0.770357459560285</v>
-      </c>
-      <c r="AK3">
-        <v>0.6510996821130438</v>
-      </c>
-      <c r="AL3">
-        <v>1.53</v>
-      </c>
-      <c r="AM3">
-        <v>1.504</v>
-      </c>
-      <c r="AN3">
-        <v>7.807807807807808</v>
-      </c>
-      <c r="AO3">
-        <v>-0.5647058823529412</v>
-      </c>
-      <c r="AP3">
-        <v>7.565465465465466</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.5744680851063829</v>
+      <c r="B54">
+        <v>0.06160104858370145</v>
+      </c>
+      <c r="C54">
+        <v>13.86793130028785</v>
+      </c>
+      <c r="D54">
+        <v>28.68673130028785</v>
+      </c>
+      <c r="E54">
+        <v>-7.373199999999999</v>
+      </c>
+      <c r="F54">
+        <v>15.1268</v>
+      </c>
+      <c r="G54">
+        <v>0.308</v>
+      </c>
+      <c r="H54">
+        <v>6.59</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>6.54</v>
+      </c>
+      <c r="K54">
+        <v>0.217</v>
+      </c>
+      <c r="L54">
+        <v>6.323</v>
+      </c>
+      <c r="M54">
+        <v>0.7260864</v>
+      </c>
+      <c r="N54">
+        <v>5.596913600000001</v>
+      </c>
+      <c r="O54">
+        <v>1.567135808</v>
+      </c>
+      <c r="P54">
+        <v>4.029777792</v>
+      </c>
+      <c r="Q54">
+        <v>4.246777792</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.09089551788271136</v>
+      </c>
+      <c r="T54">
+        <v>1.132511258319812</v>
+      </c>
+      <c r="U54">
+        <v>0.048</v>
+      </c>
+      <c r="V54">
+        <v>0.28</v>
+      </c>
+      <c r="W54">
+        <v>0.03456</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>8.708330027941578</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.06147670057804326</v>
+      </c>
+      <c r="C55">
+        <v>13.73433539370155</v>
+      </c>
+      <c r="D55">
+        <v>28.84403539370155</v>
+      </c>
+      <c r="E55">
+        <v>-7.0823</v>
+      </c>
+      <c r="F55">
+        <v>15.4177</v>
+      </c>
+      <c r="G55">
+        <v>0.308</v>
+      </c>
+      <c r="H55">
+        <v>6.59</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>6.54</v>
+      </c>
+      <c r="K55">
+        <v>0.217</v>
+      </c>
+      <c r="L55">
+        <v>6.323</v>
+      </c>
+      <c r="M55">
+        <v>0.7400496</v>
+      </c>
+      <c r="N55">
+        <v>5.582950400000001</v>
+      </c>
+      <c r="O55">
+        <v>1.563226112</v>
+      </c>
+      <c r="P55">
+        <v>4.019724288</v>
+      </c>
+      <c r="Q55">
+        <v>4.236724288</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.09182957569796439</v>
+      </c>
+      <c r="T55">
+        <v>1.152816862999226</v>
+      </c>
+      <c r="U55">
+        <v>0.048</v>
+      </c>
+      <c r="V55">
+        <v>0.28</v>
+      </c>
+      <c r="W55">
+        <v>0.03456</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>8.544021914206834</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.06135235257238506</v>
+      </c>
+      <c r="C56">
+        <v>13.60247415761007</v>
+      </c>
+      <c r="D56">
+        <v>29.00307415761007</v>
+      </c>
+      <c r="E56">
+        <v>-6.791399999999999</v>
+      </c>
+      <c r="F56">
+        <v>15.7086</v>
+      </c>
+      <c r="G56">
+        <v>0.308</v>
+      </c>
+      <c r="H56">
+        <v>6.59</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>6.54</v>
+      </c>
+      <c r="K56">
+        <v>0.217</v>
+      </c>
+      <c r="L56">
+        <v>6.323</v>
+      </c>
+      <c r="M56">
+        <v>0.7540128</v>
+      </c>
+      <c r="N56">
+        <v>5.5689872</v>
+      </c>
+      <c r="O56">
+        <v>1.559316416</v>
+      </c>
+      <c r="P56">
+        <v>4.009670784</v>
+      </c>
+      <c r="Q56">
+        <v>4.226670784</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.09280424472257623</v>
+      </c>
+      <c r="T56">
+        <v>1.174005320056005</v>
+      </c>
+      <c r="U56">
+        <v>0.048</v>
+      </c>
+      <c r="V56">
+        <v>0.28</v>
+      </c>
+      <c r="W56">
+        <v>0.03456</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>8.385799286165964</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.06122800456672686</v>
+      </c>
+      <c r="C57">
+        <v>13.47237644471171</v>
+      </c>
+      <c r="D57">
+        <v>29.16387644471171</v>
+      </c>
+      <c r="E57">
+        <v>-6.500499999999999</v>
+      </c>
+      <c r="F57">
+        <v>15.9995</v>
+      </c>
+      <c r="G57">
+        <v>0.308</v>
+      </c>
+      <c r="H57">
+        <v>6.59</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>6.54</v>
+      </c>
+      <c r="K57">
+        <v>0.217</v>
+      </c>
+      <c r="L57">
+        <v>6.323</v>
+      </c>
+      <c r="M57">
+        <v>0.7679760000000001</v>
+      </c>
+      <c r="N57">
+        <v>5.555024</v>
+      </c>
+      <c r="O57">
+        <v>1.55540672</v>
+      </c>
+      <c r="P57">
+        <v>3.99961728</v>
+      </c>
+      <c r="Q57">
+        <v>4.216617279999999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.09382223237050415</v>
+      </c>
+      <c r="T57">
+        <v>1.196135486315308</v>
+      </c>
+      <c r="U57">
+        <v>0.048</v>
+      </c>
+      <c r="V57">
+        <v>0.28</v>
+      </c>
+      <c r="W57">
+        <v>0.03456</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>8.233330208235675</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.06110365656106866</v>
+      </c>
+      <c r="C58">
+        <v>13.34407175114645</v>
+      </c>
+      <c r="D58">
+        <v>29.32647175114645</v>
+      </c>
+      <c r="E58">
+        <v>-6.209599999999998</v>
+      </c>
+      <c r="F58">
+        <v>16.2904</v>
+      </c>
+      <c r="G58">
+        <v>0.308</v>
+      </c>
+      <c r="H58">
+        <v>6.59</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>6.54</v>
+      </c>
+      <c r="K58">
+        <v>0.217</v>
+      </c>
+      <c r="L58">
+        <v>6.323</v>
+      </c>
+      <c r="M58">
+        <v>0.7819392000000001</v>
+      </c>
+      <c r="N58">
+        <v>5.5410608</v>
+      </c>
+      <c r="O58">
+        <v>1.551497024</v>
+      </c>
+      <c r="P58">
+        <v>3.989563776</v>
+      </c>
+      <c r="Q58">
+        <v>4.206563775999999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.09488649218424697</v>
+      </c>
+      <c r="T58">
+        <v>1.21927156922276</v>
+      </c>
+      <c r="U58">
+        <v>0.048</v>
+      </c>
+      <c r="V58">
+        <v>0.28</v>
+      </c>
+      <c r="W58">
+        <v>0.03456</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>8.08630645451718</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.06097930855541046</v>
+      </c>
+      <c r="C59">
+        <v>13.21759023453316</v>
+      </c>
+      <c r="D59">
+        <v>29.49089023453316</v>
+      </c>
+      <c r="E59">
+        <v>-5.918699999999998</v>
+      </c>
+      <c r="F59">
+        <v>16.5813</v>
+      </c>
+      <c r="G59">
+        <v>0.308</v>
+      </c>
+      <c r="H59">
+        <v>6.59</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>6.54</v>
+      </c>
+      <c r="K59">
+        <v>0.217</v>
+      </c>
+      <c r="L59">
+        <v>6.323</v>
+      </c>
+      <c r="M59">
+        <v>0.7959024000000001</v>
+      </c>
+      <c r="N59">
+        <v>5.5270976</v>
+      </c>
+      <c r="O59">
+        <v>1.547587328</v>
+      </c>
+      <c r="P59">
+        <v>3.979510272</v>
+      </c>
+      <c r="Q59">
+        <v>4.196510271999999</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.09600025245444295</v>
+      </c>
+      <c r="T59">
+        <v>1.243483749009629</v>
+      </c>
+      <c r="U59">
+        <v>0.048</v>
+      </c>
+      <c r="V59">
+        <v>0.28</v>
+      </c>
+      <c r="W59">
+        <v>0.03456</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>7.944441428999334</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.06085496054975227</v>
+      </c>
+      <c r="C60">
+        <v>13.09296273261705</v>
+      </c>
+      <c r="D60">
+        <v>29.65716273261705</v>
+      </c>
+      <c r="E60">
+        <v>-5.627800000000001</v>
+      </c>
+      <c r="F60">
+        <v>16.8722</v>
+      </c>
+      <c r="G60">
+        <v>0.308</v>
+      </c>
+      <c r="H60">
+        <v>6.59</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>6.54</v>
+      </c>
+      <c r="K60">
+        <v>0.217</v>
+      </c>
+      <c r="L60">
+        <v>6.323</v>
+      </c>
+      <c r="M60">
+        <v>0.8098656</v>
+      </c>
+      <c r="N60">
+        <v>5.5131344</v>
+      </c>
+      <c r="O60">
+        <v>1.543677632</v>
+      </c>
+      <c r="P60">
+        <v>3.969456768</v>
+      </c>
+      <c r="Q60">
+        <v>4.186456767999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.09716704892798159</v>
+      </c>
+      <c r="T60">
+        <v>1.26884888973873</v>
+      </c>
+      <c r="U60">
+        <v>0.048</v>
+      </c>
+      <c r="V60">
+        <v>0.28</v>
+      </c>
+      <c r="W60">
+        <v>0.03456</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>7.80746830091314</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.06136781254409407</v>
+      </c>
+      <c r="C61">
+        <v>12.12810574080739</v>
+      </c>
+      <c r="D61">
+        <v>28.98320574080739</v>
+      </c>
+      <c r="E61">
+        <v>-5.3369</v>
+      </c>
+      <c r="F61">
+        <v>17.1631</v>
+      </c>
+      <c r="G61">
+        <v>0.308</v>
+      </c>
+      <c r="H61">
+        <v>6.59</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>6.54</v>
+      </c>
+      <c r="K61">
+        <v>0.217</v>
+      </c>
+      <c r="L61">
+        <v>6.323</v>
+      </c>
+      <c r="M61">
+        <v>0.8495734500000001</v>
+      </c>
+      <c r="N61">
+        <v>5.47342655</v>
+      </c>
+      <c r="O61">
+        <v>1.532559434</v>
+      </c>
+      <c r="P61">
+        <v>3.940867116</v>
+      </c>
+      <c r="Q61">
+        <v>4.157867115999999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.09839076230266847</v>
+      </c>
+      <c r="T61">
+        <v>1.295451354405836</v>
+      </c>
+      <c r="U61">
+        <v>0.0495</v>
+      </c>
+      <c r="V61">
+        <v>0.28</v>
+      </c>
+      <c r="W61">
+        <v>0.03564</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>7.442558380326033</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.06125426453843587</v>
+      </c>
+      <c r="C62">
+        <v>11.98376966873372</v>
+      </c>
+      <c r="D62">
+        <v>29.12976966873372</v>
+      </c>
+      <c r="E62">
+        <v>-5.045999999999999</v>
+      </c>
+      <c r="F62">
+        <v>17.454</v>
+      </c>
+      <c r="G62">
+        <v>0.308</v>
+      </c>
+      <c r="H62">
+        <v>6.59</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>6.54</v>
+      </c>
+      <c r="K62">
+        <v>0.217</v>
+      </c>
+      <c r="L62">
+        <v>6.323</v>
+      </c>
+      <c r="M62">
+        <v>0.8639730000000001</v>
+      </c>
+      <c r="N62">
+        <v>5.459027000000001</v>
+      </c>
+      <c r="O62">
+        <v>1.52852756</v>
+      </c>
+      <c r="P62">
+        <v>3.93049944</v>
+      </c>
+      <c r="Q62">
+        <v>4.14749944</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.09967566134608968</v>
+      </c>
+      <c r="T62">
+        <v>1.323383942306298</v>
+      </c>
+      <c r="U62">
+        <v>0.0495</v>
+      </c>
+      <c r="V62">
+        <v>0.28</v>
+      </c>
+      <c r="W62">
+        <v>0.03564</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>7.318515740653933</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.06114071653277767</v>
+      </c>
+      <c r="C63">
+        <v>11.84092343622655</v>
+      </c>
+      <c r="D63">
+        <v>29.27782343622656</v>
+      </c>
+      <c r="E63">
+        <v>-4.755099999999999</v>
+      </c>
+      <c r="F63">
+        <v>17.7449</v>
+      </c>
+      <c r="G63">
+        <v>0.308</v>
+      </c>
+      <c r="H63">
+        <v>6.59</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>6.54</v>
+      </c>
+      <c r="K63">
+        <v>0.217</v>
+      </c>
+      <c r="L63">
+        <v>6.323</v>
+      </c>
+      <c r="M63">
+        <v>0.8783725500000001</v>
+      </c>
+      <c r="N63">
+        <v>5.44462745</v>
+      </c>
+      <c r="O63">
+        <v>1.524495686</v>
+      </c>
+      <c r="P63">
+        <v>3.920131764</v>
+      </c>
+      <c r="Q63">
+        <v>4.137131764</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1010264526481479</v>
+      </c>
+      <c r="T63">
+        <v>1.352748970611911</v>
+      </c>
+      <c r="U63">
+        <v>0.0495</v>
+      </c>
+      <c r="V63">
+        <v>0.28</v>
+      </c>
+      <c r="W63">
+        <v>0.03564</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>7.198540072774359</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.06102716852711947</v>
+      </c>
+      <c r="C64">
+        <v>11.69958987592581</v>
+      </c>
+      <c r="D64">
+        <v>29.42738987592581</v>
+      </c>
+      <c r="E64">
+        <v>-4.464200000000002</v>
+      </c>
+      <c r="F64">
+        <v>18.0358</v>
+      </c>
+      <c r="G64">
+        <v>0.308</v>
+      </c>
+      <c r="H64">
+        <v>6.59</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>6.54</v>
+      </c>
+      <c r="K64">
+        <v>0.217</v>
+      </c>
+      <c r="L64">
+        <v>6.323</v>
+      </c>
+      <c r="M64">
+        <v>0.8927721</v>
+      </c>
+      <c r="N64">
+        <v>5.4302279</v>
+      </c>
+      <c r="O64">
+        <v>1.520463812</v>
+      </c>
+      <c r="P64">
+        <v>3.909764088</v>
+      </c>
+      <c r="Q64">
+        <v>4.126764088</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1024483382292618</v>
+      </c>
+      <c r="T64">
+        <v>1.383659526723082</v>
+      </c>
+      <c r="U64">
+        <v>0.0495</v>
+      </c>
+      <c r="V64">
+        <v>0.28</v>
+      </c>
+      <c r="W64">
+        <v>0.03564</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>7.082434587729613</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.06091362052146128</v>
+      </c>
+      <c r="C65">
+        <v>11.55979228943131</v>
+      </c>
+      <c r="D65">
+        <v>29.57849228943131</v>
+      </c>
+      <c r="E65">
+        <v>-4.173300000000001</v>
+      </c>
+      <c r="F65">
+        <v>18.3267</v>
+      </c>
+      <c r="G65">
+        <v>0.308</v>
+      </c>
+      <c r="H65">
+        <v>6.59</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>6.54</v>
+      </c>
+      <c r="K65">
+        <v>0.217</v>
+      </c>
+      <c r="L65">
+        <v>6.323</v>
+      </c>
+      <c r="M65">
+        <v>0.90717165</v>
+      </c>
+      <c r="N65">
+        <v>5.41582835</v>
+      </c>
+      <c r="O65">
+        <v>1.516431938</v>
+      </c>
+      <c r="P65">
+        <v>3.899396412</v>
+      </c>
+      <c r="Q65">
+        <v>4.116396411999999</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1039470824904359</v>
+      </c>
+      <c r="T65">
+        <v>1.416240923705128</v>
+      </c>
+      <c r="U65">
+        <v>0.0495</v>
+      </c>
+      <c r="V65">
+        <v>0.28</v>
+      </c>
+      <c r="W65">
+        <v>0.03564</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>6.970014991098983</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.06080007251580308</v>
+      </c>
+      <c r="C66">
+        <v>11.421554459405</v>
+      </c>
+      <c r="D66">
+        <v>29.731154459405</v>
+      </c>
+      <c r="E66">
+        <v>-3.882400000000001</v>
+      </c>
+      <c r="F66">
+        <v>18.6176</v>
+      </c>
+      <c r="G66">
+        <v>0.308</v>
+      </c>
+      <c r="H66">
+        <v>6.59</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>6.54</v>
+      </c>
+      <c r="K66">
+        <v>0.217</v>
+      </c>
+      <c r="L66">
+        <v>6.323</v>
+      </c>
+      <c r="M66">
+        <v>0.9215712</v>
+      </c>
+      <c r="N66">
+        <v>5.401428800000001</v>
+      </c>
+      <c r="O66">
+        <v>1.512400064</v>
+      </c>
+      <c r="P66">
+        <v>3.889028736</v>
+      </c>
+      <c r="Q66">
+        <v>4.106028736</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1055290903216752</v>
+      </c>
+      <c r="T66">
+        <v>1.450632398297288</v>
+      </c>
+      <c r="U66">
+        <v>0.0495</v>
+      </c>
+      <c r="V66">
+        <v>0.28</v>
+      </c>
+      <c r="W66">
+        <v>0.03564</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>6.861108506863062</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.06068652451014488</v>
+      </c>
+      <c r="C67">
+        <v>11.28490066204976</v>
+      </c>
+      <c r="D67">
+        <v>29.88540066204976</v>
+      </c>
+      <c r="E67">
+        <v>-3.5915</v>
+      </c>
+      <c r="F67">
+        <v>18.9085</v>
+      </c>
+      <c r="G67">
+        <v>0.308</v>
+      </c>
+      <c r="H67">
+        <v>6.59</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>6.54</v>
+      </c>
+      <c r="K67">
+        <v>0.217</v>
+      </c>
+      <c r="L67">
+        <v>6.323</v>
+      </c>
+      <c r="M67">
+        <v>0.9359707500000001</v>
+      </c>
+      <c r="N67">
+        <v>5.38702925</v>
+      </c>
+      <c r="O67">
+        <v>1.50836819</v>
+      </c>
+      <c r="P67">
+        <v>3.87866106</v>
+      </c>
+      <c r="Q67">
+        <v>4.095661059999999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.107201498600414</v>
+      </c>
+      <c r="T67">
+        <v>1.486989100008999</v>
+      </c>
+      <c r="U67">
+        <v>0.0495</v>
+      </c>
+      <c r="V67">
+        <v>0.28</v>
+      </c>
+      <c r="W67">
+        <v>0.03564</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>6.755552991372861</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.06057297650448668</v>
+      </c>
+      <c r="C68">
+        <v>11.14985567997865</v>
+      </c>
+      <c r="D68">
+        <v>30.04125567997865</v>
+      </c>
+      <c r="E68">
+        <v>-3.300599999999999</v>
+      </c>
+      <c r="F68">
+        <v>19.1994</v>
+      </c>
+      <c r="G68">
+        <v>0.308</v>
+      </c>
+      <c r="H68">
+        <v>6.59</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>6.54</v>
+      </c>
+      <c r="K68">
+        <v>0.217</v>
+      </c>
+      <c r="L68">
+        <v>6.323</v>
+      </c>
+      <c r="M68">
+        <v>0.9503703000000001</v>
+      </c>
+      <c r="N68">
+        <v>5.3726297</v>
+      </c>
+      <c r="O68">
+        <v>1.504336316</v>
+      </c>
+      <c r="P68">
+        <v>3.868293384</v>
+      </c>
+      <c r="Q68">
+        <v>4.085293384</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1089722838367256</v>
+      </c>
+      <c r="T68">
+        <v>1.525484431233164</v>
+      </c>
+      <c r="U68">
+        <v>0.0495</v>
+      </c>
+      <c r="V68">
+        <v>0.28</v>
+      </c>
+      <c r="W68">
+        <v>0.03564</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>6.65319612786721</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.06045942849882849</v>
+      </c>
+      <c r="C69">
+        <v>11.01644481548903</v>
+      </c>
+      <c r="D69">
+        <v>30.19874481548904</v>
+      </c>
+      <c r="E69">
+        <v>-3.009699999999999</v>
+      </c>
+      <c r="F69">
+        <v>19.4903</v>
+      </c>
+      <c r="G69">
+        <v>0.308</v>
+      </c>
+      <c r="H69">
+        <v>6.59</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>6.54</v>
+      </c>
+      <c r="K69">
+        <v>0.217</v>
+      </c>
+      <c r="L69">
+        <v>6.323</v>
+      </c>
+      <c r="M69">
+        <v>0.9647698500000002</v>
+      </c>
+      <c r="N69">
+        <v>5.358230150000001</v>
+      </c>
+      <c r="O69">
+        <v>1.500304442</v>
+      </c>
+      <c r="P69">
+        <v>3.857925708000001</v>
+      </c>
+      <c r="Q69">
+        <v>4.074925708</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1108503893903894</v>
+      </c>
+      <c r="T69">
+        <v>1.566312812834552</v>
+      </c>
+      <c r="U69">
+        <v>0.0495</v>
+      </c>
+      <c r="V69">
+        <v>0.28</v>
+      </c>
+      <c r="W69">
+        <v>0.03564</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>6.553894693122924</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.06034588049317029</v>
+      </c>
+      <c r="C70">
+        <v>10.88469390425645</v>
+      </c>
+      <c r="D70">
+        <v>30.35789390425645</v>
+      </c>
+      <c r="E70">
+        <v>-2.718799999999998</v>
+      </c>
+      <c r="F70">
+        <v>19.7812</v>
+      </c>
+      <c r="G70">
+        <v>0.308</v>
+      </c>
+      <c r="H70">
+        <v>6.59</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>6.54</v>
+      </c>
+      <c r="K70">
+        <v>0.217</v>
+      </c>
+      <c r="L70">
+        <v>6.323</v>
+      </c>
+      <c r="M70">
+        <v>0.9791694000000002</v>
+      </c>
+      <c r="N70">
+        <v>5.3438306</v>
+      </c>
+      <c r="O70">
+        <v>1.496272568</v>
+      </c>
+      <c r="P70">
+        <v>3.847558032</v>
+      </c>
+      <c r="Q70">
+        <v>4.064558032</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1128458765411572</v>
+      </c>
+      <c r="T70">
+        <v>1.609692968286025</v>
+      </c>
+      <c r="U70">
+        <v>0.0495</v>
+      </c>
+      <c r="V70">
+        <v>0.28</v>
+      </c>
+      <c r="W70">
+        <v>0.03564</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>6.457513888812293</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.0602323324875121</v>
+      </c>
+      <c r="C71">
+        <v>10.75462932946365</v>
+      </c>
+      <c r="D71">
+        <v>30.51872932946365</v>
+      </c>
+      <c r="E71">
+        <v>-2.427899999999998</v>
+      </c>
+      <c r="F71">
+        <v>20.0721</v>
+      </c>
+      <c r="G71">
+        <v>0.308</v>
+      </c>
+      <c r="H71">
+        <v>6.59</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>6.54</v>
+      </c>
+      <c r="K71">
+        <v>0.217</v>
+      </c>
+      <c r="L71">
+        <v>6.323</v>
+      </c>
+      <c r="M71">
+        <v>0.9935689500000001</v>
+      </c>
+      <c r="N71">
+        <v>5.32943105</v>
+      </c>
+      <c r="O71">
+        <v>1.492240694</v>
+      </c>
+      <c r="P71">
+        <v>3.837190356</v>
+      </c>
+      <c r="Q71">
+        <v>4.054190355999999</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1149701047984261</v>
+      </c>
+      <c r="T71">
+        <v>1.655871843444046</v>
+      </c>
+      <c r="U71">
+        <v>0.0495</v>
+      </c>
+      <c r="V71">
+        <v>0.28</v>
+      </c>
+      <c r="W71">
+        <v>0.03564</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>6.363926731003419</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.0601187844818539</v>
+      </c>
+      <c r="C72">
+        <v>10.62627803638138</v>
+      </c>
+      <c r="D72">
+        <v>30.68127803638138</v>
+      </c>
+      <c r="E72">
+        <v>-2.136999999999997</v>
+      </c>
+      <c r="F72">
+        <v>20.363</v>
+      </c>
+      <c r="G72">
+        <v>0.308</v>
+      </c>
+      <c r="H72">
+        <v>6.59</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>6.54</v>
+      </c>
+      <c r="K72">
+        <v>0.217</v>
+      </c>
+      <c r="L72">
+        <v>6.323</v>
+      </c>
+      <c r="M72">
+        <v>1.0079685</v>
+      </c>
+      <c r="N72">
+        <v>5.3150315</v>
+      </c>
+      <c r="O72">
+        <v>1.48820882</v>
+      </c>
+      <c r="P72">
+        <v>3.82682268</v>
+      </c>
+      <c r="Q72">
+        <v>4.04382268</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1172359482728463</v>
+      </c>
+      <c r="T72">
+        <v>1.705129310279268</v>
+      </c>
+      <c r="U72">
+        <v>0.0495</v>
+      </c>
+      <c r="V72">
+        <v>0.28</v>
+      </c>
+      <c r="W72">
+        <v>0.03564</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>6.273013491989084</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.0600052364761957</v>
+      </c>
+      <c r="C73">
+        <v>10.49966754741733</v>
+      </c>
+      <c r="D73">
+        <v>30.84556754741733</v>
+      </c>
+      <c r="E73">
+        <v>-1.8461</v>
+      </c>
+      <c r="F73">
+        <v>20.6539</v>
+      </c>
+      <c r="G73">
+        <v>0.308</v>
+      </c>
+      <c r="H73">
+        <v>6.59</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>6.54</v>
+      </c>
+      <c r="K73">
+        <v>0.217</v>
+      </c>
+      <c r="L73">
+        <v>6.323</v>
+      </c>
+      <c r="M73">
+        <v>1.02236805</v>
+      </c>
+      <c r="N73">
+        <v>5.300631950000001</v>
+      </c>
+      <c r="O73">
+        <v>1.484176946</v>
+      </c>
+      <c r="P73">
+        <v>3.816455004</v>
+      </c>
+      <c r="Q73">
+        <v>4.033455004</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1196580568144679</v>
+      </c>
+      <c r="T73">
+        <v>1.757783843792781</v>
+      </c>
+      <c r="U73">
+        <v>0.0495</v>
+      </c>
+      <c r="V73">
+        <v>0.28</v>
+      </c>
+      <c r="W73">
+        <v>0.03564</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>6.184661189285014</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.0606174484705375</v>
+      </c>
+      <c r="C74">
+        <v>9.343220577050456</v>
+      </c>
+      <c r="D74">
+        <v>29.98002057705046</v>
+      </c>
+      <c r="E74">
+        <v>-1.555199999999999</v>
+      </c>
+      <c r="F74">
+        <v>20.9448</v>
+      </c>
+      <c r="G74">
+        <v>0.308</v>
+      </c>
+      <c r="H74">
+        <v>6.59</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>6.54</v>
+      </c>
+      <c r="K74">
+        <v>0.217</v>
+      </c>
+      <c r="L74">
+        <v>6.323</v>
+      </c>
+      <c r="M74">
+        <v>1.06609032</v>
+      </c>
+      <c r="N74">
+        <v>5.256909680000001</v>
+      </c>
+      <c r="O74">
+        <v>1.4719347104</v>
+      </c>
+      <c r="P74">
+        <v>3.7849749696</v>
+      </c>
+      <c r="Q74">
+        <v>4.0019749696</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1222531731090625</v>
+      </c>
+      <c r="T74">
+        <v>1.814199415414402</v>
+      </c>
+      <c r="U74">
+        <v>0.0509</v>
+      </c>
+      <c r="V74">
+        <v>0.28</v>
+      </c>
+      <c r="W74">
+        <v>0.036648</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>5.931017176856085</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.0605139804648793</v>
+      </c>
+      <c r="C75">
+        <v>9.195176602168303</v>
+      </c>
+      <c r="D75">
+        <v>30.1228766021683</v>
+      </c>
+      <c r="E75">
+        <v>-1.264300000000002</v>
+      </c>
+      <c r="F75">
+        <v>21.2357</v>
+      </c>
+      <c r="G75">
+        <v>0.308</v>
+      </c>
+      <c r="H75">
+        <v>6.59</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>6.54</v>
+      </c>
+      <c r="K75">
+        <v>0.217</v>
+      </c>
+      <c r="L75">
+        <v>6.323</v>
+      </c>
+      <c r="M75">
+        <v>1.08089713</v>
+      </c>
+      <c r="N75">
+        <v>5.24210287</v>
+      </c>
+      <c r="O75">
+        <v>1.4677888036</v>
+      </c>
+      <c r="P75">
+        <v>3.7743140664</v>
+      </c>
+      <c r="Q75">
+        <v>3.9913140664</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1250405202402937</v>
+      </c>
+      <c r="T75">
+        <v>1.874793918267255</v>
+      </c>
+      <c r="U75">
+        <v>0.0509</v>
+      </c>
+      <c r="V75">
+        <v>0.28</v>
+      </c>
+      <c r="W75">
+        <v>0.036648</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>5.849770366214221</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.06041051245922111</v>
+      </c>
+      <c r="C76">
+        <v>9.048500575227497</v>
+      </c>
+      <c r="D76">
+        <v>30.2671005752275</v>
+      </c>
+      <c r="E76">
+        <v>-0.9734000000000016</v>
+      </c>
+      <c r="F76">
+        <v>21.5266</v>
+      </c>
+      <c r="G76">
+        <v>0.308</v>
+      </c>
+      <c r="H76">
+        <v>6.59</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>6.54</v>
+      </c>
+      <c r="K76">
+        <v>0.217</v>
+      </c>
+      <c r="L76">
+        <v>6.323</v>
+      </c>
+      <c r="M76">
+        <v>1.09570394</v>
+      </c>
+      <c r="N76">
+        <v>5.22729606</v>
+      </c>
+      <c r="O76">
+        <v>1.4636428968</v>
+      </c>
+      <c r="P76">
+        <v>3.7636531632</v>
+      </c>
+      <c r="Q76">
+        <v>3.9806531632</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.128042278689312</v>
+      </c>
+      <c r="T76">
+        <v>1.940049536724173</v>
+      </c>
+      <c r="U76">
+        <v>0.0509</v>
+      </c>
+      <c r="V76">
+        <v>0.28</v>
+      </c>
+      <c r="W76">
+        <v>0.036648</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>5.770719415319435</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.06030704445356291</v>
+      </c>
+      <c r="C77">
+        <v>8.903212239365576</v>
+      </c>
+      <c r="D77">
+        <v>30.41271223936558</v>
+      </c>
+      <c r="E77">
+        <v>-0.682500000000001</v>
+      </c>
+      <c r="F77">
+        <v>21.8175</v>
+      </c>
+      <c r="G77">
+        <v>0.308</v>
+      </c>
+      <c r="H77">
+        <v>6.59</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>6.54</v>
+      </c>
+      <c r="K77">
+        <v>0.217</v>
+      </c>
+      <c r="L77">
+        <v>6.323</v>
+      </c>
+      <c r="M77">
+        <v>1.11051075</v>
+      </c>
+      <c r="N77">
+        <v>5.212489250000001</v>
+      </c>
+      <c r="O77">
+        <v>1.45949699</v>
+      </c>
+      <c r="P77">
+        <v>3.752992260000001</v>
+      </c>
+      <c r="Q77">
+        <v>3.969992260000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1312841778142516</v>
+      </c>
+      <c r="T77">
+        <v>2.010525604657644</v>
+      </c>
+      <c r="U77">
+        <v>0.0509</v>
+      </c>
+      <c r="V77">
+        <v>0.28</v>
+      </c>
+      <c r="W77">
+        <v>0.036648</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>5.693776489781842</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.06020357644790472</v>
+      </c>
+      <c r="C78">
+        <v>8.759331719484837</v>
+      </c>
+      <c r="D78">
+        <v>30.55973171948484</v>
+      </c>
+      <c r="E78">
+        <v>-0.3916000000000004</v>
+      </c>
+      <c r="F78">
+        <v>22.1084</v>
+      </c>
+      <c r="G78">
+        <v>0.308</v>
+      </c>
+      <c r="H78">
+        <v>6.59</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>6.54</v>
+      </c>
+      <c r="K78">
+        <v>0.217</v>
+      </c>
+      <c r="L78">
+        <v>6.323</v>
+      </c>
+      <c r="M78">
+        <v>1.12531756</v>
+      </c>
+      <c r="N78">
+        <v>5.19768244</v>
+      </c>
+      <c r="O78">
+        <v>1.4553510832</v>
+      </c>
+      <c r="P78">
+        <v>3.7423313568</v>
+      </c>
+      <c r="Q78">
+        <v>3.9593313568</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.134796235199603</v>
+      </c>
+      <c r="T78">
+        <v>2.086874678252239</v>
+      </c>
+      <c r="U78">
+        <v>0.0509</v>
+      </c>
+      <c r="V78">
+        <v>0.28</v>
+      </c>
+      <c r="W78">
+        <v>0.036648</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>5.618858378074186</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.06010010844224652</v>
+      </c>
+      <c r="C79">
+        <v>8.616879531524759</v>
+      </c>
+      <c r="D79">
+        <v>30.70817953152476</v>
+      </c>
+      <c r="E79">
+        <v>-0.1006999999999998</v>
+      </c>
+      <c r="F79">
+        <v>22.3993</v>
+      </c>
+      <c r="G79">
+        <v>0.308</v>
+      </c>
+      <c r="H79">
+        <v>6.59</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>6.54</v>
+      </c>
+      <c r="K79">
+        <v>0.217</v>
+      </c>
+      <c r="L79">
+        <v>6.323</v>
+      </c>
+      <c r="M79">
+        <v>1.14012437</v>
+      </c>
+      <c r="N79">
+        <v>5.18287563</v>
+      </c>
+      <c r="O79">
+        <v>1.4512051764</v>
+      </c>
+      <c r="P79">
+        <v>3.7316704536</v>
+      </c>
+      <c r="Q79">
+        <v>3.9486704536</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.1386136888793327</v>
+      </c>
+      <c r="T79">
+        <v>2.169862801724623</v>
+      </c>
+      <c r="U79">
+        <v>0.0509</v>
+      </c>
+      <c r="V79">
+        <v>0.28</v>
+      </c>
+      <c r="W79">
+        <v>0.036648</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>5.545886191345949</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.05999664043658831</v>
+      </c>
+      <c r="C80">
+        <v>8.475876592005939</v>
+      </c>
+      <c r="D80">
+        <v>30.85807659200594</v>
+      </c>
+      <c r="E80">
+        <v>0.1902000000000008</v>
+      </c>
+      <c r="F80">
+        <v>22.6902</v>
+      </c>
+      <c r="G80">
+        <v>0.308</v>
+      </c>
+      <c r="H80">
+        <v>6.59</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>6.54</v>
+      </c>
+      <c r="K80">
+        <v>0.217</v>
+      </c>
+      <c r="L80">
+        <v>6.323</v>
+      </c>
+      <c r="M80">
+        <v>1.15493118</v>
+      </c>
+      <c r="N80">
+        <v>5.16806882</v>
+      </c>
+      <c r="O80">
+        <v>1.4470592696</v>
+      </c>
+      <c r="P80">
+        <v>3.7210095504</v>
+      </c>
+      <c r="Q80">
+        <v>3.9380095504</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.1427781838026742</v>
+      </c>
+      <c r="T80">
+        <v>2.260395300058134</v>
+      </c>
+      <c r="U80">
+        <v>0.0509</v>
+      </c>
+      <c r="V80">
+        <v>0.28</v>
+      </c>
+      <c r="W80">
+        <v>0.036648</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>5.474785086328693</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.05989317243093012</v>
+      </c>
+      <c r="C81">
+        <v>8.336344227854813</v>
+      </c>
+      <c r="D81">
+        <v>31.00944422785481</v>
+      </c>
+      <c r="E81">
+        <v>0.4811000000000014</v>
+      </c>
+      <c r="F81">
+        <v>22.9811</v>
+      </c>
+      <c r="G81">
+        <v>0.308</v>
+      </c>
+      <c r="H81">
+        <v>6.59</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>6.54</v>
+      </c>
+      <c r="K81">
+        <v>0.217</v>
+      </c>
+      <c r="L81">
+        <v>6.323</v>
+      </c>
+      <c r="M81">
+        <v>1.16973799</v>
+      </c>
+      <c r="N81">
+        <v>5.153262010000001</v>
+      </c>
+      <c r="O81">
+        <v>1.4429133628</v>
+      </c>
+      <c r="P81">
+        <v>3.7103486472</v>
+      </c>
+      <c r="Q81">
+        <v>3.9273486472</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.1473392972901434</v>
+      </c>
+      <c r="T81">
+        <v>2.359549941090075</v>
+      </c>
+      <c r="U81">
+        <v>0.0509</v>
+      </c>
+      <c r="V81">
+        <v>0.28</v>
+      </c>
+      <c r="W81">
+        <v>0.036648</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>5.405484009286559</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.05978970442527191</v>
+      </c>
+      <c r="C82">
+        <v>8.198304186519234</v>
+      </c>
+      <c r="D82">
+        <v>31.16230418651924</v>
+      </c>
+      <c r="E82">
+        <v>0.772000000000002</v>
+      </c>
+      <c r="F82">
+        <v>23.272</v>
+      </c>
+      <c r="G82">
+        <v>0.308</v>
+      </c>
+      <c r="H82">
+        <v>6.59</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>6.54</v>
+      </c>
+      <c r="K82">
+        <v>0.217</v>
+      </c>
+      <c r="L82">
+        <v>6.323</v>
+      </c>
+      <c r="M82">
+        <v>1.1845448</v>
+      </c>
+      <c r="N82">
+        <v>5.1384552</v>
+      </c>
+      <c r="O82">
+        <v>1.438767456</v>
+      </c>
+      <c r="P82">
+        <v>3.699687744</v>
+      </c>
+      <c r="Q82">
+        <v>3.916687744</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.1523565221263596</v>
+      </c>
+      <c r="T82">
+        <v>2.468620046225209</v>
+      </c>
+      <c r="U82">
+        <v>0.0509</v>
+      </c>
+      <c r="V82">
+        <v>0.28</v>
+      </c>
+      <c r="W82">
+        <v>0.036648</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>5.337915459170476</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.05968623641961372</v>
+      </c>
+      <c r="C83">
+        <v>8.061778646384351</v>
+      </c>
+      <c r="D83">
+        <v>31.31667864638435</v>
+      </c>
+      <c r="E83">
+        <v>1.062900000000003</v>
+      </c>
+      <c r="F83">
+        <v>23.5629</v>
+      </c>
+      <c r="G83">
+        <v>0.308</v>
+      </c>
+      <c r="H83">
+        <v>6.59</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>6.54</v>
+      </c>
+      <c r="K83">
+        <v>0.217</v>
+      </c>
+      <c r="L83">
+        <v>6.323</v>
+      </c>
+      <c r="M83">
+        <v>1.19935161</v>
+      </c>
+      <c r="N83">
+        <v>5.12364839</v>
+      </c>
+      <c r="O83">
+        <v>1.4346215492</v>
+      </c>
+      <c r="P83">
+        <v>3.6890268408</v>
+      </c>
+      <c r="Q83">
+        <v>3.906026840800001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.1579018758927038</v>
+      </c>
+      <c r="T83">
+        <v>2.589171215058779</v>
+      </c>
+      <c r="U83">
+        <v>0.0509</v>
+      </c>
+      <c r="V83">
+        <v>0.28</v>
+      </c>
+      <c r="W83">
+        <v>0.036648</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>5.27201526831652</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.05958276841395553</v>
+      </c>
+      <c r="C84">
+        <v>7.926790227499982</v>
+      </c>
+      <c r="D84">
+        <v>31.47259022749999</v>
+      </c>
+      <c r="E84">
+        <v>1.353800000000003</v>
+      </c>
+      <c r="F84">
+        <v>23.8538</v>
+      </c>
+      <c r="G84">
+        <v>0.308</v>
+      </c>
+      <c r="H84">
+        <v>6.59</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>6.54</v>
+      </c>
+      <c r="K84">
+        <v>0.217</v>
+      </c>
+      <c r="L84">
+        <v>6.323</v>
+      </c>
+      <c r="M84">
+        <v>1.21415842</v>
+      </c>
+      <c r="N84">
+        <v>5.10884158</v>
+      </c>
+      <c r="O84">
+        <v>1.4304756424</v>
+      </c>
+      <c r="P84">
+        <v>3.6783659376</v>
+      </c>
+      <c r="Q84">
+        <v>3.8953659376</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.1640633800775307</v>
+      </c>
+      <c r="T84">
+        <v>2.72311695820719</v>
+      </c>
+      <c r="U84">
+        <v>0.0509</v>
+      </c>
+      <c r="V84">
+        <v>0.28</v>
+      </c>
+      <c r="W84">
+        <v>0.036648</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>5.207722399190708</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.05947930040829733</v>
+      </c>
+      <c r="C85">
+        <v>7.793362002629809</v>
+      </c>
+      <c r="D85">
+        <v>31.63006200262981</v>
+      </c>
+      <c r="E85">
+        <v>1.6447</v>
+      </c>
+      <c r="F85">
+        <v>24.1447</v>
+      </c>
+      <c r="G85">
+        <v>0.308</v>
+      </c>
+      <c r="H85">
+        <v>6.59</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>6.54</v>
+      </c>
+      <c r="K85">
+        <v>0.217</v>
+      </c>
+      <c r="L85">
+        <v>6.323</v>
+      </c>
+      <c r="M85">
+        <v>1.22896523</v>
+      </c>
+      <c r="N85">
+        <v>5.09403477</v>
+      </c>
+      <c r="O85">
+        <v>1.4263297356</v>
+      </c>
+      <c r="P85">
+        <v>3.6677050344</v>
+      </c>
+      <c r="Q85">
+        <v>3.8847050344</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.1709497671076314</v>
+      </c>
+      <c r="T85">
+        <v>2.872821024078944</v>
+      </c>
+      <c r="U85">
+        <v>0.0509</v>
+      </c>
+      <c r="V85">
+        <v>0.28</v>
+      </c>
+      <c r="W85">
+        <v>0.036648</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>5.144978755826966</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.05937583240263913</v>
+      </c>
+      <c r="C86">
+        <v>7.661517508633896</v>
+      </c>
+      <c r="D86">
+        <v>31.78911750863389</v>
+      </c>
+      <c r="E86">
+        <v>1.935599999999997</v>
+      </c>
+      <c r="F86">
+        <v>24.4356</v>
+      </c>
+      <c r="G86">
+        <v>0.308</v>
+      </c>
+      <c r="H86">
+        <v>6.59</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>6.54</v>
+      </c>
+      <c r="K86">
+        <v>0.217</v>
+      </c>
+      <c r="L86">
+        <v>6.323</v>
+      </c>
+      <c r="M86">
+        <v>1.24377204</v>
+      </c>
+      <c r="N86">
+        <v>5.079227960000001</v>
+      </c>
+      <c r="O86">
+        <v>1.4221838288</v>
+      </c>
+      <c r="P86">
+        <v>3.6570441312</v>
+      </c>
+      <c r="Q86">
+        <v>3.8740441312</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.1786969525164946</v>
+      </c>
+      <c r="T86">
+        <v>3.041238098184664</v>
+      </c>
+      <c r="U86">
+        <v>0.0509</v>
+      </c>
+      <c r="V86">
+        <v>0.28</v>
+      </c>
+      <c r="W86">
+        <v>0.036648</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>5.083729008733788</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.05927236439698093</v>
+      </c>
+      <c r="C87">
+        <v>7.53128075819669</v>
+      </c>
+      <c r="D87">
+        <v>31.94978075819669</v>
+      </c>
+      <c r="E87">
+        <v>2.226499999999998</v>
+      </c>
+      <c r="F87">
+        <v>24.7265</v>
+      </c>
+      <c r="G87">
+        <v>0.308</v>
+      </c>
+      <c r="H87">
+        <v>6.59</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>6.54</v>
+      </c>
+      <c r="K87">
+        <v>0.217</v>
+      </c>
+      <c r="L87">
+        <v>6.323</v>
+      </c>
+      <c r="M87">
+        <v>1.25857885</v>
+      </c>
+      <c r="N87">
+        <v>5.06442115</v>
+      </c>
+      <c r="O87">
+        <v>1.418037922</v>
+      </c>
+      <c r="P87">
+        <v>3.646383228</v>
+      </c>
+      <c r="Q87">
+        <v>3.863383228</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.1874770959798729</v>
+      </c>
+      <c r="T87">
+        <v>3.232110782171149</v>
+      </c>
+      <c r="U87">
+        <v>0.0509</v>
+      </c>
+      <c r="V87">
+        <v>0.28</v>
+      </c>
+      <c r="W87">
+        <v>0.036648</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>5.023920432160449</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.05916889639132274</v>
+      </c>
+      <c r="C88">
+        <v>7.402676251912066</v>
+      </c>
+      <c r="D88">
+        <v>32.11207625191206</v>
+      </c>
+      <c r="E88">
+        <v>2.517399999999999</v>
+      </c>
+      <c r="F88">
+        <v>25.0174</v>
+      </c>
+      <c r="G88">
+        <v>0.308</v>
+      </c>
+      <c r="H88">
+        <v>6.59</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>6.54</v>
+      </c>
+      <c r="K88">
+        <v>0.217</v>
+      </c>
+      <c r="L88">
+        <v>6.323</v>
+      </c>
+      <c r="M88">
+        <v>1.27338566</v>
+      </c>
+      <c r="N88">
+        <v>5.049614340000001</v>
+      </c>
+      <c r="O88">
+        <v>1.4138920152</v>
+      </c>
+      <c r="P88">
+        <v>3.635722324800001</v>
+      </c>
+      <c r="Q88">
+        <v>3.852722324800001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.1975115456523052</v>
+      </c>
+      <c r="T88">
+        <v>3.450250992441418</v>
+      </c>
+      <c r="U88">
+        <v>0.0509</v>
+      </c>
+      <c r="V88">
+        <v>0.28</v>
+      </c>
+      <c r="W88">
+        <v>0.036648</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>4.965502752716723</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.05906542838566453</v>
+      </c>
+      <c r="C89">
+        <v>7.275728990738944</v>
+      </c>
+      <c r="D89">
+        <v>32.27602899073894</v>
+      </c>
+      <c r="E89">
+        <v>2.808299999999999</v>
+      </c>
+      <c r="F89">
+        <v>25.3083</v>
+      </c>
+      <c r="G89">
+        <v>0.308</v>
+      </c>
+      <c r="H89">
+        <v>6.59</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>6.54</v>
+      </c>
+      <c r="K89">
+        <v>0.217</v>
+      </c>
+      <c r="L89">
+        <v>6.323</v>
+      </c>
+      <c r="M89">
+        <v>1.28819247</v>
+      </c>
+      <c r="N89">
+        <v>5.03480753</v>
+      </c>
+      <c r="O89">
+        <v>1.4097461084</v>
+      </c>
+      <c r="P89">
+        <v>3.6250614216</v>
+      </c>
+      <c r="Q89">
+        <v>3.8420614216</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.2090897568128041</v>
+      </c>
+      <c r="T89">
+        <v>3.701951235060959</v>
+      </c>
+      <c r="U89">
+        <v>0.0509</v>
+      </c>
+      <c r="V89">
+        <v>0.28</v>
+      </c>
+      <c r="W89">
+        <v>0.036648</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>4.908428008432622</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.05896196038000634</v>
+      </c>
+      <c r="C90">
+        <v>7.150464488840075</v>
+      </c>
+      <c r="D90">
+        <v>32.44166448884008</v>
+      </c>
+      <c r="E90">
+        <v>3.0992</v>
+      </c>
+      <c r="F90">
+        <v>25.5992</v>
+      </c>
+      <c r="G90">
+        <v>0.308</v>
+      </c>
+      <c r="H90">
+        <v>6.59</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>6.54</v>
+      </c>
+      <c r="K90">
+        <v>0.217</v>
+      </c>
+      <c r="L90">
+        <v>6.323</v>
+      </c>
+      <c r="M90">
+        <v>1.30299928</v>
+      </c>
+      <c r="N90">
+        <v>5.020000720000001</v>
+      </c>
+      <c r="O90">
+        <v>1.4056002016</v>
+      </c>
+      <c r="P90">
+        <v>3.6144005184</v>
+      </c>
+      <c r="Q90">
+        <v>3.8314005184</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.2225976698333862</v>
+      </c>
+      <c r="T90">
+        <v>3.995601518117091</v>
+      </c>
+      <c r="U90">
+        <v>0.0509</v>
+      </c>
+      <c r="V90">
+        <v>0.28</v>
+      </c>
+      <c r="W90">
+        <v>0.036648</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>4.852650417427705</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.05885849237434814</v>
+      </c>
+      <c r="C91">
+        <v>7.026908786818591</v>
+      </c>
+      <c r="D91">
+        <v>32.60900878681859</v>
+      </c>
+      <c r="E91">
+        <v>3.3901</v>
+      </c>
+      <c r="F91">
+        <v>25.8901</v>
+      </c>
+      <c r="G91">
+        <v>0.308</v>
+      </c>
+      <c r="H91">
+        <v>6.59</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>6.54</v>
+      </c>
+      <c r="K91">
+        <v>0.217</v>
+      </c>
+      <c r="L91">
+        <v>6.323</v>
+      </c>
+      <c r="M91">
+        <v>1.31780609</v>
+      </c>
+      <c r="N91">
+        <v>5.005193910000001</v>
+      </c>
+      <c r="O91">
+        <v>1.4014542948</v>
+      </c>
+      <c r="P91">
+        <v>3.6037396152</v>
+      </c>
+      <c r="Q91">
+        <v>3.8207396152</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.2385615670395286</v>
+      </c>
+      <c r="T91">
+        <v>4.342642761728882</v>
+      </c>
+      <c r="U91">
+        <v>0.0509</v>
+      </c>
+      <c r="V91">
+        <v>0.28</v>
+      </c>
+      <c r="W91">
+        <v>0.036648</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>4.798126255434137</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.05875502436868995</v>
+      </c>
+      <c r="C92">
+        <v>6.905088465365939</v>
+      </c>
+      <c r="D92">
+        <v>32.77808846536594</v>
+      </c>
+      <c r="E92">
+        <v>3.681000000000001</v>
+      </c>
+      <c r="F92">
+        <v>26.181</v>
+      </c>
+      <c r="G92">
+        <v>0.308</v>
+      </c>
+      <c r="H92">
+        <v>6.59</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>6.54</v>
+      </c>
+      <c r="K92">
+        <v>0.217</v>
+      </c>
+      <c r="L92">
+        <v>6.323</v>
+      </c>
+      <c r="M92">
+        <v>1.3326129</v>
+      </c>
+      <c r="N92">
+        <v>4.9903871</v>
+      </c>
+      <c r="O92">
+        <v>1.397308388</v>
+      </c>
+      <c r="P92">
+        <v>3.593078712</v>
+      </c>
+      <c r="Q92">
+        <v>3.810078712</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.2577182436868995</v>
+      </c>
+      <c r="T92">
+        <v>4.759092254063033</v>
+      </c>
+      <c r="U92">
+        <v>0.0509</v>
+      </c>
+      <c r="V92">
+        <v>0.28</v>
+      </c>
+      <c r="W92">
+        <v>0.036648</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>4.744813741484869</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.05865155636303174</v>
+      </c>
+      <c r="C93">
+        <v>6.785030659336964</v>
+      </c>
+      <c r="D93">
+        <v>32.94893065933697</v>
+      </c>
+      <c r="E93">
+        <v>3.971900000000002</v>
+      </c>
+      <c r="F93">
+        <v>26.4719</v>
+      </c>
+      <c r="G93">
+        <v>0.308</v>
+      </c>
+      <c r="H93">
+        <v>6.59</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>6.54</v>
+      </c>
+      <c r="K93">
+        <v>0.217</v>
+      </c>
+      <c r="L93">
+        <v>6.323</v>
+      </c>
+      <c r="M93">
+        <v>1.34741971</v>
+      </c>
+      <c r="N93">
+        <v>4.97558029</v>
+      </c>
+      <c r="O93">
+        <v>1.3931624812</v>
+      </c>
+      <c r="P93">
+        <v>3.5824178088</v>
+      </c>
+      <c r="Q93">
+        <v>3.7994178088</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.2811319595892416</v>
+      </c>
+      <c r="T93">
+        <v>5.268086078026993</v>
+      </c>
+      <c r="U93">
+        <v>0.0509</v>
+      </c>
+      <c r="V93">
+        <v>0.28</v>
+      </c>
+      <c r="W93">
+        <v>0.036648</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>4.69267293113888</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.05854808835737355</v>
+      </c>
+      <c r="C94">
+        <v>6.666763072267134</v>
+      </c>
+      <c r="D94">
+        <v>33.12156307226714</v>
+      </c>
+      <c r="E94">
+        <v>4.262800000000002</v>
+      </c>
+      <c r="F94">
+        <v>26.7628</v>
+      </c>
+      <c r="G94">
+        <v>0.308</v>
+      </c>
+      <c r="H94">
+        <v>6.59</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>6.54</v>
+      </c>
+      <c r="K94">
+        <v>0.217</v>
+      </c>
+      <c r="L94">
+        <v>6.323</v>
+      </c>
+      <c r="M94">
+        <v>1.36222652</v>
+      </c>
+      <c r="N94">
+        <v>4.96077348</v>
+      </c>
+      <c r="O94">
+        <v>1.3890165744</v>
+      </c>
+      <c r="P94">
+        <v>3.5717569056</v>
+      </c>
+      <c r="Q94">
+        <v>3.7887569056</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.3103991044671695</v>
+      </c>
+      <c r="T94">
+        <v>5.904328357981946</v>
+      </c>
+      <c r="U94">
+        <v>0.0509</v>
+      </c>
+      <c r="V94">
+        <v>0.28</v>
+      </c>
+      <c r="W94">
+        <v>0.036648</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>4.641665616669979</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.05844462035171535</v>
+      </c>
+      <c r="C95">
+        <v>6.550313991348919</v>
+      </c>
+      <c r="D95">
+        <v>33.29601399134892</v>
+      </c>
+      <c r="E95">
+        <v>4.553700000000003</v>
+      </c>
+      <c r="F95">
+        <v>27.0537</v>
+      </c>
+      <c r="G95">
+        <v>0.308</v>
+      </c>
+      <c r="H95">
+        <v>6.59</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>6.54</v>
+      </c>
+      <c r="K95">
+        <v>0.217</v>
+      </c>
+      <c r="L95">
+        <v>6.323</v>
+      </c>
+      <c r="M95">
+        <v>1.37703333</v>
+      </c>
+      <c r="N95">
+        <v>4.945966670000001</v>
+      </c>
+      <c r="O95">
+        <v>1.3848706676</v>
+      </c>
+      <c r="P95">
+        <v>3.5610960024</v>
+      </c>
+      <c r="Q95">
+        <v>3.7780960024</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.348028290738791</v>
+      </c>
+      <c r="T95">
+        <v>6.722354146495456</v>
+      </c>
+      <c r="U95">
+        <v>0.0509</v>
+      </c>
+      <c r="V95">
+        <v>0.28</v>
+      </c>
+      <c r="W95">
+        <v>0.036648</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>4.591755233695034</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.05834115234605715</v>
+      </c>
+      <c r="C96">
+        <v>6.435712302883644</v>
+      </c>
+      <c r="D96">
+        <v>33.47231230288364</v>
+      </c>
+      <c r="E96">
+        <v>4.8446</v>
+      </c>
+      <c r="F96">
+        <v>27.3446</v>
+      </c>
+      <c r="G96">
+        <v>0.308</v>
+      </c>
+      <c r="H96">
+        <v>6.59</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>6.54</v>
+      </c>
+      <c r="K96">
+        <v>0.217</v>
+      </c>
+      <c r="L96">
+        <v>6.323</v>
+      </c>
+      <c r="M96">
+        <v>1.39184014</v>
+      </c>
+      <c r="N96">
+        <v>4.93115986</v>
+      </c>
+      <c r="O96">
+        <v>1.3807247608</v>
+      </c>
+      <c r="P96">
+        <v>3.5504350992</v>
+      </c>
+      <c r="Q96">
+        <v>3.7674350992</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.3982005391009529</v>
+      </c>
+      <c r="T96">
+        <v>7.813055197846801</v>
+      </c>
+      <c r="U96">
+        <v>0.0509</v>
+      </c>
+      <c r="V96">
+        <v>0.28</v>
+      </c>
+      <c r="W96">
+        <v>0.036648</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>4.542906773762107</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.06001608434039896</v>
+      </c>
+      <c r="C97">
+        <v>3.502296092013111</v>
+      </c>
+      <c r="D97">
+        <v>30.82979609201311</v>
+      </c>
+      <c r="E97">
+        <v>5.1355</v>
+      </c>
+      <c r="F97">
+        <v>27.6355</v>
+      </c>
+      <c r="G97">
+        <v>0.308</v>
+      </c>
+      <c r="H97">
+        <v>6.59</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>6.54</v>
+      </c>
+      <c r="K97">
+        <v>0.217</v>
+      </c>
+      <c r="L97">
+        <v>6.323</v>
+      </c>
+      <c r="M97">
+        <v>1.47849925</v>
+      </c>
+      <c r="N97">
+        <v>4.84450075</v>
+      </c>
+      <c r="O97">
+        <v>1.35646021</v>
+      </c>
+      <c r="P97">
+        <v>3.48804054</v>
+      </c>
+      <c r="Q97">
+        <v>3.70504054</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.4684416868079797</v>
+      </c>
+      <c r="T97">
+        <v>9.340036669738689</v>
+      </c>
+      <c r="U97">
+        <v>0.0535</v>
+      </c>
+      <c r="V97">
+        <v>0.28</v>
+      </c>
+      <c r="W97">
+        <v>0.03852</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>4.276633890751043</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.05993133633474075</v>
+      </c>
+      <c r="C98">
+        <v>3.335040129108474</v>
+      </c>
+      <c r="D98">
+        <v>30.95344012910847</v>
+      </c>
+      <c r="E98">
+        <v>5.426399999999997</v>
+      </c>
+      <c r="F98">
+        <v>27.9264</v>
+      </c>
+      <c r="G98">
+        <v>0.308</v>
+      </c>
+      <c r="H98">
+        <v>6.59</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>6.54</v>
+      </c>
+      <c r="K98">
+        <v>0.217</v>
+      </c>
+      <c r="L98">
+        <v>6.323</v>
+      </c>
+      <c r="M98">
+        <v>1.4940624</v>
+      </c>
+      <c r="N98">
+        <v>4.828937600000001</v>
+      </c>
+      <c r="O98">
+        <v>1.352102528</v>
+      </c>
+      <c r="P98">
+        <v>3.476835072</v>
+      </c>
+      <c r="Q98">
+        <v>3.693835072</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.5738034083685184</v>
+      </c>
+      <c r="T98">
+        <v>11.63050887757649</v>
+      </c>
+      <c r="U98">
+        <v>0.0535</v>
+      </c>
+      <c r="V98">
+        <v>0.28</v>
+      </c>
+      <c r="W98">
+        <v>0.03852</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>4.232085621055721</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.05984658832908256</v>
+      </c>
+      <c r="C99">
+        <v>3.168779917666381</v>
+      </c>
+      <c r="D99">
+        <v>31.07807991766638</v>
+      </c>
+      <c r="E99">
+        <v>5.717299999999998</v>
+      </c>
+      <c r="F99">
+        <v>28.2173</v>
+      </c>
+      <c r="G99">
+        <v>0.308</v>
+      </c>
+      <c r="H99">
+        <v>6.59</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>6.54</v>
+      </c>
+      <c r="K99">
+        <v>0.217</v>
+      </c>
+      <c r="L99">
+        <v>6.323</v>
+      </c>
+      <c r="M99">
+        <v>1.50962555</v>
+      </c>
+      <c r="N99">
+        <v>4.81337445</v>
+      </c>
+      <c r="O99">
+        <v>1.347744846</v>
+      </c>
+      <c r="P99">
+        <v>3.465629604</v>
+      </c>
+      <c r="Q99">
+        <v>3.682629604</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>0.7494062776360848</v>
+      </c>
+      <c r="T99">
+        <v>15.44796255730619</v>
+      </c>
+      <c r="U99">
+        <v>0.0535</v>
+      </c>
+      <c r="V99">
+        <v>0.28</v>
+      </c>
+      <c r="W99">
+        <v>0.03852</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>4.188455872385044</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.05976184032342437</v>
+      </c>
+      <c r="C100">
+        <v>3.003527535054484</v>
+      </c>
+      <c r="D100">
+        <v>31.20372753505448</v>
+      </c>
+      <c r="E100">
+        <v>6.008199999999999</v>
+      </c>
+      <c r="F100">
+        <v>28.5082</v>
+      </c>
+      <c r="G100">
+        <v>0.308</v>
+      </c>
+      <c r="H100">
+        <v>6.59</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>6.54</v>
+      </c>
+      <c r="K100">
+        <v>0.217</v>
+      </c>
+      <c r="L100">
+        <v>6.323</v>
+      </c>
+      <c r="M100">
+        <v>1.5251887</v>
+      </c>
+      <c r="N100">
+        <v>4.7978113</v>
+      </c>
+      <c r="O100">
+        <v>1.343387164</v>
+      </c>
+      <c r="P100">
+        <v>3.454424136</v>
+      </c>
+      <c r="Q100">
+        <v>3.671424136</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.100612016171217</v>
+      </c>
+      <c r="T100">
+        <v>23.08286991676559</v>
+      </c>
+      <c r="U100">
+        <v>0.0535</v>
+      </c>
+      <c r="V100">
+        <v>0.28</v>
+      </c>
+      <c r="W100">
+        <v>0.03852</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>4.145716526748461</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.05967709231776616</v>
+      </c>
+      <c r="C101">
+        <v>2.839295254746823</v>
+      </c>
+      <c r="D101">
+        <v>31.33039525474682</v>
+      </c>
+      <c r="E101">
+        <v>6.299099999999999</v>
+      </c>
+      <c r="F101">
+        <v>28.7991</v>
+      </c>
+      <c r="G101">
+        <v>0.308</v>
+      </c>
+      <c r="H101">
+        <v>6.59</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>6.54</v>
+      </c>
+      <c r="K101">
+        <v>0.217</v>
+      </c>
+      <c r="L101">
+        <v>6.323</v>
+      </c>
+      <c r="M101">
+        <v>1.54075185</v>
+      </c>
+      <c r="N101">
+        <v>4.782248150000001</v>
+      </c>
+      <c r="O101">
+        <v>1.339029482</v>
+      </c>
+      <c r="P101">
+        <v>3.443218668000001</v>
+      </c>
+      <c r="Q101">
+        <v>3.660218668000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>2.154229231776615</v>
+      </c>
+      <c r="T101">
+        <v>45.9875919951438</v>
+      </c>
+      <c r="U101">
+        <v>0.0535</v>
+      </c>
+      <c r="V101">
+        <v>0.28</v>
+      </c>
+      <c r="W101">
+        <v>0.03852</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>4.10384060223585</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/new_zealand/new_zealand_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_telecom_wireless.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07334929072204936</v>
+        <v>0.07317631270802763</v>
       </c>
       <c r="C2">
-        <v>21.96623246672697</v>
+        <v>21.76094200204209</v>
       </c>
       <c r="D2">
-        <v>21.96623246672697</v>
+        <v>22.01324200204209</v>
       </c>
       <c r="E2">
-        <v>-19.3</v>
+        <v>-19.0477</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2523</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01269069</v>
       </c>
       <c r="N2">
-        <v>7.215000000000001</v>
+        <v>7.20230931</v>
       </c>
       <c r="O2">
-        <v>2.0202</v>
+        <v>2.0166466068</v>
       </c>
       <c r="P2">
-        <v>5.194800000000001</v>
+        <v>5.1856627032</v>
       </c>
       <c r="Q2">
-        <v>5.329800000000001</v>
+        <v>5.3206627032</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07334929072204936</v>
+        <v>0.07354964920002791</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.6408694965364412</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>568.5270068057765</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07317631270802763</v>
+        <v>0.07300333469400588</v>
       </c>
       <c r="C3">
-        <v>21.76094200204209</v>
+        <v>21.55585317738957</v>
       </c>
       <c r="D3">
-        <v>22.01324200204209</v>
+        <v>22.06045317738957</v>
       </c>
       <c r="E3">
-        <v>-19.0477</v>
+        <v>-18.7954</v>
       </c>
       <c r="F3">
-        <v>0.2523</v>
+        <v>0.5046</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1527,28 +1527,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M3">
-        <v>0.01269069</v>
+        <v>0.02538138</v>
       </c>
       <c r="N3">
-        <v>7.20230931</v>
+        <v>7.189618620000001</v>
       </c>
       <c r="O3">
-        <v>2.0166466068</v>
+        <v>2.0130932136</v>
       </c>
       <c r="P3">
-        <v>5.1856627032</v>
+        <v>5.176525406400001</v>
       </c>
       <c r="Q3">
-        <v>5.3206627032</v>
+        <v>5.3115254064</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07354964920002791</v>
+        <v>0.07375409662653662</v>
       </c>
       <c r="T3">
-        <v>0.6408694965364412</v>
+        <v>0.6455911461093907</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>568.5270068057765</v>
+        <v>284.2635034028883</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07300333469400588</v>
+        <v>0.07283035667998415</v>
       </c>
       <c r="C4">
-        <v>21.55585317738957</v>
+        <v>21.35096729291274</v>
       </c>
       <c r="D4">
-        <v>22.06045317738957</v>
+        <v>22.10786729291274</v>
       </c>
       <c r="E4">
-        <v>-18.7954</v>
+        <v>-18.5431</v>
       </c>
       <c r="F4">
-        <v>0.5046</v>
+        <v>0.7569</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1609,28 +1609,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M4">
-        <v>0.02538138</v>
+        <v>0.03807207</v>
       </c>
       <c r="N4">
-        <v>7.189618620000001</v>
+        <v>7.176927930000001</v>
       </c>
       <c r="O4">
-        <v>2.0130932136</v>
+        <v>2.009539820400001</v>
       </c>
       <c r="P4">
-        <v>5.176525406400001</v>
+        <v>5.1673881096</v>
       </c>
       <c r="Q4">
-        <v>5.3115254064</v>
+        <v>5.3023881096</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07375409662653662</v>
+        <v>0.07396275946390118</v>
       </c>
       <c r="T4">
-        <v>0.6455911461093907</v>
+        <v>0.6504101492817825</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>284.2635034028883</v>
+        <v>189.5090022685922</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07283035667998415</v>
+        <v>0.07265737866596242</v>
       </c>
       <c r="C5">
-        <v>21.35096729291274</v>
+        <v>21.14628565995652</v>
       </c>
       <c r="D5">
-        <v>22.10786729291274</v>
+        <v>22.15548565995652</v>
       </c>
       <c r="E5">
-        <v>-18.5431</v>
+        <v>-18.2908</v>
       </c>
       <c r="F5">
-        <v>0.7569</v>
+        <v>1.0092</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1691,28 +1691,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M5">
-        <v>0.03807207</v>
+        <v>0.05076276</v>
       </c>
       <c r="N5">
-        <v>7.176927930000001</v>
+        <v>7.164237240000001</v>
       </c>
       <c r="O5">
-        <v>2.009539820400001</v>
+        <v>2.0059864272</v>
       </c>
       <c r="P5">
-        <v>5.1673881096</v>
+        <v>5.1582508128</v>
       </c>
       <c r="Q5">
-        <v>5.3023881096</v>
+        <v>5.2932508128</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07396275946390118</v>
+        <v>0.07417576944371085</v>
       </c>
       <c r="T5">
-        <v>0.6504101492817825</v>
+        <v>0.6553295483535991</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>189.5090022685922</v>
+        <v>142.1317517014441</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07265737866596242</v>
+        <v>0.07248440065194067</v>
       </c>
       <c r="C6">
-        <v>21.14628565995652</v>
+        <v>20.9418096011883</v>
       </c>
       <c r="D6">
-        <v>22.15548565995652</v>
+        <v>22.20330960118831</v>
       </c>
       <c r="E6">
-        <v>-18.2908</v>
+        <v>-18.0385</v>
       </c>
       <c r="F6">
-        <v>1.0092</v>
+        <v>1.2615</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1773,28 +1773,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M6">
-        <v>0.05076276</v>
+        <v>0.06345344999999999</v>
       </c>
       <c r="N6">
-        <v>7.164237240000001</v>
+        <v>7.151546550000001</v>
       </c>
       <c r="O6">
-        <v>2.0059864272</v>
+        <v>2.002433034000001</v>
       </c>
       <c r="P6">
-        <v>5.1582508128</v>
+        <v>5.149113516</v>
       </c>
       <c r="Q6">
-        <v>5.2932508128</v>
+        <v>5.284113516</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07417576944371085</v>
+        <v>0.07439326384414807</v>
       </c>
       <c r="T6">
-        <v>0.6553295483535991</v>
+        <v>0.6603525137216645</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>142.1317517014441</v>
+        <v>113.7054013611553</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07248440065194067</v>
+        <v>0.07231142263791893</v>
       </c>
       <c r="C7">
-        <v>20.9418096011883</v>
+        <v>20.73754045072039</v>
       </c>
       <c r="D7">
-        <v>22.20330960118831</v>
+        <v>22.25134045072039</v>
       </c>
       <c r="E7">
-        <v>-18.0385</v>
+        <v>-17.7862</v>
       </c>
       <c r="F7">
-        <v>1.2615</v>
+        <v>1.5138</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1855,28 +1855,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M7">
-        <v>0.06345344999999999</v>
+        <v>0.07614414</v>
       </c>
       <c r="N7">
-        <v>7.151546550000001</v>
+        <v>7.13885586</v>
       </c>
       <c r="O7">
-        <v>2.002433034000001</v>
+        <v>1.9988796408</v>
       </c>
       <c r="P7">
-        <v>5.149113516</v>
+        <v>5.1399762192</v>
       </c>
       <c r="Q7">
-        <v>5.284113516</v>
+        <v>5.2749762192</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07439326384414807</v>
+        <v>0.07461538578502014</v>
       </c>
       <c r="T7">
-        <v>0.6603525137216645</v>
+        <v>0.6654823506933059</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>113.7054013611553</v>
+        <v>94.75450113429609</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07231142263791893</v>
+        <v>0.07213844462389719</v>
       </c>
       <c r="C8">
-        <v>20.73754045072039</v>
+        <v>20.53347955423407</v>
       </c>
       <c r="D8">
-        <v>22.25134045072039</v>
+        <v>22.29957955423407</v>
       </c>
       <c r="E8">
-        <v>-17.7862</v>
+        <v>-17.5339</v>
       </c>
       <c r="F8">
-        <v>1.5138</v>
+        <v>1.7661</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1937,28 +1937,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M8">
-        <v>0.07614414</v>
+        <v>0.08883482999999999</v>
       </c>
       <c r="N8">
-        <v>7.13885586</v>
+        <v>7.126165170000001</v>
       </c>
       <c r="O8">
-        <v>1.9988796408</v>
+        <v>1.9953262476</v>
       </c>
       <c r="P8">
-        <v>5.1399762192</v>
+        <v>5.130838922400001</v>
       </c>
       <c r="Q8">
-        <v>5.2749762192</v>
+        <v>5.2658389224</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07461538578502014</v>
+        <v>0.07484228454182494</v>
       </c>
       <c r="T8">
-        <v>0.6654823506933059</v>
+        <v>0.670722506739606</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>94.75450113429609</v>
+        <v>81.21814382939667</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07213844462389719</v>
+        <v>0.07196546660987546</v>
       </c>
       <c r="C9">
-        <v>20.53347955423407</v>
+        <v>20.32962826910532</v>
       </c>
       <c r="D9">
-        <v>22.29957955423407</v>
+        <v>22.34802826910532</v>
       </c>
       <c r="E9">
-        <v>-17.5339</v>
+        <v>-17.2816</v>
       </c>
       <c r="F9">
-        <v>1.7661</v>
+        <v>2.0184</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2019,28 +2019,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M9">
-        <v>0.08883483</v>
+        <v>0.10152552</v>
       </c>
       <c r="N9">
-        <v>7.126165170000001</v>
+        <v>7.113474480000001</v>
       </c>
       <c r="O9">
-        <v>1.9953262476</v>
+        <v>1.9917728544</v>
       </c>
       <c r="P9">
-        <v>5.130838922400001</v>
+        <v>5.1217016256</v>
       </c>
       <c r="Q9">
-        <v>5.2658389224</v>
+        <v>5.2567016256</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07484228454182494</v>
+        <v>0.07507411588029941</v>
       </c>
       <c r="T9">
-        <v>0.670722506739606</v>
+        <v>0.6760765792216954</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>81.21814382939665</v>
+        <v>71.06587585072207</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07196546660987546</v>
+        <v>0.07179248859585373</v>
       </c>
       <c r="C10">
-        <v>20.32962826910532</v>
+        <v>20.12598796453208</v>
       </c>
       <c r="D10">
-        <v>22.34802826910532</v>
+        <v>22.39668796453208</v>
       </c>
       <c r="E10">
-        <v>-17.2816</v>
+        <v>-17.0293</v>
       </c>
       <c r="F10">
-        <v>2.0184</v>
+        <v>2.2707</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2101,28 +2101,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M10">
-        <v>0.10152552</v>
+        <v>0.11421621</v>
       </c>
       <c r="N10">
-        <v>7.113474480000001</v>
+        <v>7.10078379</v>
       </c>
       <c r="O10">
-        <v>1.9917728544</v>
+        <v>1.9882194612</v>
       </c>
       <c r="P10">
-        <v>5.1217016256</v>
+        <v>5.1125643288</v>
       </c>
       <c r="Q10">
-        <v>5.2567016256</v>
+        <v>5.247564328799999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07507411588029941</v>
+        <v>0.07531104241302607</v>
       </c>
       <c r="T10">
-        <v>0.6760765792216954</v>
+        <v>0.6815483236264681</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>71.06587585072207</v>
+        <v>63.16966742286406</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07179248859585373</v>
+        <v>0.07161951058183198</v>
       </c>
       <c r="C11">
-        <v>20.12598796453208</v>
+        <v>19.92256002166328</v>
       </c>
       <c r="D11">
-        <v>22.39668796453208</v>
+        <v>22.44556002166328</v>
       </c>
       <c r="E11">
-        <v>-17.0293</v>
+        <v>-16.777</v>
       </c>
       <c r="F11">
-        <v>2.2707</v>
+        <v>2.523</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2183,28 +2183,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M11">
-        <v>0.11421621</v>
+        <v>0.1269069</v>
       </c>
       <c r="N11">
-        <v>7.10078379</v>
+        <v>7.088093100000001</v>
       </c>
       <c r="O11">
-        <v>1.9882194612</v>
+        <v>1.984666068</v>
       </c>
       <c r="P11">
-        <v>5.1125643288</v>
+        <v>5.103427032000001</v>
       </c>
       <c r="Q11">
-        <v>5.247564328799999</v>
+        <v>5.238427032000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07531104241302607</v>
+        <v>0.07555323397981331</v>
       </c>
       <c r="T11">
-        <v>0.6815483236264681</v>
+        <v>0.6871416623513468</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>63.16966742286406</v>
+        <v>56.85270068057766</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07161951058183198</v>
+        <v>0.07144653256781024</v>
       </c>
       <c r="C12">
-        <v>19.92256002166328</v>
+        <v>19.71934583372948</v>
       </c>
       <c r="D12">
-        <v>22.44556002166328</v>
+        <v>22.49464583372948</v>
       </c>
       <c r="E12">
-        <v>-16.777</v>
+        <v>-16.5247</v>
       </c>
       <c r="F12">
-        <v>2.523</v>
+        <v>2.7753</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2265,28 +2265,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M12">
-        <v>0.1269069</v>
+        <v>0.13959759</v>
       </c>
       <c r="N12">
-        <v>7.088093100000001</v>
+        <v>7.075402410000001</v>
       </c>
       <c r="O12">
-        <v>1.984666068</v>
+        <v>1.9811126748</v>
       </c>
       <c r="P12">
-        <v>5.103427032000001</v>
+        <v>5.0942897352</v>
       </c>
       <c r="Q12">
-        <v>5.238427032000001</v>
+        <v>5.2292897352</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07555323397981331</v>
+        <v>0.07580086805371937</v>
       </c>
       <c r="T12">
-        <v>0.6871416623513468</v>
+        <v>0.6928606940812788</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>56.85270068057766</v>
+        <v>51.68427334597969</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07144653256781024</v>
+        <v>0.0712735545537885</v>
       </c>
       <c r="C13">
-        <v>19.71934583372948</v>
+        <v>19.51634680617525</v>
       </c>
       <c r="D13">
-        <v>22.49464583372948</v>
+        <v>22.54394680617525</v>
       </c>
       <c r="E13">
-        <v>-16.5247</v>
+        <v>-16.2724</v>
       </c>
       <c r="F13">
-        <v>2.7753</v>
+        <v>3.0276</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2347,28 +2347,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M13">
-        <v>0.13959759</v>
+        <v>0.15228828</v>
       </c>
       <c r="N13">
-        <v>7.075402410000001</v>
+        <v>7.062711720000001</v>
       </c>
       <c r="O13">
-        <v>1.9811126748</v>
+        <v>1.9775592816</v>
       </c>
       <c r="P13">
-        <v>5.0942897352</v>
+        <v>5.085152438400001</v>
       </c>
       <c r="Q13">
-        <v>5.2292897352</v>
+        <v>5.2201524384</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07580086805371937</v>
+        <v>0.07605413017475966</v>
       </c>
       <c r="T13">
-        <v>0.6928606940812788</v>
+        <v>0.698709703805073</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>51.68427334597969</v>
+        <v>47.37725056714805</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0712735545537885</v>
+        <v>0.07110057653976676</v>
       </c>
       <c r="C14">
-        <v>19.51634680617525</v>
+        <v>19.3135643567934</v>
       </c>
       <c r="D14">
-        <v>22.54394680617525</v>
+        <v>22.5934643567934</v>
       </c>
       <c r="E14">
-        <v>-16.2724</v>
+        <v>-16.0201</v>
       </c>
       <c r="F14">
-        <v>3.0276</v>
+        <v>3.2799</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2429,28 +2429,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M14">
-        <v>0.15228828</v>
+        <v>0.16497897</v>
       </c>
       <c r="N14">
-        <v>7.062711720000001</v>
+        <v>7.050021030000001</v>
       </c>
       <c r="O14">
-        <v>1.9775592816</v>
+        <v>1.9740058884</v>
       </c>
       <c r="P14">
-        <v>5.085152438400001</v>
+        <v>5.0760151416</v>
       </c>
       <c r="Q14">
-        <v>5.2201524384</v>
+        <v>5.2110151416</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07605413017475966</v>
+        <v>0.07631321441352501</v>
       </c>
       <c r="T14">
-        <v>0.698709703805073</v>
+        <v>0.7046931735225177</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>47.37725056714805</v>
+        <v>43.73284667736743</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07110057653976676</v>
+        <v>0.07092759852574504</v>
       </c>
       <c r="C15">
-        <v>19.3135643567934</v>
+        <v>19.11099991586078</v>
       </c>
       <c r="D15">
-        <v>22.5934643567934</v>
+        <v>22.64319991586078</v>
       </c>
       <c r="E15">
-        <v>-16.0201</v>
+        <v>-15.7678</v>
       </c>
       <c r="F15">
-        <v>3.2799</v>
+        <v>3.5322</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2511,28 +2511,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M15">
-        <v>0.16497897</v>
+        <v>0.17766966</v>
       </c>
       <c r="N15">
-        <v>7.050021030000001</v>
+        <v>7.03733034</v>
       </c>
       <c r="O15">
-        <v>1.9740058884</v>
+        <v>1.9704524952</v>
       </c>
       <c r="P15">
-        <v>5.0760151416</v>
+        <v>5.0668778448</v>
       </c>
       <c r="Q15">
-        <v>5.2110151416</v>
+        <v>5.2018778448</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07631321441352501</v>
+        <v>0.07657832386714539</v>
       </c>
       <c r="T15">
-        <v>0.7046931735225177</v>
+        <v>0.7108157936985077</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>43.73284667736743</v>
+        <v>40.60907191469833</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07092759852574504</v>
+        <v>0.07075462051172329</v>
       </c>
       <c r="C16">
-        <v>19.11099991586078</v>
+        <v>18.90865492627606</v>
       </c>
       <c r="D16">
-        <v>22.64319991586078</v>
+        <v>22.69315492627607</v>
       </c>
       <c r="E16">
-        <v>-15.7678</v>
+        <v>-15.5155</v>
       </c>
       <c r="F16">
-        <v>3.5322</v>
+        <v>3.7845</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2593,28 +2593,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M16">
-        <v>0.17766966</v>
+        <v>0.19036035</v>
       </c>
       <c r="N16">
-        <v>7.03733034</v>
+        <v>7.024639650000001</v>
       </c>
       <c r="O16">
-        <v>1.9704524952</v>
+        <v>1.966899102</v>
       </c>
       <c r="P16">
-        <v>5.0668778448</v>
+        <v>5.057740548000001</v>
       </c>
       <c r="Q16">
-        <v>5.2018778448</v>
+        <v>5.192740548000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07657832386714539</v>
+        <v>0.07684967119026269</v>
       </c>
       <c r="T16">
-        <v>0.7108157936985077</v>
+        <v>0.7170824755256973</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>40.60907191469833</v>
+        <v>37.90180045371844</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07075462051172329</v>
+        <v>0.07058164249770156</v>
       </c>
       <c r="C17">
-        <v>18.90865492627606</v>
+        <v>18.70653084369927</v>
       </c>
       <c r="D17">
-        <v>22.69315492627607</v>
+        <v>22.74333084369927</v>
       </c>
       <c r="E17">
-        <v>-15.5155</v>
+        <v>-15.2632</v>
       </c>
       <c r="F17">
-        <v>3.7845</v>
+        <v>4.0368</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2675,28 +2675,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M17">
-        <v>0.19036035</v>
+        <v>0.20305104</v>
       </c>
       <c r="N17">
-        <v>7.024639650000001</v>
+        <v>7.011948960000001</v>
       </c>
       <c r="O17">
-        <v>1.966899102</v>
+        <v>1.9633457088</v>
       </c>
       <c r="P17">
-        <v>5.057740548000001</v>
+        <v>5.0486032512</v>
       </c>
       <c r="Q17">
-        <v>5.192740548000001</v>
+        <v>5.1836032512</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07684967119026269</v>
+        <v>0.07712747916393042</v>
       </c>
       <c r="T17">
-        <v>0.7170824755256973</v>
+        <v>0.7234983640630582</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>37.90180045371844</v>
+        <v>35.53293792536103</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07058164249770156</v>
+        <v>0.07040866448367981</v>
       </c>
       <c r="C18">
-        <v>18.70653084369927</v>
+        <v>18.50462913669313</v>
       </c>
       <c r="D18">
-        <v>22.74333084369927</v>
+        <v>22.79372913669313</v>
       </c>
       <c r="E18">
-        <v>-15.2632</v>
+        <v>-15.0109</v>
       </c>
       <c r="F18">
-        <v>4.0368</v>
+        <v>4.2891</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2757,28 +2757,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M18">
-        <v>0.20305104</v>
+        <v>0.21574173</v>
       </c>
       <c r="N18">
-        <v>7.011948960000001</v>
+        <v>6.99925827</v>
       </c>
       <c r="O18">
-        <v>1.9633457088</v>
+        <v>1.9597923156</v>
       </c>
       <c r="P18">
-        <v>5.0486032512</v>
+        <v>5.0394659544</v>
       </c>
       <c r="Q18">
-        <v>5.1836032512</v>
+        <v>5.1744659544</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07712747916393042</v>
+        <v>0.07741198130563832</v>
       </c>
       <c r="T18">
-        <v>0.7234983640630582</v>
+        <v>0.7300688523242108</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>35.53293792536103</v>
+        <v>33.44276510622215</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07040866448367981</v>
+        <v>0.07023568646965808</v>
       </c>
       <c r="C19">
-        <v>18.50462913669313</v>
+        <v>18.30295128686641</v>
       </c>
       <c r="D19">
-        <v>22.79372913669313</v>
+        <v>22.84435128686641</v>
       </c>
       <c r="E19">
-        <v>-15.0109</v>
+        <v>-14.7586</v>
       </c>
       <c r="F19">
-        <v>4.2891</v>
+        <v>4.5414</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2839,28 +2839,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M19">
-        <v>0.21574173</v>
+        <v>0.22843242</v>
       </c>
       <c r="N19">
-        <v>6.99925827</v>
+        <v>6.986567580000001</v>
       </c>
       <c r="O19">
-        <v>1.9597923156</v>
+        <v>1.956238922400001</v>
       </c>
       <c r="P19">
-        <v>5.0394659544</v>
+        <v>5.0303286576</v>
       </c>
       <c r="Q19">
-        <v>5.1744659544</v>
+        <v>5.1653286576</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07741198130563832</v>
+        <v>0.07770342252397326</v>
       </c>
       <c r="T19">
-        <v>0.7300688523242108</v>
+        <v>0.7367995963966111</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>33.44276510622215</v>
+        <v>31.58483371143203</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07023568646965808</v>
+        <v>0.07006270845563634</v>
       </c>
       <c r="C20">
-        <v>18.30295128686641</v>
+        <v>18.10149878901905</v>
       </c>
       <c r="D20">
-        <v>22.84435128686641</v>
+        <v>22.89519878901905</v>
       </c>
       <c r="E20">
-        <v>-14.7586</v>
+        <v>-14.5063</v>
       </c>
       <c r="F20">
-        <v>4.5414</v>
+        <v>4.7937</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2921,28 +2921,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M20">
-        <v>0.22843242</v>
+        <v>0.24112311</v>
       </c>
       <c r="N20">
-        <v>6.986567580000001</v>
+        <v>6.973876890000001</v>
       </c>
       <c r="O20">
-        <v>1.956238922400001</v>
+        <v>1.9526855292</v>
       </c>
       <c r="P20">
-        <v>5.0303286576</v>
+        <v>5.021191360800001</v>
       </c>
       <c r="Q20">
-        <v>5.1653286576</v>
+        <v>5.1561913608</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07770342252397326</v>
+        <v>0.07800205982177325</v>
       </c>
       <c r="T20">
-        <v>0.7367995963966111</v>
+        <v>0.7436965316806756</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>31.58483371143203</v>
+        <v>29.92247404240929</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07006270845563634</v>
+        <v>0.0698897304416146</v>
       </c>
       <c r="C21">
-        <v>18.10149878901905</v>
+        <v>17.90027315128934</v>
       </c>
       <c r="D21">
-        <v>22.89519878901905</v>
+        <v>22.94627315128934</v>
       </c>
       <c r="E21">
-        <v>-14.5063</v>
+        <v>-14.254</v>
       </c>
       <c r="F21">
-        <v>4.7937</v>
+        <v>5.046</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3003,28 +3003,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M21">
-        <v>0.24112311</v>
+        <v>0.2538138</v>
       </c>
       <c r="N21">
-        <v>6.973876890000001</v>
+        <v>6.961186200000001</v>
       </c>
       <c r="O21">
-        <v>1.9526855292</v>
+        <v>1.949132136</v>
       </c>
       <c r="P21">
-        <v>5.021191360800001</v>
+        <v>5.012054064000001</v>
       </c>
       <c r="Q21">
-        <v>5.1561913608</v>
+        <v>5.147054064000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07800205982177325</v>
+        <v>0.07830816305201824</v>
       </c>
       <c r="T21">
-        <v>0.7436965316806756</v>
+        <v>0.7507658903468417</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>29.92247404240929</v>
+        <v>28.42635034028883</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0698897304416146</v>
+        <v>0.06971675242759287</v>
       </c>
       <c r="C22">
-        <v>17.90027315128934</v>
+        <v>17.69927589530301</v>
       </c>
       <c r="D22">
-        <v>22.94627315128934</v>
+        <v>22.99757589530302</v>
       </c>
       <c r="E22">
-        <v>-14.254</v>
+        <v>-14.0017</v>
       </c>
       <c r="F22">
-        <v>5.046</v>
+        <v>5.2983</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3085,28 +3085,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M22">
-        <v>0.2538138</v>
+        <v>0.26650449</v>
       </c>
       <c r="N22">
-        <v>6.961186200000001</v>
+        <v>6.948495510000001</v>
       </c>
       <c r="O22">
-        <v>1.949132136</v>
+        <v>1.9455787428</v>
       </c>
       <c r="P22">
-        <v>5.012054064000001</v>
+        <v>5.0029167672</v>
       </c>
       <c r="Q22">
-        <v>5.147054064000001</v>
+        <v>5.1379167672</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07830816305201824</v>
+        <v>0.0786220157311302</v>
       </c>
       <c r="T22">
-        <v>0.7507658903468417</v>
+        <v>0.7580142201184804</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>28.42635034028883</v>
+        <v>27.07271460979889</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06971675242759287</v>
+        <v>0.06954377441357112</v>
       </c>
       <c r="C23">
-        <v>17.69927589530301</v>
+        <v>17.49850855632436</v>
       </c>
       <c r="D23">
-        <v>22.99757589530302</v>
+        <v>23.04910855632436</v>
       </c>
       <c r="E23">
-        <v>-14.0017</v>
+        <v>-13.7494</v>
       </c>
       <c r="F23">
-        <v>5.2983</v>
+        <v>5.5506</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3167,28 +3167,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M23">
-        <v>0.26650449</v>
+        <v>0.27919518</v>
       </c>
       <c r="N23">
-        <v>6.948495510000001</v>
+        <v>6.93580482</v>
       </c>
       <c r="O23">
-        <v>1.9455787428</v>
+        <v>1.9420253496</v>
       </c>
       <c r="P23">
-        <v>5.0029167672</v>
+        <v>4.9937794704</v>
       </c>
       <c r="Q23">
-        <v>5.1379167672</v>
+        <v>5.1287794704</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0786220157311302</v>
+        <v>0.07894391591483477</v>
       </c>
       <c r="T23">
-        <v>0.7580142201184804</v>
+        <v>0.7654484044996483</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>27.07271460979889</v>
+        <v>25.84213667298985</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06954377441357112</v>
+        <v>0.06937079639954938</v>
       </c>
       <c r="C24">
-        <v>17.49850855632436</v>
+        <v>17.29797268340936</v>
       </c>
       <c r="D24">
-        <v>23.04910855632436</v>
+        <v>23.10087268340936</v>
       </c>
       <c r="E24">
-        <v>-13.7494</v>
+        <v>-13.4971</v>
       </c>
       <c r="F24">
-        <v>5.5506</v>
+        <v>5.8029</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3249,28 +3249,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M24">
-        <v>0.27919518</v>
+        <v>0.29188587</v>
       </c>
       <c r="N24">
-        <v>6.93580482</v>
+        <v>6.923114130000001</v>
       </c>
       <c r="O24">
-        <v>1.9420253496</v>
+        <v>1.9384719564</v>
       </c>
       <c r="P24">
-        <v>4.9937794704</v>
+        <v>4.984642173600001</v>
       </c>
       <c r="Q24">
-        <v>5.1287794704</v>
+        <v>5.119642173600001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07894391591483477</v>
+        <v>0.07927417714227192</v>
       </c>
       <c r="T24">
-        <v>0.7654484044996483</v>
+        <v>0.7730756845790283</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>25.84213667298985</v>
+        <v>24.71856551329464</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06937079639954938</v>
+        <v>0.06919781838552765</v>
       </c>
       <c r="C25">
-        <v>17.29797268340936</v>
+        <v>17.09766983956091</v>
       </c>
       <c r="D25">
-        <v>23.10087268340936</v>
+        <v>23.15286983956091</v>
       </c>
       <c r="E25">
-        <v>-13.4971</v>
+        <v>-13.2448</v>
       </c>
       <c r="F25">
-        <v>5.8029</v>
+        <v>6.0552</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3331,28 +3331,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M25">
-        <v>0.29188587</v>
+        <v>0.30457656</v>
       </c>
       <c r="N25">
-        <v>6.923114130000001</v>
+        <v>6.910423440000001</v>
       </c>
       <c r="O25">
-        <v>1.9384719564</v>
+        <v>1.9349185632</v>
       </c>
       <c r="P25">
-        <v>4.984642173600001</v>
+        <v>4.975504876800001</v>
       </c>
       <c r="Q25">
-        <v>5.119642173600001</v>
+        <v>5.1105048768</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07927417714227192</v>
+        <v>0.07961312945464163</v>
       </c>
       <c r="T25">
-        <v>0.7730756845790283</v>
+        <v>0.7809036825552342</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>24.71856551329464</v>
+        <v>23.68862528357402</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06919781838552765</v>
+        <v>0.06902484037150591</v>
       </c>
       <c r="C26">
-        <v>17.09766983956091</v>
+        <v>16.89760160188618</v>
       </c>
       <c r="D26">
-        <v>23.15286983956091</v>
+        <v>23.20510160188618</v>
       </c>
       <c r="E26">
-        <v>-13.2448</v>
+        <v>-12.9925</v>
       </c>
       <c r="F26">
-        <v>6.0552</v>
+        <v>6.3075</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3413,28 +3413,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M26">
-        <v>0.30457656</v>
+        <v>0.31726725</v>
       </c>
       <c r="N26">
-        <v>6.910423440000001</v>
+        <v>6.897732750000001</v>
       </c>
       <c r="O26">
-        <v>1.9349185632</v>
+        <v>1.931365170000001</v>
       </c>
       <c r="P26">
-        <v>4.975504876800001</v>
+        <v>4.966367580000001</v>
       </c>
       <c r="Q26">
-        <v>5.1105048768</v>
+        <v>5.101367580000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07961312945464163</v>
+        <v>0.07996112049534121</v>
       </c>
       <c r="T26">
-        <v>0.7809036825552342</v>
+        <v>0.7889404271441388</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>23.68862528357402</v>
+        <v>22.74108027223106</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06902484037150591</v>
+        <v>0.06885186235748417</v>
       </c>
       <c r="C27">
-        <v>16.89760160188618</v>
+        <v>16.69776956175599</v>
       </c>
       <c r="D27">
-        <v>23.20510160188618</v>
+        <v>23.25756956175599</v>
       </c>
       <c r="E27">
-        <v>-12.9925</v>
+        <v>-12.7402</v>
       </c>
       <c r="F27">
-        <v>6.3075</v>
+        <v>6.5598</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3495,28 +3495,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M27">
-        <v>0.31726725</v>
+        <v>0.32995794</v>
       </c>
       <c r="N27">
-        <v>6.897732750000001</v>
+        <v>6.885042060000001</v>
       </c>
       <c r="O27">
-        <v>1.931365170000001</v>
+        <v>1.9278117768</v>
       </c>
       <c r="P27">
-        <v>4.966367580000001</v>
+        <v>4.9572302832</v>
       </c>
       <c r="Q27">
-        <v>5.101367580000001</v>
+        <v>5.0922302832</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07996112049534121</v>
+        <v>0.08031851669930293</v>
       </c>
       <c r="T27">
-        <v>0.7889404271441388</v>
+        <v>0.7971943810462572</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>22.74108027223106</v>
+        <v>21.86642333868371</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06885186235748417</v>
+        <v>0.06867888434346242</v>
       </c>
       <c r="C28">
-        <v>16.69776956175599</v>
+        <v>16.49817532496649</v>
       </c>
       <c r="D28">
-        <v>23.25756956175599</v>
+        <v>23.31027532496649</v>
       </c>
       <c r="E28">
-        <v>-12.7402</v>
+        <v>-12.4879</v>
       </c>
       <c r="F28">
-        <v>6.5598</v>
+        <v>6.812100000000001</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3577,28 +3577,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M28">
-        <v>0.32995794</v>
+        <v>0.34264863</v>
       </c>
       <c r="N28">
-        <v>6.885042060000001</v>
+        <v>6.872351370000001</v>
       </c>
       <c r="O28">
-        <v>1.9278117768</v>
+        <v>1.9242583836</v>
       </c>
       <c r="P28">
-        <v>4.9572302832</v>
+        <v>4.948092986400001</v>
       </c>
       <c r="Q28">
-        <v>5.0922302832</v>
+        <v>5.083092986400001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08031851669930293</v>
+        <v>0.08068570458008552</v>
       </c>
       <c r="T28">
-        <v>0.7971943810462572</v>
+        <v>0.805674470671721</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>21.86642333868371</v>
+        <v>21.05655580762135</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06867888434346242</v>
+        <v>0.0685059063294407</v>
       </c>
       <c r="C29">
-        <v>16.49817532496649</v>
+        <v>16.29882051190295</v>
       </c>
       <c r="D29">
-        <v>23.31027532496649</v>
+        <v>23.36322051190295</v>
       </c>
       <c r="E29">
-        <v>-12.4879</v>
+        <v>-12.2356</v>
       </c>
       <c r="F29">
-        <v>6.812100000000001</v>
+        <v>7.064400000000001</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3659,28 +3659,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M29">
-        <v>0.34264863</v>
+        <v>0.35533932</v>
       </c>
       <c r="N29">
-        <v>6.872351370000001</v>
+        <v>6.859660680000001</v>
       </c>
       <c r="O29">
-        <v>1.9242583836</v>
+        <v>1.9207049904</v>
       </c>
       <c r="P29">
-        <v>4.948092986400001</v>
+        <v>4.9389556896</v>
       </c>
       <c r="Q29">
-        <v>5.083092986400001</v>
+        <v>5.0739556896</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08068570458008552</v>
+        <v>0.08106309212422319</v>
       </c>
       <c r="T29">
-        <v>0.805674470671721</v>
+        <v>0.8143901183423369</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>21.05655580762135</v>
+        <v>20.30453595734916</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0685059063294407</v>
+        <v>0.06833292831541896</v>
       </c>
       <c r="C30">
-        <v>16.29882051190295</v>
+        <v>16.09970675770585</v>
       </c>
       <c r="D30">
-        <v>23.36322051190295</v>
+        <v>23.41640675770585</v>
       </c>
       <c r="E30">
-        <v>-12.2356</v>
+        <v>-11.9833</v>
       </c>
       <c r="F30">
-        <v>7.064400000000001</v>
+        <v>7.316700000000001</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3741,28 +3741,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M30">
-        <v>0.35533932</v>
+        <v>0.36803001</v>
       </c>
       <c r="N30">
-        <v>6.859660680000001</v>
+        <v>6.846969990000001</v>
       </c>
       <c r="O30">
-        <v>1.9207049904</v>
+        <v>1.9171515972</v>
       </c>
       <c r="P30">
-        <v>4.9389556896</v>
+        <v>4.929818392800001</v>
       </c>
       <c r="Q30">
-        <v>5.0739556896</v>
+        <v>5.0648183928</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08106309212422319</v>
+        <v>0.08145111030340697</v>
       </c>
       <c r="T30">
-        <v>0.8143901183423369</v>
+        <v>0.8233512772149417</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>20.30453595734916</v>
+        <v>19.60437954502678</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06833292831541894</v>
+        <v>0.06815995030139721</v>
       </c>
       <c r="C31">
-        <v>16.09970675770585</v>
+        <v>15.90083571243919</v>
       </c>
       <c r="D31">
-        <v>23.41640675770585</v>
+        <v>23.46983571243919</v>
       </c>
       <c r="E31">
-        <v>-11.9833</v>
+        <v>-11.731</v>
       </c>
       <c r="F31">
-        <v>7.3167</v>
+        <v>7.569</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3823,28 +3823,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M31">
-        <v>0.36803001</v>
+        <v>0.3807207</v>
       </c>
       <c r="N31">
-        <v>6.846969990000001</v>
+        <v>6.8342793</v>
       </c>
       <c r="O31">
-        <v>1.9171515972</v>
+        <v>1.913598204</v>
       </c>
       <c r="P31">
-        <v>4.929818392800001</v>
+        <v>4.920681096</v>
       </c>
       <c r="Q31">
-        <v>5.0648183928</v>
+        <v>5.055681096</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08145111030340697</v>
+        <v>0.08185021471628173</v>
       </c>
       <c r="T31">
-        <v>0.8233512772149417</v>
+        <v>0.8325684691981926</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>19.60437954502678</v>
+        <v>18.95090022685922</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06815995030139721</v>
+        <v>0.06798697228737546</v>
       </c>
       <c r="C32">
-        <v>15.90083571243919</v>
+        <v>15.70220904126115</v>
       </c>
       <c r="D32">
-        <v>23.46983571243919</v>
+        <v>23.52350904126115</v>
       </c>
       <c r="E32">
-        <v>-11.731</v>
+        <v>-11.4787</v>
       </c>
       <c r="F32">
-        <v>7.569</v>
+        <v>7.8213</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3905,28 +3905,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M32">
-        <v>0.3807207</v>
+        <v>0.39341139</v>
       </c>
       <c r="N32">
-        <v>6.8342793</v>
+        <v>6.821588610000001</v>
       </c>
       <c r="O32">
-        <v>1.913598204</v>
+        <v>1.910044810800001</v>
       </c>
       <c r="P32">
-        <v>4.920681096</v>
+        <v>4.9115437992</v>
       </c>
       <c r="Q32">
-        <v>5.055681096</v>
+        <v>5.0465437992</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08185021471628173</v>
+        <v>0.08226088737300793</v>
       </c>
       <c r="T32">
-        <v>0.8325684691981926</v>
+        <v>0.8420528261664652</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>18.95090022685922</v>
+        <v>18.33958086470247</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06798697228737546</v>
+        <v>0.06781399427335373</v>
       </c>
       <c r="C33">
-        <v>15.70220904126115</v>
+        <v>15.50382842459703</v>
       </c>
       <c r="D33">
-        <v>23.52350904126115</v>
+        <v>23.57742842459703</v>
       </c>
       <c r="E33">
-        <v>-11.4787</v>
+        <v>-11.2264</v>
       </c>
       <c r="F33">
-        <v>7.8213</v>
+        <v>8.073600000000001</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3987,28 +3987,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M33">
-        <v>0.39341139</v>
+        <v>0.40610208</v>
       </c>
       <c r="N33">
-        <v>6.821588610000001</v>
+        <v>6.808897920000001</v>
       </c>
       <c r="O33">
-        <v>1.910044810800001</v>
+        <v>1.9064914176</v>
       </c>
       <c r="P33">
-        <v>4.9115437992</v>
+        <v>4.9024065024</v>
       </c>
       <c r="Q33">
-        <v>5.0465437992</v>
+        <v>5.0374065024</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08226088737300793</v>
+        <v>0.08268363863728491</v>
       </c>
       <c r="T33">
-        <v>0.8420528261664652</v>
+        <v>0.8518161348102751</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>18.33958086470247</v>
+        <v>17.76646896268052</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06781399427335373</v>
+        <v>0.067641016259332</v>
       </c>
       <c r="C34">
-        <v>15.50382842459703</v>
+        <v>15.30569555831473</v>
       </c>
       <c r="D34">
-        <v>23.57742842459703</v>
+        <v>23.63159555831473</v>
       </c>
       <c r="E34">
-        <v>-11.2264</v>
+        <v>-10.9741</v>
       </c>
       <c r="F34">
-        <v>8.073600000000001</v>
+        <v>8.325900000000001</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4069,28 +4069,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M34">
-        <v>0.40610208</v>
+        <v>0.41879277</v>
       </c>
       <c r="N34">
-        <v>6.808897920000001</v>
+        <v>6.79620723</v>
       </c>
       <c r="O34">
-        <v>1.9064914176</v>
+        <v>1.9029380244</v>
       </c>
       <c r="P34">
-        <v>4.9024065024</v>
+        <v>4.8932692056</v>
       </c>
       <c r="Q34">
-        <v>5.0374065024</v>
+        <v>5.0282692056</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08268363863728491</v>
+        <v>0.08311900934228657</v>
       </c>
       <c r="T34">
-        <v>0.8518161348102751</v>
+        <v>0.861870885503154</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>17.76646896268052</v>
+        <v>17.22809111532656</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.067641016259332</v>
+        <v>0.06746803824531025</v>
       </c>
       <c r="C35">
-        <v>15.30569555831473</v>
+        <v>15.10781215390245</v>
       </c>
       <c r="D35">
-        <v>23.63159555831473</v>
+        <v>23.68601215390245</v>
       </c>
       <c r="E35">
-        <v>-10.9741</v>
+        <v>-10.7218</v>
       </c>
       <c r="F35">
-        <v>8.325900000000001</v>
+        <v>8.578200000000001</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4151,28 +4151,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M35">
-        <v>0.41879277</v>
+        <v>0.43148346</v>
       </c>
       <c r="N35">
-        <v>6.79620723</v>
+        <v>6.783516540000001</v>
       </c>
       <c r="O35">
-        <v>1.9029380244</v>
+        <v>1.8993846312</v>
       </c>
       <c r="P35">
-        <v>4.8932692056</v>
+        <v>4.884131908800001</v>
       </c>
       <c r="Q35">
-        <v>5.0282692056</v>
+        <v>5.0191319088</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08311900934228657</v>
+        <v>0.08356757309895495</v>
       </c>
       <c r="T35">
-        <v>0.861870885503154</v>
+        <v>0.8722303256109688</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>17.22809111532656</v>
+        <v>16.72138255311107</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06746803824531025</v>
+        <v>0.06729506023128852</v>
       </c>
       <c r="C36">
-        <v>15.10781215390245</v>
+        <v>14.91017993864896</v>
       </c>
       <c r="D36">
-        <v>23.68601215390245</v>
+        <v>23.74067993864896</v>
       </c>
       <c r="E36">
-        <v>-10.7218</v>
+        <v>-10.4695</v>
       </c>
       <c r="F36">
-        <v>8.578200000000001</v>
+        <v>8.830500000000001</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4233,28 +4233,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M36">
-        <v>0.43148346</v>
+        <v>0.44417415</v>
       </c>
       <c r="N36">
-        <v>6.783516540000001</v>
+        <v>6.77082585</v>
       </c>
       <c r="O36">
-        <v>1.8993846312</v>
+        <v>1.895831238</v>
       </c>
       <c r="P36">
-        <v>4.884131908800001</v>
+        <v>4.874994612</v>
       </c>
       <c r="Q36">
-        <v>5.0191319088</v>
+        <v>5.009994612</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08356757309895495</v>
+        <v>0.08402993881736696</v>
       </c>
       <c r="T36">
-        <v>0.8722303256109688</v>
+        <v>0.8829085177221008</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>16.72138255311107</v>
+        <v>16.24362876587933</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06729506023128852</v>
+        <v>0.06712208221726679</v>
       </c>
       <c r="C37">
-        <v>14.91017993864896</v>
+        <v>14.71280065582644</v>
       </c>
       <c r="D37">
-        <v>23.74067993864896</v>
+        <v>23.79560065582644</v>
       </c>
       <c r="E37">
-        <v>-10.4695</v>
+        <v>-10.2172</v>
       </c>
       <c r="F37">
-        <v>8.830500000000001</v>
+        <v>9.082800000000001</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4315,28 +4315,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M37">
-        <v>0.44417415</v>
+        <v>0.45686484</v>
       </c>
       <c r="N37">
-        <v>6.77082585</v>
+        <v>6.758135160000001</v>
       </c>
       <c r="O37">
-        <v>1.895831238</v>
+        <v>1.8922778448</v>
       </c>
       <c r="P37">
-        <v>4.874994612</v>
+        <v>4.8658573152</v>
       </c>
       <c r="Q37">
-        <v>5.009994612</v>
+        <v>5.0008573152</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08402993881736696</v>
+        <v>0.08450675346447936</v>
       </c>
       <c r="T37">
-        <v>0.8829085177221008</v>
+        <v>0.8939204033367056</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>16.24362876587933</v>
+        <v>15.79241685571602</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06712208221726679</v>
+        <v>0.06694910420324504</v>
       </c>
       <c r="C38">
-        <v>14.71280065582644</v>
+        <v>14.5156760648757</v>
       </c>
       <c r="D38">
-        <v>23.79560065582644</v>
+        <v>23.8507760648757</v>
       </c>
       <c r="E38">
-        <v>-10.2172</v>
+        <v>-9.9649</v>
       </c>
       <c r="F38">
-        <v>9.082800000000001</v>
+        <v>9.335100000000001</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4397,28 +4397,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M38">
-        <v>0.45686484</v>
+        <v>0.46955553</v>
       </c>
       <c r="N38">
-        <v>6.758135160000001</v>
+        <v>6.745444470000001</v>
       </c>
       <c r="O38">
-        <v>1.8922778448</v>
+        <v>1.8887244516</v>
       </c>
       <c r="P38">
-        <v>4.8658573152</v>
+        <v>4.856720018400001</v>
       </c>
       <c r="Q38">
-        <v>5.0008573152</v>
+        <v>4.991720018400001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08450675346447936</v>
+        <v>0.08499870508451594</v>
       </c>
       <c r="T38">
-        <v>0.8939204033367056</v>
+        <v>0.9052818726216154</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>15.79241685571602</v>
+        <v>15.3655947785345</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06694910420324504</v>
+        <v>0.06677612618922331</v>
       </c>
       <c r="C39">
-        <v>14.5156760648757</v>
+        <v>14.3188079415941</v>
       </c>
       <c r="D39">
-        <v>23.8507760648757</v>
+        <v>23.9062079415941</v>
       </c>
       <c r="E39">
-        <v>-9.9649</v>
+        <v>-9.7126</v>
       </c>
       <c r="F39">
-        <v>9.335100000000001</v>
+        <v>9.587400000000001</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4479,28 +4479,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M39">
-        <v>0.46955553</v>
+        <v>0.48224622</v>
       </c>
       <c r="N39">
-        <v>6.745444470000001</v>
+        <v>6.73275378</v>
       </c>
       <c r="O39">
-        <v>1.8887244516</v>
+        <v>1.8851710584</v>
       </c>
       <c r="P39">
-        <v>4.856720018400001</v>
+        <v>4.8475827216</v>
       </c>
       <c r="Q39">
-        <v>4.991720018400001</v>
+        <v>4.9825827216</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08499870508451594</v>
+        <v>0.08550652611165049</v>
       </c>
       <c r="T39">
-        <v>0.9052818726216154</v>
+        <v>0.917009840915716</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>15.3655947785345</v>
+        <v>14.96123702120465</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06677612618922331</v>
+        <v>0.06660314817520156</v>
       </c>
       <c r="C40">
-        <v>14.3188079415941</v>
+        <v>14.12219807832608</v>
       </c>
       <c r="D40">
-        <v>23.9062079415941</v>
+        <v>23.96189807832608</v>
       </c>
       <c r="E40">
-        <v>-9.7126</v>
+        <v>-9.4603</v>
       </c>
       <c r="F40">
-        <v>9.587400000000001</v>
+        <v>9.839700000000001</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4561,28 +4561,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M40">
-        <v>0.48224622</v>
+        <v>0.49493691</v>
       </c>
       <c r="N40">
-        <v>6.73275378</v>
+        <v>6.720063090000001</v>
       </c>
       <c r="O40">
-        <v>1.8851710584</v>
+        <v>1.881617665200001</v>
       </c>
       <c r="P40">
-        <v>4.8475827216</v>
+        <v>4.838445424800001</v>
       </c>
       <c r="Q40">
-        <v>4.9825827216</v>
+        <v>4.9734454248</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08550652611165049</v>
+        <v>0.08603099700852716</v>
       </c>
       <c r="T40">
-        <v>0.917009840915716</v>
+        <v>0.9291223327604426</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>14.96123702120465</v>
+        <v>14.57761555912248</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06660314817520156</v>
+        <v>0.06643017016117983</v>
       </c>
       <c r="C41">
-        <v>14.12219807832608</v>
+        <v>13.92584828415631</v>
       </c>
       <c r="D41">
-        <v>23.96189807832608</v>
+        <v>24.01784828415631</v>
       </c>
       <c r="E41">
-        <v>-9.4603</v>
+        <v>-9.208</v>
       </c>
       <c r="F41">
-        <v>9.839700000000001</v>
+        <v>10.092</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4643,28 +4643,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M41">
-        <v>0.49493691</v>
+        <v>0.5076276</v>
       </c>
       <c r="N41">
-        <v>6.720063090000001</v>
+        <v>6.707372400000001</v>
       </c>
       <c r="O41">
-        <v>1.881617665200001</v>
+        <v>1.878064272</v>
       </c>
       <c r="P41">
-        <v>4.838445424800001</v>
+        <v>4.829308128</v>
       </c>
       <c r="Q41">
-        <v>4.9734454248</v>
+        <v>4.964308128</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08603099700852716</v>
+        <v>0.08657295026863306</v>
       </c>
       <c r="T41">
-        <v>0.9291223327604426</v>
+        <v>0.941638574333327</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>14.57761555912248</v>
+        <v>14.21317517014442</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06643017016117983</v>
+        <v>0.0662571921471581</v>
       </c>
       <c r="C42">
-        <v>13.92584828415631</v>
+        <v>13.72976038510562</v>
       </c>
       <c r="D42">
-        <v>24.01784828415631</v>
+        <v>24.07406038510562</v>
       </c>
       <c r="E42">
-        <v>-9.208</v>
+        <v>-8.9557</v>
       </c>
       <c r="F42">
-        <v>10.092</v>
+        <v>10.3443</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4725,28 +4725,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M42">
-        <v>0.5076276</v>
+        <v>0.52031829</v>
       </c>
       <c r="N42">
-        <v>6.707372400000001</v>
+        <v>6.694681710000001</v>
       </c>
       <c r="O42">
-        <v>1.878064272</v>
+        <v>1.8745108788</v>
       </c>
       <c r="P42">
-        <v>4.829308128</v>
+        <v>4.8201708312</v>
       </c>
       <c r="Q42">
-        <v>4.964308128</v>
+        <v>4.9551708312</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08657295026863306</v>
+        <v>0.08713327482569169</v>
       </c>
       <c r="T42">
-        <v>0.941638574333327</v>
+        <v>0.9545790952815633</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>14.21317517014442</v>
+        <v>13.8665123611165</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0662571921471581</v>
+        <v>0.06608421413313635</v>
       </c>
       <c r="C43">
-        <v>13.72976038510562</v>
+        <v>13.53393622432966</v>
       </c>
       <c r="D43">
-        <v>24.07406038510562</v>
+        <v>24.13053622432966</v>
       </c>
       <c r="E43">
-        <v>-8.9557</v>
+        <v>-8.7034</v>
       </c>
       <c r="F43">
-        <v>10.3443</v>
+        <v>10.5966</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4807,28 +4807,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M43">
-        <v>0.52031829</v>
+        <v>0.53300898</v>
       </c>
       <c r="N43">
-        <v>6.694681710000001</v>
+        <v>6.681991020000001</v>
       </c>
       <c r="O43">
-        <v>1.8745108788</v>
+        <v>1.8709574856</v>
       </c>
       <c r="P43">
-        <v>4.8201708312</v>
+        <v>4.8110335344</v>
       </c>
       <c r="Q43">
-        <v>4.9551708312</v>
+        <v>4.9460335344</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08713327482569169</v>
+        <v>0.08771292091920062</v>
       </c>
       <c r="T43">
-        <v>0.9545790952815633</v>
+        <v>0.9679658410900835</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>13.8665123611165</v>
+        <v>13.53635730489944</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06608421413313637</v>
+        <v>0.06591123611911463</v>
       </c>
       <c r="C44">
-        <v>13.53393622432965</v>
+        <v>13.33837766232028</v>
       </c>
       <c r="D44">
-        <v>24.13053622432965</v>
+        <v>24.18727766232028</v>
       </c>
       <c r="E44">
-        <v>-8.7034</v>
+        <v>-8.4511</v>
       </c>
       <c r="F44">
-        <v>10.5966</v>
+        <v>10.8489</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4889,28 +4889,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M44">
-        <v>0.53300898</v>
+        <v>0.54569967</v>
       </c>
       <c r="N44">
-        <v>6.681991020000001</v>
+        <v>6.66930033</v>
       </c>
       <c r="O44">
-        <v>1.8709574856</v>
+        <v>1.8674040924</v>
       </c>
       <c r="P44">
-        <v>4.8110335344</v>
+        <v>4.8018962376</v>
       </c>
       <c r="Q44">
-        <v>4.9460335344</v>
+        <v>4.9368962376</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08771292091920062</v>
+        <v>0.08831290547213091</v>
       </c>
       <c r="T44">
-        <v>0.9679658410900835</v>
+        <v>0.9818222972778501</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>13.53635730489944</v>
+        <v>13.22155829780876</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06591123611911463</v>
+        <v>0.06573825810509289</v>
       </c>
       <c r="C45">
-        <v>13.33837766232028</v>
+        <v>13.14308657710996</v>
       </c>
       <c r="D45">
-        <v>24.18727766232028</v>
+        <v>24.24428657710996</v>
       </c>
       <c r="E45">
-        <v>-8.4511</v>
+        <v>-8.1988</v>
       </c>
       <c r="F45">
-        <v>10.8489</v>
+        <v>11.1012</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4971,28 +4971,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M45">
-        <v>0.54569967</v>
+        <v>0.55839036</v>
       </c>
       <c r="N45">
-        <v>6.66930033</v>
+        <v>6.656609640000001</v>
       </c>
       <c r="O45">
-        <v>1.8674040924</v>
+        <v>1.8638506992</v>
       </c>
       <c r="P45">
-        <v>4.8018962376</v>
+        <v>4.792758940800001</v>
       </c>
       <c r="Q45">
-        <v>4.9368962376</v>
+        <v>4.9277589408</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08831290547213091</v>
+        <v>0.08893431804480872</v>
       </c>
       <c r="T45">
-        <v>0.9818222972778501</v>
+        <v>0.9961736269008942</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>13.22155829780876</v>
+        <v>12.92106833649492</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06573825810509289</v>
+        <v>0.06605128009107114</v>
       </c>
       <c r="C46">
-        <v>13.14308657710996</v>
+        <v>12.78781894787871</v>
       </c>
       <c r="D46">
-        <v>24.24428657710996</v>
+        <v>24.14131894787871</v>
       </c>
       <c r="E46">
-        <v>-8.1988</v>
+        <v>-7.9465</v>
       </c>
       <c r="F46">
-        <v>11.1012</v>
+        <v>11.3535</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5053,45 +5053,45 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M46">
-        <v>0.55839036</v>
+        <v>0.5881113</v>
       </c>
       <c r="N46">
-        <v>6.656609640000001</v>
+        <v>6.6268887</v>
       </c>
       <c r="O46">
-        <v>1.8638506992</v>
+        <v>1.855528836</v>
       </c>
       <c r="P46">
-        <v>4.792758940800001</v>
+        <v>4.771359864</v>
       </c>
       <c r="Q46">
-        <v>4.9277589408</v>
+        <v>4.906359864</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08893431804480872</v>
+        <v>0.08957832743831116</v>
       </c>
       <c r="T46">
-        <v>0.9961736269008942</v>
+        <v>1.011046823055685</v>
       </c>
       <c r="U46">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V46">
         <v>0.28</v>
       </c>
       <c r="W46">
-        <v>0.036216</v>
+        <v>0.037296</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y46">
-        <v>12.92106833649492</v>
+        <v>12.2680859898458</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06605128009107114</v>
+        <v>0.06588910207704941</v>
       </c>
       <c r="C47">
-        <v>12.78781894787871</v>
+        <v>12.58875748620278</v>
       </c>
       <c r="D47">
-        <v>24.14131894787871</v>
+        <v>24.19455748620278</v>
       </c>
       <c r="E47">
-        <v>-7.9465</v>
+        <v>-7.6942</v>
       </c>
       <c r="F47">
-        <v>11.3535</v>
+        <v>11.6058</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5135,28 +5135,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M47">
-        <v>0.5881113</v>
+        <v>0.60118044</v>
       </c>
       <c r="N47">
-        <v>6.6268887</v>
+        <v>6.61381956</v>
       </c>
       <c r="O47">
-        <v>1.855528836</v>
+        <v>1.8518694768</v>
       </c>
       <c r="P47">
-        <v>4.771359864</v>
+        <v>4.7619500832</v>
       </c>
       <c r="Q47">
-        <v>4.906359864</v>
+        <v>4.8969500832</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08957832743831116</v>
+        <v>0.09024618903157297</v>
       </c>
       <c r="T47">
-        <v>1.011046823055685</v>
+        <v>1.02647087832732</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>12.2680859898458</v>
+        <v>12.00138846832741</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06588910207704941</v>
+        <v>0.06572692406302766</v>
       </c>
       <c r="C48">
-        <v>12.58875748620278</v>
+        <v>12.38993135601983</v>
       </c>
       <c r="D48">
-        <v>24.19455748620278</v>
+        <v>24.24803135601983</v>
       </c>
       <c r="E48">
-        <v>-7.6942</v>
+        <v>-7.4419</v>
       </c>
       <c r="F48">
-        <v>11.6058</v>
+        <v>11.8581</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5217,28 +5217,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M48">
-        <v>0.60118044</v>
+        <v>0.61424958</v>
       </c>
       <c r="N48">
-        <v>6.61381956</v>
+        <v>6.600750420000001</v>
       </c>
       <c r="O48">
-        <v>1.8518694768</v>
+        <v>1.8482101176</v>
       </c>
       <c r="P48">
-        <v>4.7619500832</v>
+        <v>4.7525403024</v>
       </c>
       <c r="Q48">
-        <v>4.8969500832</v>
+        <v>4.8875403024</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09024618903157297</v>
+        <v>0.09093925294910879</v>
       </c>
       <c r="T48">
-        <v>1.02647087832732</v>
+        <v>1.042476973420527</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>12.00138846832741</v>
+        <v>11.74603977751194</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06572692406302766</v>
+        <v>0.06556474604900592</v>
       </c>
       <c r="C49">
-        <v>12.38993135601983</v>
+        <v>12.19134212114768</v>
       </c>
       <c r="D49">
-        <v>24.24803135601983</v>
+        <v>24.30174212114768</v>
       </c>
       <c r="E49">
-        <v>-7.4419</v>
+        <v>-7.1896</v>
       </c>
       <c r="F49">
-        <v>11.8581</v>
+        <v>12.1104</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5299,28 +5299,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M49">
-        <v>0.61424958</v>
+        <v>0.62731872</v>
       </c>
       <c r="N49">
-        <v>6.600750420000001</v>
+        <v>6.587681280000001</v>
       </c>
       <c r="O49">
-        <v>1.8482101176</v>
+        <v>1.8445507584</v>
       </c>
       <c r="P49">
-        <v>4.7525403024</v>
+        <v>4.7431305216</v>
       </c>
       <c r="Q49">
-        <v>4.8875403024</v>
+        <v>4.8781305216</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09093925294910879</v>
+        <v>0.09165897317116524</v>
       </c>
       <c r="T49">
-        <v>1.042476973420527</v>
+        <v>1.059098687555779</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>11.74603977751194</v>
+        <v>11.50133061548044</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06556474604900592</v>
+        <v>0.06540256803498418</v>
       </c>
       <c r="C50">
-        <v>12.19134212114768</v>
+        <v>11.99299135929071</v>
       </c>
       <c r="D50">
-        <v>24.30174212114768</v>
+        <v>24.35569135929071</v>
       </c>
       <c r="E50">
-        <v>-7.1896</v>
+        <v>-6.9373</v>
       </c>
       <c r="F50">
-        <v>12.1104</v>
+        <v>12.3627</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5381,28 +5381,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M50">
-        <v>0.62731872</v>
+        <v>0.64038786</v>
       </c>
       <c r="N50">
-        <v>6.587681280000001</v>
+        <v>6.574612140000001</v>
       </c>
       <c r="O50">
-        <v>1.8445507584</v>
+        <v>1.8408913992</v>
       </c>
       <c r="P50">
-        <v>4.7431305216</v>
+        <v>4.733720740800001</v>
       </c>
       <c r="Q50">
-        <v>4.8781305216</v>
+        <v>4.868720740800001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09165897317116524</v>
+        <v>0.09240691771565526</v>
       </c>
       <c r="T50">
-        <v>1.059098687555779</v>
+        <v>1.076372233617905</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>11.50133061548044</v>
+        <v>11.26660958251145</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06540256803498418</v>
+        <v>0.06524039002096245</v>
       </c>
       <c r="C51">
-        <v>11.99299135929071</v>
+        <v>11.79488066219428</v>
       </c>
       <c r="D51">
-        <v>24.35569135929071</v>
+        <v>24.40988066219428</v>
       </c>
       <c r="E51">
-        <v>-6.9373</v>
+        <v>-6.685</v>
       </c>
       <c r="F51">
-        <v>12.3627</v>
+        <v>12.615</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5463,28 +5463,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M51">
-        <v>0.64038786</v>
+        <v>0.653457</v>
       </c>
       <c r="N51">
-        <v>6.574612140000001</v>
+        <v>6.561543</v>
       </c>
       <c r="O51">
-        <v>1.8408913992</v>
+        <v>1.83723204</v>
       </c>
       <c r="P51">
-        <v>4.733720740800001</v>
+        <v>4.72431096</v>
       </c>
       <c r="Q51">
-        <v>4.868720740800001</v>
+        <v>4.85931096</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09240691771565526</v>
+        <v>0.0931847800419249</v>
       </c>
       <c r="T51">
-        <v>1.076372233617905</v>
+        <v>1.094336721522515</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>11.26660958251145</v>
+        <v>11.04127739086122</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06524039002096245</v>
+        <v>0.06507821200694071</v>
       </c>
       <c r="C52">
-        <v>11.79488066219428</v>
+        <v>11.59701163580136</v>
       </c>
       <c r="D52">
-        <v>24.40988066219428</v>
+        <v>24.46431163580136</v>
       </c>
       <c r="E52">
-        <v>-6.685</v>
+        <v>-6.432700000000001</v>
       </c>
       <c r="F52">
-        <v>12.615</v>
+        <v>12.8673</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5545,28 +5545,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M52">
-        <v>0.653457</v>
+        <v>0.66652614</v>
       </c>
       <c r="N52">
-        <v>6.561543</v>
+        <v>6.548473860000001</v>
       </c>
       <c r="O52">
-        <v>1.83723204</v>
+        <v>1.8335726808</v>
       </c>
       <c r="P52">
-        <v>4.72431096</v>
+        <v>4.7149011792</v>
       </c>
       <c r="Q52">
-        <v>4.85931096</v>
+        <v>4.8499011792</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.0931847800419249</v>
+        <v>0.09399439185089942</v>
       </c>
       <c r="T52">
-        <v>1.094336721522515</v>
+        <v>1.113034453831395</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>11.04127739086122</v>
+        <v>10.8247817557463</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06507821200694071</v>
+        <v>0.06491603399291898</v>
       </c>
       <c r="C53">
-        <v>11.59701163580136</v>
+        <v>11.39938590041113</v>
       </c>
       <c r="D53">
-        <v>24.46431163580136</v>
+        <v>24.51898590041113</v>
       </c>
       <c r="E53">
-        <v>-6.432700000000001</v>
+        <v>-6.180400000000001</v>
       </c>
       <c r="F53">
-        <v>12.8673</v>
+        <v>13.1196</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5627,28 +5627,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M53">
-        <v>0.66652614</v>
+        <v>0.67959528</v>
       </c>
       <c r="N53">
-        <v>6.548473860000001</v>
+        <v>6.535404720000001</v>
       </c>
       <c r="O53">
-        <v>1.8335726808</v>
+        <v>1.8299133216</v>
       </c>
       <c r="P53">
-        <v>4.7149011792</v>
+        <v>4.7054913984</v>
       </c>
       <c r="Q53">
-        <v>4.8499011792</v>
+        <v>4.8404913984</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09399439185089942</v>
+        <v>0.09483773748524787</v>
       </c>
       <c r="T53">
-        <v>1.113034453831395</v>
+        <v>1.132511258319812</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>10.8247817557463</v>
+        <v>10.6166128758281</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06491603399291898</v>
+        <v>0.06475385597889724</v>
       </c>
       <c r="C54">
-        <v>11.39938590041113</v>
+        <v>11.20200509083976</v>
       </c>
       <c r="D54">
-        <v>24.51898590041113</v>
+        <v>24.57390509083976</v>
       </c>
       <c r="E54">
-        <v>-6.180400000000001</v>
+        <v>-5.928100000000001</v>
       </c>
       <c r="F54">
-        <v>13.1196</v>
+        <v>13.3719</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5709,28 +5709,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M54">
-        <v>0.67959528</v>
+        <v>0.6926644199999999</v>
       </c>
       <c r="N54">
-        <v>6.535404720000001</v>
+        <v>6.522335580000001</v>
       </c>
       <c r="O54">
-        <v>1.8299133216</v>
+        <v>1.8262539624</v>
       </c>
       <c r="P54">
-        <v>4.7054913984</v>
+        <v>4.696081617600001</v>
       </c>
       <c r="Q54">
-        <v>4.8404913984</v>
+        <v>4.831081617600001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09483773748524787</v>
+        <v>0.09571697016786647</v>
       </c>
       <c r="T54">
-        <v>1.132511258319812</v>
+        <v>1.152816862999226</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>10.6166128758281</v>
+        <v>10.41629942534077</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06475385597889724</v>
+        <v>0.0645916779648755</v>
       </c>
       <c r="C55">
-        <v>11.20200509083976</v>
+        <v>11.00487085658337</v>
       </c>
       <c r="D55">
-        <v>24.57390509083976</v>
+        <v>24.62907085658338</v>
       </c>
       <c r="E55">
-        <v>-5.928100000000001</v>
+        <v>-5.675799999999999</v>
       </c>
       <c r="F55">
-        <v>13.3719</v>
+        <v>13.6242</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5791,28 +5791,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M55">
-        <v>0.6926644199999999</v>
+        <v>0.7057335600000001</v>
       </c>
       <c r="N55">
-        <v>6.522335580000001</v>
+        <v>6.509266440000001</v>
       </c>
       <c r="O55">
-        <v>1.8262539624</v>
+        <v>1.8225946032</v>
       </c>
       <c r="P55">
-        <v>4.696081617600001</v>
+        <v>4.6866718368</v>
       </c>
       <c r="Q55">
-        <v>4.831081617600001</v>
+        <v>4.8216718368</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09571697016786647</v>
+        <v>0.09663443035842501</v>
       </c>
       <c r="T55">
-        <v>1.152816862999226</v>
+        <v>1.174005320056005</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>10.41629942534077</v>
+        <v>10.22340499153817</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0645916779648755</v>
+        <v>0.06442949995085376</v>
       </c>
       <c r="C56">
-        <v>11.00487085658337</v>
+        <v>10.80798486198317</v>
       </c>
       <c r="D56">
-        <v>24.62907085658338</v>
+        <v>24.68448486198317</v>
       </c>
       <c r="E56">
-        <v>-5.675799999999999</v>
+        <v>-5.423499999999999</v>
       </c>
       <c r="F56">
-        <v>13.6242</v>
+        <v>13.8765</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5873,28 +5873,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M56">
-        <v>0.7057335600000001</v>
+        <v>0.7188027000000001</v>
       </c>
       <c r="N56">
-        <v>6.509266440000001</v>
+        <v>6.4961973</v>
       </c>
       <c r="O56">
-        <v>1.8225946032</v>
+        <v>1.818935244</v>
       </c>
       <c r="P56">
-        <v>4.6866718368</v>
+        <v>4.677262056</v>
       </c>
       <c r="Q56">
-        <v>4.8216718368</v>
+        <v>4.812262056</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09663443035842501</v>
+        <v>0.09759266655745281</v>
       </c>
       <c r="T56">
-        <v>1.174005320056005</v>
+        <v>1.196135486315308</v>
       </c>
       <c r="U56">
         <v>0.0518</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>10.22340499153817</v>
+        <v>10.03752490078293</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06442949995085376</v>
+        <v>0.06426732193683202</v>
       </c>
       <c r="C57">
-        <v>10.80798486198317</v>
+        <v>10.61134878639283</v>
       </c>
       <c r="D57">
-        <v>24.68448486198317</v>
+        <v>24.74014878639283</v>
       </c>
       <c r="E57">
-        <v>-5.423499999999999</v>
+        <v>-5.171199999999999</v>
       </c>
       <c r="F57">
-        <v>13.8765</v>
+        <v>14.1288</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5955,28 +5955,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M57">
-        <v>0.7188027000000001</v>
+        <v>0.7318718400000001</v>
       </c>
       <c r="N57">
-        <v>6.4961973</v>
+        <v>6.483128160000001</v>
       </c>
       <c r="O57">
-        <v>1.818935244</v>
+        <v>1.8152758848</v>
       </c>
       <c r="P57">
-        <v>4.677262056</v>
+        <v>4.6678522752</v>
       </c>
       <c r="Q57">
-        <v>4.812262056</v>
+        <v>4.8028522752</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09759266655745281</v>
+        <v>0.0985944589473455</v>
       </c>
       <c r="T57">
-        <v>1.196135486315308</v>
+        <v>1.21927156922276</v>
       </c>
       <c r="U57">
         <v>0.0518</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>10.03752490078293</v>
+        <v>9.858283384697518</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06426732193683202</v>
+        <v>0.06480282392281028</v>
       </c>
       <c r="C58">
-        <v>10.61134878639283</v>
+        <v>10.1761969096203</v>
       </c>
       <c r="D58">
-        <v>24.74014878639283</v>
+        <v>24.5572969096203</v>
       </c>
       <c r="E58">
-        <v>-5.171199999999999</v>
+        <v>-4.918899999999999</v>
       </c>
       <c r="F58">
-        <v>14.1288</v>
+        <v>14.3811</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6037,45 +6037,45 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M58">
-        <v>0.7318718400000001</v>
+        <v>0.7693888500000001</v>
       </c>
       <c r="N58">
-        <v>6.483128160000001</v>
+        <v>6.44561115</v>
       </c>
       <c r="O58">
-        <v>1.8152758848</v>
+        <v>1.804771122</v>
       </c>
       <c r="P58">
-        <v>4.6678522752</v>
+        <v>4.640840028</v>
       </c>
       <c r="Q58">
-        <v>4.8028522752</v>
+        <v>4.775840028</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.0985944589473455</v>
+        <v>0.09964284633211694</v>
       </c>
       <c r="T58">
-        <v>1.21927156922276</v>
+        <v>1.243483749009629</v>
       </c>
       <c r="U58">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V58">
         <v>0.28</v>
       </c>
       <c r="W58">
-        <v>0.037296</v>
+        <v>0.03852</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>9.858283384697518</v>
+        <v>9.377572861889016</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06480282392281028</v>
+        <v>0.06465288590878854</v>
       </c>
       <c r="C59">
-        <v>10.1761969096203</v>
+        <v>9.974821554798577</v>
       </c>
       <c r="D59">
-        <v>24.5572969096203</v>
+        <v>24.60822155479858</v>
       </c>
       <c r="E59">
-        <v>-4.918899999999999</v>
+        <v>-4.666599999999999</v>
       </c>
       <c r="F59">
-        <v>14.3811</v>
+        <v>14.6334</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6119,28 +6119,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M59">
-        <v>0.7693888500000001</v>
+        <v>0.7828869000000001</v>
       </c>
       <c r="N59">
-        <v>6.44561115</v>
+        <v>6.4321131</v>
       </c>
       <c r="O59">
-        <v>1.804771122</v>
+        <v>1.800991668</v>
       </c>
       <c r="P59">
-        <v>4.640840028</v>
+        <v>4.631121432</v>
       </c>
       <c r="Q59">
-        <v>4.775840028</v>
+        <v>4.766121432</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09964284633211694</v>
+        <v>0.100741156925687</v>
       </c>
       <c r="T59">
-        <v>1.243483749009629</v>
+        <v>1.26884888973873</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>9.377572861889016</v>
+        <v>9.215890571166794</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06465288590878854</v>
+        <v>0.06450294789476681</v>
       </c>
       <c r="C60">
-        <v>9.974821554798579</v>
+        <v>9.77365784447964</v>
       </c>
       <c r="D60">
-        <v>24.60822155479858</v>
+        <v>24.65935784447964</v>
       </c>
       <c r="E60">
-        <v>-4.666600000000001</v>
+        <v>-4.414300000000001</v>
       </c>
       <c r="F60">
-        <v>14.6334</v>
+        <v>14.8857</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6201,28 +6201,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M60">
-        <v>0.7828868999999999</v>
+        <v>0.79638495</v>
       </c>
       <c r="N60">
-        <v>6.4321131</v>
+        <v>6.418615050000001</v>
       </c>
       <c r="O60">
-        <v>1.800991668</v>
+        <v>1.797212214</v>
       </c>
       <c r="P60">
-        <v>4.631121432</v>
+        <v>4.621402836</v>
       </c>
       <c r="Q60">
-        <v>4.766121432</v>
+        <v>4.756402835999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.100741156925687</v>
+        <v>0.1018930436457727</v>
       </c>
       <c r="T60">
-        <v>1.26884888973873</v>
+        <v>1.295451354405836</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>9.215890571166794</v>
+        <v>9.059689036062272</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06450294789476681</v>
+        <v>0.06435300988074508</v>
       </c>
       <c r="C61">
-        <v>9.77365784447964</v>
+        <v>9.572707100813227</v>
       </c>
       <c r="D61">
-        <v>24.65935784447964</v>
+        <v>24.71070710081323</v>
       </c>
       <c r="E61">
-        <v>-4.414300000000001</v>
+        <v>-4.162000000000001</v>
       </c>
       <c r="F61">
-        <v>14.8857</v>
+        <v>15.138</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6283,28 +6283,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M61">
-        <v>0.79638495</v>
+        <v>0.809883</v>
       </c>
       <c r="N61">
-        <v>6.418615050000001</v>
+        <v>6.405117000000001</v>
       </c>
       <c r="O61">
-        <v>1.797212214</v>
+        <v>1.79343276</v>
       </c>
       <c r="P61">
-        <v>4.621402836</v>
+        <v>4.611684240000001</v>
       </c>
       <c r="Q61">
-        <v>4.756402835999999</v>
+        <v>4.74668424</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1018930436457727</v>
+        <v>0.1031025247018627</v>
       </c>
       <c r="T61">
-        <v>1.295451354405836</v>
+        <v>1.323383942306297</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>9.059689036062272</v>
+        <v>8.908694218794567</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06435300988074508</v>
+        <v>0.06420307186672333</v>
       </c>
       <c r="C62">
-        <v>9.572707100813227</v>
+        <v>9.37197065698474</v>
       </c>
       <c r="D62">
-        <v>24.71070710081323</v>
+        <v>24.76227065698474</v>
       </c>
       <c r="E62">
-        <v>-4.162000000000001</v>
+        <v>-3.909700000000001</v>
       </c>
       <c r="F62">
-        <v>15.138</v>
+        <v>15.3903</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6365,28 +6365,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M62">
-        <v>0.809883</v>
+        <v>0.8233810499999999</v>
       </c>
       <c r="N62">
-        <v>6.405117000000001</v>
+        <v>6.391618950000001</v>
       </c>
       <c r="O62">
-        <v>1.79343276</v>
+        <v>1.789653306</v>
       </c>
       <c r="P62">
-        <v>4.611684240000001</v>
+        <v>4.601965644</v>
       </c>
       <c r="Q62">
-        <v>4.74668424</v>
+        <v>4.736965644</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1031025247018627</v>
+        <v>0.1043740304274957</v>
       </c>
       <c r="T62">
-        <v>1.323383942306297</v>
+        <v>1.35274897061191</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>8.908694218794567</v>
+        <v>8.762650051273345</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06420307186672333</v>
+        <v>0.06405313385270159</v>
       </c>
       <c r="C63">
-        <v>9.37197065698474</v>
+        <v>9.171449857330613</v>
       </c>
       <c r="D63">
-        <v>24.76227065698474</v>
+        <v>24.81404985733061</v>
       </c>
       <c r="E63">
-        <v>-3.909700000000001</v>
+        <v>-3.657400000000001</v>
       </c>
       <c r="F63">
-        <v>15.3903</v>
+        <v>15.6426</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6447,28 +6447,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M63">
-        <v>0.8233810499999999</v>
+        <v>0.8368791</v>
       </c>
       <c r="N63">
-        <v>6.391618950000001</v>
+        <v>6.378120900000001</v>
       </c>
       <c r="O63">
-        <v>1.789653306</v>
+        <v>1.785873852</v>
       </c>
       <c r="P63">
-        <v>4.601965644</v>
+        <v>4.592247048000001</v>
       </c>
       <c r="Q63">
-        <v>4.736965644</v>
+        <v>4.727247048000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1043740304274957</v>
+        <v>0.1057124575071094</v>
       </c>
       <c r="T63">
-        <v>1.35274897061191</v>
+        <v>1.383659526723082</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>8.762650051273345</v>
+        <v>8.621316985930227</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06405313385270159</v>
+        <v>0.06390319583867984</v>
       </c>
       <c r="C64">
-        <v>9.171449857330613</v>
+        <v>8.971146057455158</v>
       </c>
       <c r="D64">
-        <v>24.81404985733061</v>
+        <v>24.86604605745516</v>
       </c>
       <c r="E64">
-        <v>-3.657400000000001</v>
+        <v>-3.405100000000001</v>
       </c>
       <c r="F64">
-        <v>15.6426</v>
+        <v>15.8949</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6529,28 +6529,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M64">
-        <v>0.8368791</v>
+        <v>0.85037715</v>
       </c>
       <c r="N64">
-        <v>6.378120900000001</v>
+        <v>6.364622850000001</v>
       </c>
       <c r="O64">
-        <v>1.785873852</v>
+        <v>1.782094398</v>
       </c>
       <c r="P64">
-        <v>4.592247048000001</v>
+        <v>4.582528452</v>
       </c>
       <c r="Q64">
-        <v>4.727247048000001</v>
+        <v>4.717528452</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1057124575071094</v>
+        <v>0.107123231996432</v>
       </c>
       <c r="T64">
-        <v>1.383659526723082</v>
+        <v>1.416240923705128</v>
       </c>
       <c r="U64">
         <v>0.0535</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>8.621316985930227</v>
+        <v>8.484470684566254</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.06390319583867984</v>
+        <v>0.06375325782465811</v>
       </c>
       <c r="C65">
-        <v>8.971146057455158</v>
+        <v>8.771060624348848</v>
       </c>
       <c r="D65">
-        <v>24.86604605745516</v>
+        <v>24.91826062434885</v>
       </c>
       <c r="E65">
-        <v>-3.405100000000001</v>
+        <v>-3.152799999999999</v>
       </c>
       <c r="F65">
-        <v>15.8949</v>
+        <v>16.1472</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6611,28 +6611,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M65">
-        <v>0.85037715</v>
+        <v>0.8638752000000001</v>
       </c>
       <c r="N65">
-        <v>6.364622850000001</v>
+        <v>6.351124800000001</v>
       </c>
       <c r="O65">
-        <v>1.782094398</v>
+        <v>1.778314944</v>
       </c>
       <c r="P65">
-        <v>4.582528452</v>
+        <v>4.572809856000001</v>
       </c>
       <c r="Q65">
-        <v>4.717528452</v>
+        <v>4.707809856000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.107123231996432</v>
+        <v>0.1086123828462726</v>
       </c>
       <c r="T65">
-        <v>1.416240923705128</v>
+        <v>1.450632398297288</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>8.484470684566254</v>
+        <v>8.351900830119906</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.06375325782465811</v>
+        <v>0.06360331981063637</v>
       </c>
       <c r="C66">
-        <v>8.771060624348848</v>
+        <v>8.571194936508164</v>
       </c>
       <c r="D66">
-        <v>24.91826062434885</v>
+        <v>24.97069493650816</v>
       </c>
       <c r="E66">
-        <v>-3.152799999999999</v>
+        <v>-2.900500000000001</v>
       </c>
       <c r="F66">
-        <v>16.1472</v>
+        <v>16.3995</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6693,28 +6693,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M66">
-        <v>0.8638752000000001</v>
+        <v>0.87737325</v>
       </c>
       <c r="N66">
-        <v>6.351124800000001</v>
+        <v>6.337626750000001</v>
       </c>
       <c r="O66">
-        <v>1.778314944</v>
+        <v>1.774535490000001</v>
       </c>
       <c r="P66">
-        <v>4.572809856000001</v>
+        <v>4.56309126</v>
       </c>
       <c r="Q66">
-        <v>4.707809856000001</v>
+        <v>4.69809126</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1086123828462726</v>
+        <v>0.1101866280303896</v>
       </c>
       <c r="T66">
-        <v>1.450632398297288</v>
+        <v>1.486989100008999</v>
       </c>
       <c r="U66">
         <v>0.0535</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>8.351900830119906</v>
+        <v>8.223410048118062</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.06360331981063637</v>
+        <v>0.06345338179661464</v>
       </c>
       <c r="C67">
-        <v>8.571194936508164</v>
+        <v>8.371550384056828</v>
       </c>
       <c r="D67">
-        <v>24.97069493650816</v>
+        <v>25.02335038405683</v>
       </c>
       <c r="E67">
-        <v>-2.900500000000001</v>
+        <v>-2.648199999999999</v>
       </c>
       <c r="F67">
-        <v>16.3995</v>
+        <v>16.6518</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6775,28 +6775,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M67">
-        <v>0.87737325</v>
+        <v>0.8908713</v>
       </c>
       <c r="N67">
-        <v>6.337626750000001</v>
+        <v>6.324128700000001</v>
       </c>
       <c r="O67">
-        <v>1.774535490000001</v>
+        <v>1.770756036000001</v>
       </c>
       <c r="P67">
-        <v>4.56309126</v>
+        <v>4.553372664</v>
       </c>
       <c r="Q67">
-        <v>4.69809126</v>
+        <v>4.688372664</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1101866280303896</v>
+        <v>0.111853475872396</v>
       </c>
       <c r="T67">
-        <v>1.486989100008999</v>
+        <v>1.525484431233164</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>8.223410048118062</v>
+        <v>8.09881292617688</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06345338179661464</v>
+        <v>0.06330344378259289</v>
       </c>
       <c r="C68">
-        <v>8.371550384056828</v>
+        <v>8.172128368868737</v>
       </c>
       <c r="D68">
-        <v>25.02335038405683</v>
+        <v>25.07622836886874</v>
       </c>
       <c r="E68">
-        <v>-2.648199999999999</v>
+        <v>-2.395900000000001</v>
       </c>
       <c r="F68">
-        <v>16.6518</v>
+        <v>16.9041</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6857,28 +6857,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M68">
-        <v>0.8908713</v>
+        <v>0.90436935</v>
       </c>
       <c r="N68">
-        <v>6.324128700000001</v>
+        <v>6.310630650000001</v>
       </c>
       <c r="O68">
-        <v>1.770756036000001</v>
+        <v>1.766976582000001</v>
       </c>
       <c r="P68">
-        <v>4.553372664</v>
+        <v>4.543654068</v>
       </c>
       <c r="Q68">
-        <v>4.688372664</v>
+        <v>4.678654068</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.111853475872396</v>
+        <v>0.1136213447957361</v>
       </c>
       <c r="T68">
-        <v>1.525484431233164</v>
+        <v>1.566312812834551</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>8.09881292617688</v>
+        <v>7.977935121308569</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.06330344378259289</v>
+        <v>0.06315350576857116</v>
       </c>
       <c r="C69">
-        <v>8.172128368868737</v>
+        <v>7.972930304692298</v>
       </c>
       <c r="D69">
-        <v>25.07622836886874</v>
+        <v>25.1293303046923</v>
       </c>
       <c r="E69">
-        <v>-2.395900000000001</v>
+        <v>-2.143599999999999</v>
       </c>
       <c r="F69">
-        <v>16.9041</v>
+        <v>17.1564</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6939,28 +6939,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M69">
-        <v>0.90436935</v>
+        <v>0.9178674000000001</v>
       </c>
       <c r="N69">
-        <v>6.310630650000001</v>
+        <v>6.2971326</v>
       </c>
       <c r="O69">
-        <v>1.766976582000001</v>
+        <v>1.763197128</v>
       </c>
       <c r="P69">
-        <v>4.543654068</v>
+        <v>4.533935472</v>
       </c>
       <c r="Q69">
-        <v>4.678654068</v>
+        <v>4.668935471999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1136213447957361</v>
+        <v>0.1154997055267849</v>
       </c>
       <c r="T69">
-        <v>1.566312812834551</v>
+        <v>1.609692968286025</v>
       </c>
       <c r="U69">
         <v>0.0535</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>7.977935121308569</v>
+        <v>7.860612545995205</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.06315350576857116</v>
+        <v>0.06300356775454943</v>
       </c>
       <c r="C70">
-        <v>7.972930304692298</v>
+        <v>7.773957617276498</v>
       </c>
       <c r="D70">
-        <v>25.1293303046923</v>
+        <v>25.1826576172765</v>
       </c>
       <c r="E70">
-        <v>-2.143599999999999</v>
+        <v>-1.891299999999998</v>
       </c>
       <c r="F70">
-        <v>17.1564</v>
+        <v>17.4087</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7021,28 +7021,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M70">
-        <v>0.9178674000000001</v>
+        <v>0.9313654500000002</v>
       </c>
       <c r="N70">
-        <v>6.2971326</v>
+        <v>6.28363455</v>
       </c>
       <c r="O70">
-        <v>1.763197128</v>
+        <v>1.759417674</v>
       </c>
       <c r="P70">
-        <v>4.533935472</v>
+        <v>4.524216876000001</v>
       </c>
       <c r="Q70">
-        <v>4.668935471999999</v>
+        <v>4.659216876</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1154997055267849</v>
+        <v>0.1174992508211272</v>
       </c>
       <c r="T70">
-        <v>1.609692968286025</v>
+        <v>1.655871843444046</v>
       </c>
       <c r="U70">
         <v>0.0535</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>7.860612545995205</v>
+        <v>7.746690625038753</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.06300356775454943</v>
+        <v>0.06285362974052769</v>
       </c>
       <c r="C71">
-        <v>7.773957617276498</v>
+        <v>7.575211744498457</v>
       </c>
       <c r="D71">
-        <v>25.1826576172765</v>
+        <v>25.23621174449846</v>
       </c>
       <c r="E71">
-        <v>-1.891299999999998</v>
+        <v>-1.638999999999999</v>
       </c>
       <c r="F71">
-        <v>17.4087</v>
+        <v>17.661</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7103,28 +7103,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M71">
-        <v>0.9313654500000002</v>
+        <v>0.9448635000000001</v>
       </c>
       <c r="N71">
-        <v>6.28363455</v>
+        <v>6.2701365</v>
       </c>
       <c r="O71">
-        <v>1.759417674</v>
+        <v>1.75563822</v>
       </c>
       <c r="P71">
-        <v>4.524216876000001</v>
+        <v>4.51449828</v>
       </c>
       <c r="Q71">
-        <v>4.659216876</v>
+        <v>4.64949828</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1174992508211272</v>
+        <v>0.1196320991350923</v>
       </c>
       <c r="T71">
-        <v>1.655871843444046</v>
+        <v>1.705129310279268</v>
       </c>
       <c r="U71">
         <v>0.0535</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>7.746690625038753</v>
+        <v>7.636023616109629</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.06285362974052769</v>
+        <v>0.06311265172650594</v>
       </c>
       <c r="C72">
-        <v>7.575211744498457</v>
+        <v>7.230538152375033</v>
       </c>
       <c r="D72">
-        <v>25.23621174449846</v>
+        <v>25.14383815237504</v>
       </c>
       <c r="E72">
-        <v>-1.638999999999999</v>
+        <v>-1.386699999999998</v>
       </c>
       <c r="F72">
-        <v>17.661</v>
+        <v>17.9133</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7185,45 +7185,45 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M72">
-        <v>0.9448635000000001</v>
+        <v>0.9726921900000002</v>
       </c>
       <c r="N72">
-        <v>6.2701365</v>
+        <v>6.242307810000001</v>
       </c>
       <c r="O72">
-        <v>1.75563822</v>
+        <v>1.7478461868</v>
       </c>
       <c r="P72">
-        <v>4.51449828</v>
+        <v>4.4944616232</v>
       </c>
       <c r="Q72">
-        <v>4.64949828</v>
+        <v>4.6294616232</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1196320991350923</v>
+        <v>0.1219120404362274</v>
       </c>
       <c r="T72">
-        <v>1.705129310279268</v>
+        <v>1.757783843792781</v>
       </c>
       <c r="U72">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V72">
         <v>0.28</v>
       </c>
       <c r="W72">
-        <v>0.03852</v>
+        <v>0.039096</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y72">
-        <v>7.636023616109629</v>
+        <v>7.417557243879998</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.06311265172650596</v>
+        <v>0.06296847371248421</v>
       </c>
       <c r="C73">
-        <v>7.230538152375033</v>
+        <v>7.02957195145531</v>
       </c>
       <c r="D73">
-        <v>25.14383815237503</v>
+        <v>25.19517195145531</v>
       </c>
       <c r="E73">
-        <v>-1.386700000000001</v>
+        <v>-1.134399999999999</v>
       </c>
       <c r="F73">
-        <v>17.9133</v>
+        <v>18.1656</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7267,28 +7267,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M73">
-        <v>0.97269219</v>
+        <v>0.9863920800000001</v>
       </c>
       <c r="N73">
-        <v>6.242307810000001</v>
+        <v>6.228607920000001</v>
       </c>
       <c r="O73">
-        <v>1.7478461868</v>
+        <v>1.7440102176</v>
       </c>
       <c r="P73">
-        <v>4.4944616232</v>
+        <v>4.4845977024</v>
       </c>
       <c r="Q73">
-        <v>4.6294616232</v>
+        <v>4.6195977024</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1219120404362274</v>
+        <v>0.1243548346874436</v>
       </c>
       <c r="T73">
-        <v>1.757783843792781</v>
+        <v>1.814199415414402</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>7.417557243879999</v>
+        <v>7.314535615492777</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.06296847371248421</v>
+        <v>0.06282429569846247</v>
       </c>
       <c r="C74">
-        <v>7.02957195145531</v>
+        <v>6.82881578608173</v>
       </c>
       <c r="D74">
-        <v>25.19517195145531</v>
+        <v>25.24671578608173</v>
       </c>
       <c r="E74">
-        <v>-1.134399999999999</v>
+        <v>-0.8821000000000012</v>
       </c>
       <c r="F74">
-        <v>18.1656</v>
+        <v>18.4179</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7349,28 +7349,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M74">
-        <v>0.9863920800000001</v>
+        <v>1.00009197</v>
       </c>
       <c r="N74">
-        <v>6.228607920000001</v>
+        <v>6.214908030000001</v>
       </c>
       <c r="O74">
-        <v>1.7440102176</v>
+        <v>1.7401742484</v>
       </c>
       <c r="P74">
-        <v>4.4845977024</v>
+        <v>4.4747337816</v>
       </c>
       <c r="Q74">
-        <v>4.6195977024</v>
+        <v>4.6097337816</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1243548346874436</v>
+        <v>0.1269785766609721</v>
       </c>
       <c r="T74">
-        <v>1.814199415414402</v>
+        <v>1.874793918267254</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>7.314535615492777</v>
+        <v>7.214336497472329</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.06282429569846247</v>
+        <v>0.06268011768444073</v>
       </c>
       <c r="C75">
-        <v>6.82881578608173</v>
+        <v>6.628270947957791</v>
       </c>
       <c r="D75">
-        <v>25.24671578608173</v>
+        <v>25.29847094795779</v>
       </c>
       <c r="E75">
-        <v>-0.8821000000000012</v>
+        <v>-0.6297999999999995</v>
       </c>
       <c r="F75">
-        <v>18.4179</v>
+        <v>18.6702</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7431,28 +7431,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M75">
-        <v>1.00009197</v>
+        <v>1.01379186</v>
       </c>
       <c r="N75">
-        <v>6.214908030000001</v>
+        <v>6.20120814</v>
       </c>
       <c r="O75">
-        <v>1.7401742484</v>
+        <v>1.7363382792</v>
       </c>
       <c r="P75">
-        <v>4.4747337816</v>
+        <v>4.4648698608</v>
       </c>
       <c r="Q75">
-        <v>4.6097337816</v>
+        <v>4.5998698608</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1269785766609721</v>
+        <v>0.1298041449401567</v>
       </c>
       <c r="T75">
-        <v>1.874793918267254</v>
+        <v>1.940049536724172</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>7.214336497472329</v>
+        <v>7.116845463722702</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.06268011768444073</v>
+        <v>0.062535939670419</v>
       </c>
       <c r="C76">
-        <v>6.628270947957791</v>
+        <v>6.427938739400599</v>
       </c>
       <c r="D76">
-        <v>25.29847094795779</v>
+        <v>25.3504387394006</v>
       </c>
       <c r="E76">
-        <v>-0.6297999999999995</v>
+        <v>-0.3775000000000013</v>
       </c>
       <c r="F76">
-        <v>18.6702</v>
+        <v>18.9225</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7513,28 +7513,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M76">
-        <v>1.01379186</v>
+        <v>1.02749175</v>
       </c>
       <c r="N76">
-        <v>6.20120814</v>
+        <v>6.18750825</v>
       </c>
       <c r="O76">
-        <v>1.7363382792</v>
+        <v>1.73250231</v>
       </c>
       <c r="P76">
-        <v>4.4648698608</v>
+        <v>4.45500594</v>
       </c>
       <c r="Q76">
-        <v>4.5998698608</v>
+        <v>4.59000594</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1298041449401567</v>
+        <v>0.132855758681676</v>
       </c>
       <c r="T76">
-        <v>1.940049536724172</v>
+        <v>2.010525604657644</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>7.116845463722702</v>
+        <v>7.021954190873066</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.062535939670419</v>
+        <v>0.06239176165639726</v>
       </c>
       <c r="C77">
-        <v>6.427938739400599</v>
+        <v>6.227820473450087</v>
       </c>
       <c r="D77">
-        <v>25.3504387394006</v>
+        <v>25.40262047345009</v>
       </c>
       <c r="E77">
-        <v>-0.3775000000000013</v>
+        <v>-0.1251999999999995</v>
       </c>
       <c r="F77">
-        <v>18.9225</v>
+        <v>19.1748</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7595,28 +7595,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M77">
-        <v>1.02749175</v>
+        <v>1.04119164</v>
       </c>
       <c r="N77">
-        <v>6.18750825</v>
+        <v>6.173808360000001</v>
       </c>
       <c r="O77">
-        <v>1.73250231</v>
+        <v>1.7286663408</v>
       </c>
       <c r="P77">
-        <v>4.45500594</v>
+        <v>4.4451420192</v>
       </c>
       <c r="Q77">
-        <v>4.59000594</v>
+        <v>4.5801420192</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.132855758681676</v>
+        <v>0.1361616735683219</v>
       </c>
       <c r="T77">
-        <v>2.010525604657644</v>
+        <v>2.086874678252238</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>7.021954190873066</v>
+        <v>6.929560056782631</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.06239176165639726</v>
+        <v>0.06224758364237552</v>
       </c>
       <c r="C78">
-        <v>6.227820473450087</v>
+        <v>6.02791747397962</v>
       </c>
       <c r="D78">
-        <v>25.40262047345009</v>
+        <v>25.45501747397962</v>
       </c>
       <c r="E78">
-        <v>-0.1251999999999995</v>
+        <v>0.1270999999999987</v>
       </c>
       <c r="F78">
-        <v>19.1748</v>
+        <v>19.4271</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7677,28 +7677,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M78">
-        <v>1.04119164</v>
+        <v>1.05489153</v>
       </c>
       <c r="N78">
-        <v>6.173808360000001</v>
+        <v>6.160108470000001</v>
       </c>
       <c r="O78">
-        <v>1.7286663408</v>
+        <v>1.7248303716</v>
       </c>
       <c r="P78">
-        <v>4.4451420192</v>
+        <v>4.4352780984</v>
       </c>
       <c r="Q78">
-        <v>4.5801420192</v>
+        <v>4.5702780984</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1361616735683219</v>
+        <v>0.1397550593146762</v>
       </c>
       <c r="T78">
-        <v>2.086874678252238</v>
+        <v>2.169862801724623</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>6.929560056782631</v>
+        <v>6.839565770330909</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.06224758364237552</v>
+        <v>0.06210340562835377</v>
       </c>
       <c r="C79">
-        <v>6.02791747397962</v>
+        <v>5.828231075807953</v>
       </c>
       <c r="D79">
-        <v>25.45501747397962</v>
+        <v>25.50763107580795</v>
       </c>
       <c r="E79">
-        <v>0.1270999999999987</v>
+        <v>0.3794000000000004</v>
       </c>
       <c r="F79">
-        <v>19.4271</v>
+        <v>19.6794</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7759,28 +7759,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M79">
-        <v>1.05489153</v>
+        <v>1.06859142</v>
       </c>
       <c r="N79">
-        <v>6.160108470000001</v>
+        <v>6.146408580000001</v>
       </c>
       <c r="O79">
-        <v>1.7248303716</v>
+        <v>1.7209944024</v>
       </c>
       <c r="P79">
-        <v>4.4352780984</v>
+        <v>4.4254141776</v>
       </c>
       <c r="Q79">
-        <v>4.5702780984</v>
+        <v>4.5604141776</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1397550593146762</v>
+        <v>0.1436751164925172</v>
       </c>
       <c r="T79">
-        <v>2.169862801724623</v>
+        <v>2.260395300058134</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>6.839565770330909</v>
+        <v>6.751879029685639</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.06210340562835377</v>
+        <v>0.06195922761433204</v>
       </c>
       <c r="C80">
-        <v>5.828231075807953</v>
+        <v>5.628762624812552</v>
       </c>
       <c r="D80">
-        <v>25.50763107580795</v>
+        <v>25.56046262481255</v>
       </c>
       <c r="E80">
-        <v>0.3794000000000004</v>
+        <v>0.6317000000000021</v>
       </c>
       <c r="F80">
-        <v>19.6794</v>
+        <v>19.9317</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7841,28 +7841,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M80">
-        <v>1.06859142</v>
+        <v>1.08229131</v>
       </c>
       <c r="N80">
-        <v>6.146408580000001</v>
+        <v>6.13270869</v>
       </c>
       <c r="O80">
-        <v>1.7209944024</v>
+        <v>1.7171584332</v>
       </c>
       <c r="P80">
-        <v>4.4254141776</v>
+        <v>4.4155502568</v>
       </c>
       <c r="Q80">
-        <v>4.5604141776</v>
+        <v>4.550550256799999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1436751164925172</v>
+        <v>0.1479685124492002</v>
       </c>
       <c r="T80">
-        <v>2.260395300058134</v>
+        <v>2.359549941090074</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>6.751879029685639</v>
+        <v>6.666412206525061</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.06195922761433204</v>
+        <v>0.0618150496003103</v>
       </c>
       <c r="C81">
-        <v>5.628762624812552</v>
+        <v>5.429513478044434</v>
       </c>
       <c r="D81">
-        <v>25.56046262481255</v>
+        <v>25.61351347804444</v>
       </c>
       <c r="E81">
-        <v>0.6317000000000021</v>
+        <v>0.8840000000000003</v>
       </c>
       <c r="F81">
-        <v>19.9317</v>
+        <v>20.184</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7923,28 +7923,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M81">
-        <v>1.08229131</v>
+        <v>1.0959912</v>
       </c>
       <c r="N81">
-        <v>6.13270869</v>
+        <v>6.1190088</v>
       </c>
       <c r="O81">
-        <v>1.7171584332</v>
+        <v>1.713322464</v>
       </c>
       <c r="P81">
-        <v>4.4155502568</v>
+        <v>4.405686336</v>
       </c>
       <c r="Q81">
-        <v>4.550550256799999</v>
+        <v>4.540686336</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1479685124492002</v>
+        <v>0.1526912480015515</v>
       </c>
       <c r="T81">
-        <v>2.359549941090074</v>
+        <v>2.468620046225209</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>6.666412206525061</v>
+        <v>6.583082053943499</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0618150496003103</v>
+        <v>0.06167087158628856</v>
       </c>
       <c r="C82">
-        <v>5.429513478044434</v>
+        <v>5.230485003844251</v>
       </c>
       <c r="D82">
-        <v>25.61351347804444</v>
+        <v>25.66678500384425</v>
       </c>
       <c r="E82">
-        <v>0.8840000000000003</v>
+        <v>1.136300000000002</v>
       </c>
       <c r="F82">
-        <v>20.184</v>
+        <v>20.4363</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8005,28 +8005,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M82">
-        <v>1.0959912</v>
+        <v>1.10969109</v>
       </c>
       <c r="N82">
-        <v>6.1190088</v>
+        <v>6.105308910000001</v>
       </c>
       <c r="O82">
-        <v>1.713322464</v>
+        <v>1.7094864948</v>
       </c>
       <c r="P82">
-        <v>4.405686336</v>
+        <v>4.3958224152</v>
       </c>
       <c r="Q82">
-        <v>4.540686336</v>
+        <v>4.5308224152</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1526912480015515</v>
+        <v>0.1579111136120451</v>
       </c>
       <c r="T82">
-        <v>2.468620046225209</v>
+        <v>2.589171215058778</v>
       </c>
       <c r="U82">
         <v>0.0543</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>6.583082053943499</v>
+        <v>6.501809435993579</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.06167087158628856</v>
+        <v>0.06152669357226682</v>
       </c>
       <c r="C83">
-        <v>5.230485003844251</v>
+        <v>5.031678581960037</v>
       </c>
       <c r="D83">
-        <v>25.66678500384425</v>
+        <v>25.72027858196004</v>
       </c>
       <c r="E83">
-        <v>1.136300000000002</v>
+        <v>1.3886</v>
       </c>
       <c r="F83">
-        <v>20.4363</v>
+        <v>20.6886</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8087,28 +8087,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M83">
-        <v>1.10969109</v>
+        <v>1.12339098</v>
       </c>
       <c r="N83">
-        <v>6.105308910000001</v>
+        <v>6.091609020000001</v>
       </c>
       <c r="O83">
-        <v>1.7094864948</v>
+        <v>1.7056505256</v>
       </c>
       <c r="P83">
-        <v>4.3958224152</v>
+        <v>4.385958494400001</v>
       </c>
       <c r="Q83">
-        <v>4.5308224152</v>
+        <v>4.5209584944</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1579111136120451</v>
+        <v>0.1637109642903713</v>
       </c>
       <c r="T83">
-        <v>2.589171215058778</v>
+        <v>2.723116958207189</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>6.501809435993579</v>
+        <v>6.422519077018047</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.06152669357226682</v>
+        <v>0.06138251555824509</v>
       </c>
       <c r="C84">
-        <v>5.031678581960037</v>
+        <v>4.833095603666266</v>
       </c>
       <c r="D84">
-        <v>25.72027858196004</v>
+        <v>25.77399560366627</v>
       </c>
       <c r="E84">
-        <v>1.3886</v>
+        <v>1.640900000000002</v>
       </c>
       <c r="F84">
-        <v>20.6886</v>
+        <v>20.9409</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8169,28 +8169,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M84">
-        <v>1.12339098</v>
+        <v>1.13709087</v>
       </c>
       <c r="N84">
-        <v>6.091609020000001</v>
+        <v>6.07790913</v>
       </c>
       <c r="O84">
-        <v>1.7056505256</v>
+        <v>1.7018145564</v>
       </c>
       <c r="P84">
-        <v>4.385958494400001</v>
+        <v>4.3760945736</v>
       </c>
       <c r="Q84">
-        <v>4.5209584944</v>
+        <v>4.511094573599999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1637109642903713</v>
+        <v>0.1701931503426183</v>
       </c>
       <c r="T84">
-        <v>2.723116958207189</v>
+        <v>2.872821024078943</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>6.422519077018047</v>
+        <v>6.345139329102166</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.06138251555824509</v>
+        <v>0.06123833754422336</v>
       </c>
       <c r="C85">
-        <v>4.833095603666266</v>
+        <v>4.634737471884499</v>
       </c>
       <c r="D85">
-        <v>25.77399560366627</v>
+        <v>25.8279374718845</v>
       </c>
       <c r="E85">
-        <v>1.640900000000002</v>
+        <v>1.8932</v>
       </c>
       <c r="F85">
-        <v>20.9409</v>
+        <v>21.1932</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8251,28 +8251,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M85">
-        <v>1.13709087</v>
+        <v>1.15079076</v>
       </c>
       <c r="N85">
-        <v>6.07790913</v>
+        <v>6.06420924</v>
       </c>
       <c r="O85">
-        <v>1.7018145564</v>
+        <v>1.6979785872</v>
       </c>
       <c r="P85">
-        <v>4.3760945736</v>
+        <v>4.366230652800001</v>
       </c>
       <c r="Q85">
-        <v>4.511094573599999</v>
+        <v>4.5012306528</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1701931503426183</v>
+        <v>0.177485609651396</v>
       </c>
       <c r="T85">
-        <v>2.872821024078943</v>
+        <v>3.041238098184666</v>
       </c>
       <c r="U85">
         <v>0.0543</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>6.345139329102166</v>
+        <v>6.269601956136666</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.06123833754422335</v>
+        <v>0.06109415953020161</v>
       </c>
       <c r="C86">
-        <v>4.634737471884499</v>
+        <v>4.436605601305516</v>
       </c>
       <c r="D86">
-        <v>25.8279374718845</v>
+        <v>25.88210560130551</v>
       </c>
       <c r="E86">
-        <v>1.8932</v>
+        <v>2.145499999999998</v>
       </c>
       <c r="F86">
-        <v>21.1932</v>
+        <v>21.4455</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8333,28 +8333,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M86">
-        <v>1.15079076</v>
+        <v>1.16449065</v>
       </c>
       <c r="N86">
-        <v>6.06420924</v>
+        <v>6.05050935</v>
       </c>
       <c r="O86">
-        <v>1.6979785872</v>
+        <v>1.694142618</v>
       </c>
       <c r="P86">
-        <v>4.366230652800001</v>
+        <v>4.356366732</v>
       </c>
       <c r="Q86">
-        <v>4.5012306528</v>
+        <v>4.491366731999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.177485609651396</v>
+        <v>0.1857503968680107</v>
       </c>
       <c r="T86">
-        <v>3.041238098184664</v>
+        <v>3.232110782171149</v>
       </c>
       <c r="U86">
         <v>0.0543</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>6.269601956136666</v>
+        <v>6.195841933123293</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.06109415953020161</v>
+        <v>0.06094998151617988</v>
       </c>
       <c r="C87">
-        <v>4.436605601305516</v>
+        <v>4.238701418512974</v>
       </c>
       <c r="D87">
-        <v>25.88210560130551</v>
+        <v>25.93650141851298</v>
       </c>
       <c r="E87">
-        <v>2.145499999999998</v>
+        <v>2.3978</v>
       </c>
       <c r="F87">
-        <v>21.4455</v>
+        <v>21.6978</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8415,28 +8415,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M87">
-        <v>1.16449065</v>
+        <v>1.17819054</v>
       </c>
       <c r="N87">
-        <v>6.05050935</v>
+        <v>6.036809460000001</v>
       </c>
       <c r="O87">
-        <v>1.694142618</v>
+        <v>1.6903066488</v>
       </c>
       <c r="P87">
-        <v>4.356366732</v>
+        <v>4.346502811200001</v>
       </c>
       <c r="Q87">
-        <v>4.491366731999999</v>
+        <v>4.4815028112</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1857503968680107</v>
+        <v>0.1951958679727134</v>
       </c>
       <c r="T87">
-        <v>3.232110782171149</v>
+        <v>3.450250992441418</v>
       </c>
       <c r="U87">
         <v>0.0543</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>6.195841933123293</v>
+        <v>6.123797259482324</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.06094998151617988</v>
+        <v>0.06143220350215813</v>
       </c>
       <c r="C88">
-        <v>4.238701418512974</v>
+        <v>3.805357832420906</v>
       </c>
       <c r="D88">
-        <v>25.93650141851298</v>
+        <v>25.75545783242091</v>
       </c>
       <c r="E88">
-        <v>2.3978</v>
+        <v>2.650099999999998</v>
       </c>
       <c r="F88">
-        <v>21.6978</v>
+        <v>21.9501</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8497,45 +8497,45 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M88">
-        <v>1.17819054</v>
+        <v>1.21384053</v>
       </c>
       <c r="N88">
-        <v>6.036809460000001</v>
+        <v>6.001159470000001</v>
       </c>
       <c r="O88">
-        <v>1.6903066488</v>
+        <v>1.680324651600001</v>
       </c>
       <c r="P88">
-        <v>4.346502811200001</v>
+        <v>4.320834818400001</v>
       </c>
       <c r="Q88">
-        <v>4.4815028112</v>
+        <v>4.455834818400001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1951958679727134</v>
+        <v>0.2060944884781395</v>
       </c>
       <c r="T88">
-        <v>3.450250992441418</v>
+        <v>3.701951235060958</v>
       </c>
       <c r="U88">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V88">
         <v>0.28</v>
       </c>
       <c r="W88">
-        <v>0.039096</v>
+        <v>0.039816</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y88">
-        <v>6.123797259482324</v>
+        <v>5.943943888576534</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.06143220350215813</v>
+        <v>0.0612952254881364</v>
       </c>
       <c r="C89">
-        <v>3.805357832420906</v>
+        <v>3.604226822996758</v>
       </c>
       <c r="D89">
-        <v>25.75545783242091</v>
+        <v>25.80662682299676</v>
       </c>
       <c r="E89">
-        <v>2.650099999999998</v>
+        <v>2.9024</v>
       </c>
       <c r="F89">
-        <v>21.9501</v>
+        <v>22.2024</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8579,28 +8579,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M89">
-        <v>1.21384053</v>
+        <v>1.22779272</v>
       </c>
       <c r="N89">
-        <v>6.001159470000001</v>
+        <v>5.987207280000001</v>
       </c>
       <c r="O89">
-        <v>1.680324651600001</v>
+        <v>1.6764180384</v>
       </c>
       <c r="P89">
-        <v>4.320834818400001</v>
+        <v>4.3107892416</v>
       </c>
       <c r="Q89">
-        <v>4.455834818400001</v>
+        <v>4.4457892416</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2060944884781395</v>
+        <v>0.21880954573447</v>
       </c>
       <c r="T89">
-        <v>3.701951235060958</v>
+        <v>3.99560151811709</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.943943888576534</v>
+        <v>5.876399071660891</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0612952254881364</v>
+        <v>0.06115824747411466</v>
       </c>
       <c r="C90">
-        <v>3.604226822996758</v>
+        <v>3.403299535652817</v>
       </c>
       <c r="D90">
-        <v>25.80662682299676</v>
+        <v>25.85799953565282</v>
       </c>
       <c r="E90">
-        <v>2.9024</v>
+        <v>3.154699999999998</v>
       </c>
       <c r="F90">
-        <v>22.2024</v>
+        <v>22.4547</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8661,28 +8661,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M90">
-        <v>1.22779272</v>
+        <v>1.24174491</v>
       </c>
       <c r="N90">
-        <v>5.987207280000001</v>
+        <v>5.97325509</v>
       </c>
       <c r="O90">
-        <v>1.6764180384</v>
+        <v>1.6725114252</v>
       </c>
       <c r="P90">
-        <v>4.3107892416</v>
+        <v>4.300743664800001</v>
       </c>
       <c r="Q90">
-        <v>4.4457892416</v>
+        <v>4.4357436648</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.21880954573447</v>
+        <v>0.2338364315828606</v>
       </c>
       <c r="T90">
-        <v>3.99560151811709</v>
+        <v>4.342642761728881</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.876399071660891</v>
+        <v>5.810372115799533</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.06115824747411466</v>
+        <v>0.06102126946009291</v>
       </c>
       <c r="C91">
-        <v>3.403299535652817</v>
+        <v>3.202577189451716</v>
       </c>
       <c r="D91">
-        <v>25.85799953565282</v>
+        <v>25.90957718945172</v>
       </c>
       <c r="E91">
-        <v>3.154699999999998</v>
+        <v>3.407</v>
       </c>
       <c r="F91">
-        <v>22.4547</v>
+        <v>22.707</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8743,28 +8743,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M91">
-        <v>1.24174491</v>
+        <v>1.2556971</v>
       </c>
       <c r="N91">
-        <v>5.97325509</v>
+        <v>5.959302900000001</v>
       </c>
       <c r="O91">
-        <v>1.6725114252</v>
+        <v>1.668604812</v>
       </c>
       <c r="P91">
-        <v>4.300743664800001</v>
+        <v>4.290698088000001</v>
       </c>
       <c r="Q91">
-        <v>4.4357436648</v>
+        <v>4.425698088000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2338364315828606</v>
+        <v>0.2518686946009293</v>
       </c>
       <c r="T91">
-        <v>4.342642761728881</v>
+        <v>4.759092254063032</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.810372115799533</v>
+        <v>5.745812425623982</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.06102126946009291</v>
+        <v>0.06088429144607117</v>
       </c>
       <c r="C92">
-        <v>3.202577189451716</v>
+        <v>3.002061013201914</v>
       </c>
       <c r="D92">
-        <v>25.90957718945172</v>
+        <v>25.96136101320192</v>
       </c>
       <c r="E92">
-        <v>3.407</v>
+        <v>3.659300000000002</v>
       </c>
       <c r="F92">
-        <v>22.707</v>
+        <v>22.9593</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8825,28 +8825,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M92">
-        <v>1.2556971</v>
+        <v>1.26964929</v>
       </c>
       <c r="N92">
-        <v>5.959302900000001</v>
+        <v>5.94535071</v>
       </c>
       <c r="O92">
-        <v>1.668604812</v>
+        <v>1.6646981988</v>
       </c>
       <c r="P92">
-        <v>4.290698088000001</v>
+        <v>4.2806525112</v>
       </c>
       <c r="Q92">
-        <v>4.425698088000001</v>
+        <v>4.4156525112</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2518686946009293</v>
+        <v>0.2739081271785688</v>
       </c>
       <c r="T92">
-        <v>4.759092254063032</v>
+        <v>5.268086078026992</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.745812425623982</v>
+        <v>5.682671629738004</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.06088429144607117</v>
+        <v>0.06074731343204944</v>
       </c>
       <c r="C93">
-        <v>3.002061013201914</v>
+        <v>2.801752245555335</v>
       </c>
       <c r="D93">
-        <v>25.96136101320192</v>
+        <v>26.01335224555534</v>
       </c>
       <c r="E93">
-        <v>3.659300000000002</v>
+        <v>3.9116</v>
       </c>
       <c r="F93">
-        <v>22.9593</v>
+        <v>23.2116</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8907,28 +8907,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M93">
-        <v>1.26964929</v>
+        <v>1.28360148</v>
       </c>
       <c r="N93">
-        <v>5.94535071</v>
+        <v>5.93139852</v>
       </c>
       <c r="O93">
-        <v>1.6646981988</v>
+        <v>1.6607915856</v>
       </c>
       <c r="P93">
-        <v>4.2806525112</v>
+        <v>4.2706069344</v>
       </c>
       <c r="Q93">
-        <v>4.4156525112</v>
+        <v>4.4056069344</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2739081271785688</v>
+        <v>0.3014574179006182</v>
       </c>
       <c r="T93">
-        <v>5.268086078026992</v>
+        <v>5.904328357981945</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.682671629738004</v>
+        <v>5.620903459849547</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.06074731343204944</v>
+        <v>0.0606103354180277</v>
       </c>
       <c r="C94">
-        <v>2.801752245555335</v>
+        <v>2.601652135106093</v>
       </c>
       <c r="D94">
-        <v>26.01335224555534</v>
+        <v>26.0655521351061</v>
       </c>
       <c r="E94">
-        <v>3.9116</v>
+        <v>4.163900000000002</v>
       </c>
       <c r="F94">
-        <v>23.2116</v>
+        <v>23.4639</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8989,28 +8989,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M94">
-        <v>1.28360148</v>
+        <v>1.29755367</v>
       </c>
       <c r="N94">
-        <v>5.93139852</v>
+        <v>5.917446330000001</v>
       </c>
       <c r="O94">
-        <v>1.6607915856</v>
+        <v>1.6568849724</v>
       </c>
       <c r="P94">
-        <v>4.2706069344</v>
+        <v>4.2605613576</v>
       </c>
       <c r="Q94">
-        <v>4.4056069344</v>
+        <v>4.3955613576</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3014574179006182</v>
+        <v>0.3368779345432532</v>
       </c>
       <c r="T94">
-        <v>5.904328357981945</v>
+        <v>6.722354146495454</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.620903459849547</v>
+        <v>5.560463637700628</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.0606103354180277</v>
+        <v>0.06047335740400597</v>
       </c>
       <c r="C95">
-        <v>2.601652135106093</v>
+        <v>2.401761940490459</v>
       </c>
       <c r="D95">
-        <v>26.0655521351061</v>
+        <v>26.11796194049046</v>
       </c>
       <c r="E95">
-        <v>4.163900000000002</v>
+        <v>4.4162</v>
       </c>
       <c r="F95">
-        <v>23.4639</v>
+        <v>23.7162</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9071,28 +9071,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M95">
-        <v>1.29755367</v>
+        <v>1.31150586</v>
       </c>
       <c r="N95">
-        <v>5.917446330000001</v>
+        <v>5.903494140000001</v>
       </c>
       <c r="O95">
-        <v>1.6568849724</v>
+        <v>1.6529783592</v>
       </c>
       <c r="P95">
-        <v>4.2605613576</v>
+        <v>4.250515780800001</v>
       </c>
       <c r="Q95">
-        <v>4.3955613576</v>
+        <v>4.3855157808</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3368779345432532</v>
+        <v>0.3841052900667665</v>
       </c>
       <c r="T95">
-        <v>6.722354146495454</v>
+        <v>7.813055197846801</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.560463637700628</v>
+        <v>5.501309769214452</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.06047335740400597</v>
+        <v>0.06033637938998423</v>
       </c>
       <c r="C96">
-        <v>2.401761940490459</v>
+        <v>2.202082930488015</v>
       </c>
       <c r="D96">
-        <v>26.11796194049046</v>
+        <v>26.17058293048802</v>
       </c>
       <c r="E96">
-        <v>4.4162</v>
+        <v>4.668500000000002</v>
       </c>
       <c r="F96">
-        <v>23.7162</v>
+        <v>23.9685</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9153,28 +9153,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M96">
-        <v>1.31150586</v>
+        <v>1.32545805</v>
       </c>
       <c r="N96">
-        <v>5.903494140000001</v>
+        <v>5.889541950000001</v>
       </c>
       <c r="O96">
-        <v>1.6529783592</v>
+        <v>1.649071746</v>
       </c>
       <c r="P96">
-        <v>4.250515780800001</v>
+        <v>4.240470204</v>
       </c>
       <c r="Q96">
-        <v>4.3855157808</v>
+        <v>4.375470204</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3841052900667665</v>
+        <v>0.4502235877996851</v>
       </c>
       <c r="T96">
-        <v>7.813055197846801</v>
+        <v>9.340036669738687</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.501309769214452</v>
+        <v>5.443401245327983</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.06033637938998423</v>
+        <v>0.06019940137596248</v>
       </c>
       <c r="C97">
-        <v>2.202082930488015</v>
+        <v>2.002616384124067</v>
       </c>
       <c r="D97">
-        <v>26.17058293048802</v>
+        <v>26.22341638412407</v>
       </c>
       <c r="E97">
-        <v>4.668500000000002</v>
+        <v>4.9208</v>
       </c>
       <c r="F97">
-        <v>23.9685</v>
+        <v>24.2208</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9235,28 +9235,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M97">
-        <v>1.32545805</v>
+        <v>1.33941024</v>
       </c>
       <c r="N97">
-        <v>5.889541950000001</v>
+        <v>5.87558976</v>
       </c>
       <c r="O97">
-        <v>1.649071746</v>
+        <v>1.6451651328</v>
       </c>
       <c r="P97">
-        <v>4.240470204</v>
+        <v>4.2304246272</v>
       </c>
       <c r="Q97">
-        <v>4.375470204</v>
+        <v>4.365424627199999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4502235877996851</v>
+        <v>0.5494010343990632</v>
       </c>
       <c r="T97">
-        <v>9.340036669738687</v>
+        <v>11.63050887757652</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>5.443401245327983</v>
+        <v>5.386699149022483</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.06019940137596249</v>
+        <v>0.06006242336194076</v>
       </c>
       <c r="C98">
-        <v>2.002616384124067</v>
+        <v>1.803363590773216</v>
       </c>
       <c r="D98">
-        <v>26.22341638412407</v>
+        <v>26.27646359077321</v>
       </c>
       <c r="E98">
-        <v>4.9208</v>
+        <v>5.173099999999998</v>
       </c>
       <c r="F98">
-        <v>24.2208</v>
+        <v>24.4731</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9317,28 +9317,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M98">
-        <v>1.33941024</v>
+        <v>1.35336243</v>
       </c>
       <c r="N98">
-        <v>5.87558976</v>
+        <v>5.861637570000001</v>
       </c>
       <c r="O98">
-        <v>1.6451651328</v>
+        <v>1.6412585196</v>
       </c>
       <c r="P98">
-        <v>4.2304246272</v>
+        <v>4.2203790504</v>
       </c>
       <c r="Q98">
-        <v>4.365424627199999</v>
+        <v>4.3553790504</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5494010343990618</v>
+        <v>0.714696778731358</v>
       </c>
       <c r="T98">
-        <v>11.63050887757649</v>
+        <v>15.44796255730619</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>5.386699149022483</v>
+        <v>5.331166168104726</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.06006242336194076</v>
+        <v>0.05992544534791901</v>
       </c>
       <c r="C99">
-        <v>1.803363590773216</v>
+        <v>1.604325850264317</v>
       </c>
       <c r="D99">
-        <v>26.27646359077321</v>
+        <v>26.32972585026432</v>
       </c>
       <c r="E99">
-        <v>5.173099999999998</v>
+        <v>5.4254</v>
       </c>
       <c r="F99">
-        <v>24.4731</v>
+        <v>24.7254</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9399,28 +9399,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M99">
-        <v>1.35336243</v>
+        <v>1.36731462</v>
       </c>
       <c r="N99">
-        <v>5.861637570000001</v>
+        <v>5.847685380000001</v>
       </c>
       <c r="O99">
-        <v>1.6412585196</v>
+        <v>1.6373519064</v>
       </c>
       <c r="P99">
-        <v>4.2203790504</v>
+        <v>4.2103334736</v>
       </c>
       <c r="Q99">
-        <v>4.3553790504</v>
+        <v>4.3453334736</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.714696778731358</v>
+        <v>1.04528826739595</v>
       </c>
       <c r="T99">
-        <v>15.44796255730619</v>
+        <v>23.08286991676559</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.331166168104726</v>
+        <v>5.276766513328147</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.05992544534791901</v>
+        <v>0.05978846733389727</v>
       </c>
       <c r="C100">
-        <v>1.604325850264317</v>
+        <v>1.405504472986614</v>
       </c>
       <c r="D100">
-        <v>26.32972585026432</v>
+        <v>26.38320447298661</v>
       </c>
       <c r="E100">
-        <v>5.4254</v>
+        <v>5.677699999999998</v>
       </c>
       <c r="F100">
-        <v>24.7254</v>
+        <v>24.9777</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9481,28 +9481,28 @@
         <v>7.215000000000001</v>
       </c>
       <c r="M100">
-        <v>1.36731462</v>
+        <v>1.38126681</v>
       </c>
       <c r="N100">
-        <v>5.847685380000001</v>
+        <v>5.83373319</v>
       </c>
       <c r="O100">
-        <v>1.6373519064</v>
+        <v>1.6334452932</v>
       </c>
       <c r="P100">
-        <v>4.2103334736</v>
+        <v>4.2002878968</v>
       </c>
       <c r="Q100">
-        <v>4.3453334736</v>
+        <v>4.3352878968</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.04528826739595</v>
+        <v>2.037062733389726</v>
       </c>
       <c r="T100">
-        <v>23.08286991676559</v>
+        <v>45.98759199514379</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.276766513328147</v>
+        <v>5.223465841476347</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.05978846733389727</v>
-      </c>
-      <c r="C101">
-        <v>1.405504472986614</v>
-      </c>
-      <c r="D101">
-        <v>26.38320447298661</v>
-      </c>
-      <c r="E101">
-        <v>5.677699999999998</v>
-      </c>
-      <c r="F101">
-        <v>24.9777</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>5.93</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>7.350000000000001</v>
-      </c>
-      <c r="K101">
-        <v>0.135</v>
-      </c>
-      <c r="L101">
-        <v>7.215000000000001</v>
-      </c>
-      <c r="M101">
-        <v>1.38126681</v>
-      </c>
-      <c r="N101">
-        <v>5.83373319</v>
-      </c>
-      <c r="O101">
-        <v>1.6334452932</v>
-      </c>
-      <c r="P101">
-        <v>4.2002878968</v>
-      </c>
-      <c r="Q101">
-        <v>4.3352878968</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.037062733389726</v>
-      </c>
-      <c r="T101">
-        <v>45.98759199514379</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.28</v>
-      </c>
-      <c r="W101">
-        <v>0.039816</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.223465841476347</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
